--- a/tables_Trials/kinase_project-trials-tables_values.xlsx
+++ b/tables_Trials/kinase_project-trials-tables_values.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -59,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2705,10 +2703,10 @@
       <c r="F2" s="4" t="n">
         <v>0.07037924507405544</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="4" t="n">
         <v>0.888</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.888</v>
       </c>
       <c r="I2" s="4" t="n">
@@ -2751,10 +2749,10 @@
       <c r="F3" s="4" t="n">
         <v>1.697337126604945</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="4" t="n">
         <v>0.057</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="4" t="n">
         <v>0.057</v>
       </c>
       <c r="I3" s="4" t="n">
@@ -2797,10 +2795,10 @@
       <c r="F4" s="4" t="n">
         <v>1.718500090546677</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="4" t="n">
         <v>0.055</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="4" t="n">
         <v>0.055</v>
       </c>
       <c r="I4" s="4" t="n">
@@ -2841,8 +2839,8 @@
         <v>-0</v>
       </c>
       <c r="F5" s="4" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n">
         <v>0</v>
       </c>
@@ -2879,8 +2877,8 @@
       </c>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n">
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n">
         <v>0.9450000000000001</v>
       </c>
       <c r="I6" s="4" t="n">
@@ -2919,10 +2917,10 @@
       <c r="F7" s="4" t="n">
         <v>0.3146342861669798</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="4" t="n">
         <v>0.588</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.588</v>
       </c>
       <c r="I7" s="4" t="n">
@@ -2965,10 +2963,10 @@
       <c r="F8" s="4" t="n">
         <v>0.5732935355600606</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="4" t="n">
         <v>0.38</v>
       </c>
       <c r="I8" s="4" t="n">
@@ -3009,8 +3007,8 @@
         <v>1.995</v>
       </c>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n">
         <v>0</v>
       </c>
@@ -3049,8 +3047,8 @@
         <v>2.002</v>
       </c>
       <c r="F10" s="4" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n">
         <v>0</v>
       </c>
@@ -3091,10 +3089,10 @@
       <c r="F11" s="4" t="n">
         <v>2.039396480388078</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="4" t="n">
         <v>0.03200000000000001</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="4" t="n">
         <v>0.03200000000000001</v>
       </c>
       <c r="I11" s="4" t="n">
@@ -3133,8 +3131,8 @@
       </c>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n">
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n">
         <v>0.968388</v>
       </c>
       <c r="I12" s="4" t="n">
@@ -3173,10 +3171,10 @@
       <c r="F13" s="4" t="n">
         <v>0.3146342861669798</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="4" t="n">
         <v>0.588</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="4" t="n">
         <v>0.588</v>
       </c>
       <c r="I13" s="4" t="n">
@@ -3219,10 +3217,10 @@
       <c r="F14" s="4" t="n">
         <v>0.5732935355600606</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="4" t="n">
         <v>0.38</v>
       </c>
       <c r="I14" s="4" t="n">
@@ -3263,8 +3261,8 @@
         <v>1.995</v>
       </c>
       <c r="F15" s="4" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n">
         <v>0</v>
       </c>
@@ -3303,8 +3301,8 @@
         <v>2.002</v>
       </c>
       <c r="F16" s="4" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n">
         <v>0</v>
       </c>
@@ -3345,10 +3343,10 @@
       <c r="F17" s="4" t="n">
         <v>2.039396480388078</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="4" t="n">
         <v>0.03200000000000001</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H17" s="4" t="n">
         <v>0.03200000000000001</v>
       </c>
       <c r="I17" s="4" t="n">
@@ -3387,8 +3385,8 @@
       </c>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n">
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n">
         <v>0.968388</v>
       </c>
       <c r="I18" s="4" t="n">
@@ -3427,10 +3425,10 @@
       <c r="F19" s="4" t="n">
         <v>1.407279803103612</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
       <c r="I19" s="4" t="n">
@@ -3471,8 +3469,8 @@
         <v>1</v>
       </c>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n">
         <v>0</v>
       </c>
@@ -3513,10 +3511,10 @@
       <c r="F21" s="4" t="n">
         <v>0.05783560110369775</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G21" s="4" t="n">
         <v>0.907</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="4" t="n">
         <v>0.907</v>
       </c>
       <c r="I21" s="4" t="n">
@@ -3555,8 +3553,8 @@
       </c>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n">
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
       <c r="I22" s="4" t="n">
@@ -3595,10 +3593,10 @@
       <c r="F23" s="4" t="n">
         <v>1.407279803103612</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
       <c r="I23" s="4" t="n">
@@ -3639,8 +3637,8 @@
         <v>1</v>
       </c>
       <c r="F24" s="4" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="n">
         <v>0</v>
       </c>
@@ -3681,10 +3679,10 @@
       <c r="F25" s="4" t="n">
         <v>0.05783560110369775</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="G25" s="4" t="n">
         <v>0.907</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H25" s="4" t="n">
         <v>0.907</v>
       </c>
       <c r="I25" s="4" t="n">
@@ -3723,8 +3721,8 @@
       </c>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n">
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
       <c r="I26" s="4" t="n">
@@ -3763,10 +3761,10 @@
       <c r="F27" s="4" t="n">
         <v>0.3424853662747186</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="4" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H27" s="4" t="n">
         <v>0.5610000000000001</v>
       </c>
       <c r="I27" s="4" t="n">
@@ -3809,10 +3807,10 @@
       <c r="F28" s="4" t="n">
         <v>0.4877791005498772</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="G28" s="4" t="n">
         <v>0.439</v>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H28" s="4" t="n">
         <v>0.439</v>
       </c>
       <c r="I28" s="4" t="n">
@@ -3851,8 +3849,8 @@
       </c>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n">
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n">
         <v>0.5610000000000001</v>
       </c>
       <c r="I29" s="4" t="n">
@@ -3891,10 +3889,10 @@
       <c r="F30" s="4" t="n">
         <v>0.0005927964476482441</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="G30" s="4" t="n">
         <v>0.999</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="4" t="n">
         <v>0.999</v>
       </c>
       <c r="I30" s="4" t="n">
@@ -3935,8 +3933,8 @@
         <v>2</v>
       </c>
       <c r="F31" s="4" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n">
         <v>0</v>
       </c>
@@ -3977,10 +3975,10 @@
       <c r="F32" s="4" t="n">
         <v>4.092845002796916</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G32" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="I32" s="4" t="n">
@@ -4019,8 +4017,8 @@
       </c>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n">
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n">
         <v>0.999</v>
       </c>
       <c r="I33" s="4" t="n">
@@ -4059,10 +4057,10 @@
       <c r="F34" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="G34" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H34" s="4" t="n">
         <v>0.378</v>
       </c>
       <c r="I34" s="4" t="n">
@@ -4105,10 +4103,10 @@
       <c r="F35" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G35" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H35" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I35" s="4" t="n">
@@ -4151,10 +4149,10 @@
       <c r="F36" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G36" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="H36" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
       <c r="I36" s="4" t="n">
@@ -4197,10 +4195,10 @@
       <c r="F37" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="G37" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
       <c r="I37" s="4" t="n">
@@ -4239,8 +4237,8 @@
       </c>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n">
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n">
         <v>1.61</v>
       </c>
       <c r="I38" s="4" t="n">
@@ -4279,10 +4277,10 @@
       <c r="F39" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="G39" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H39" s="4" t="n">
         <v>0.378</v>
       </c>
       <c r="I39" s="4" t="n">
@@ -4325,10 +4323,10 @@
       <c r="F40" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="G40" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="H40" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I40" s="4" t="n">
@@ -4371,10 +4369,10 @@
       <c r="F41" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="G41" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
       <c r="I41" s="4" t="n">
@@ -4417,10 +4415,10 @@
       <c r="F42" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G42" s="5" t="n">
+      <c r="G42" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H42" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
       <c r="I42" s="4" t="n">
@@ -4459,8 +4457,8 @@
       </c>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n">
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n">
         <v>1.61</v>
       </c>
       <c r="I43" s="4" t="n">
@@ -4499,10 +4497,10 @@
       <c r="F44" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="G44" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="H44" s="4" t="n">
         <v>0.378</v>
       </c>
       <c r="I44" s="4" t="n">
@@ -4545,10 +4543,10 @@
       <c r="F45" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="G45" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="H45" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I45" s="4" t="n">
@@ -4591,10 +4589,10 @@
       <c r="F46" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="G46" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H46" s="5" t="n">
+      <c r="H46" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
       <c r="I46" s="4" t="n">
@@ -4637,10 +4635,10 @@
       <c r="F47" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G47" s="5" t="n">
+      <c r="G47" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H47" s="5" t="n">
+      <c r="H47" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
       <c r="I47" s="4" t="n">
@@ -4679,8 +4677,8 @@
       </c>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n">
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n">
         <v>1.61</v>
       </c>
       <c r="I48" s="4" t="n">
@@ -4719,10 +4717,10 @@
       <c r="F49" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="G49" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="H49" s="4" t="n">
         <v>0.378</v>
       </c>
       <c r="I49" s="4" t="n">
@@ -4765,10 +4763,10 @@
       <c r="F50" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G50" s="5" t="n">
+      <c r="G50" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H50" s="5" t="n">
+      <c r="H50" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I50" s="4" t="n">
@@ -4811,10 +4809,10 @@
       <c r="F51" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G51" s="5" t="n">
+      <c r="G51" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H51" s="5" t="n">
+      <c r="H51" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
       <c r="I51" s="4" t="n">
@@ -4857,10 +4855,10 @@
       <c r="F52" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G52" s="5" t="n">
+      <c r="G52" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H52" s="5" t="n">
+      <c r="H52" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
       <c r="I52" s="4" t="n">
@@ -4899,8 +4897,8 @@
       </c>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n">
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n">
         <v>1.61</v>
       </c>
       <c r="I53" s="4" t="n">
@@ -4939,10 +4937,10 @@
       <c r="F54" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G54" s="5" t="n">
+      <c r="G54" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H54" s="5" t="n">
+      <c r="H54" s="4" t="n">
         <v>0.378</v>
       </c>
       <c r="I54" s="4" t="n">
@@ -4985,10 +4983,10 @@
       <c r="F55" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G55" s="5" t="n">
+      <c r="G55" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H55" s="5" t="n">
+      <c r="H55" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I55" s="4" t="n">
@@ -5031,10 +5029,10 @@
       <c r="F56" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G56" s="5" t="n">
+      <c r="G56" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H56" s="5" t="n">
+      <c r="H56" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
       <c r="I56" s="4" t="n">
@@ -5077,10 +5075,10 @@
       <c r="F57" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G57" s="5" t="n">
+      <c r="G57" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H57" s="5" t="n">
+      <c r="H57" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
       <c r="I57" s="4" t="n">
@@ -5119,8 +5117,8 @@
       </c>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n">
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n">
         <v>1.61</v>
       </c>
       <c r="I58" s="4" t="n">
@@ -5159,10 +5157,10 @@
       <c r="F59" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G59" s="5" t="n">
+      <c r="G59" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H59" s="5" t="n">
+      <c r="H59" s="4" t="n">
         <v>0.378</v>
       </c>
       <c r="I59" s="4" t="n">
@@ -5205,10 +5203,10 @@
       <c r="F60" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G60" s="5" t="n">
+      <c r="G60" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H60" s="5" t="n">
+      <c r="H60" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I60" s="4" t="n">
@@ -5251,10 +5249,10 @@
       <c r="F61" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G61" s="5" t="n">
+      <c r="G61" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H61" s="5" t="n">
+      <c r="H61" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
       <c r="I61" s="4" t="n">
@@ -5297,10 +5295,10 @@
       <c r="F62" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G62" s="5" t="n">
+      <c r="G62" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H62" s="5" t="n">
+      <c r="H62" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
       <c r="I62" s="4" t="n">
@@ -5339,8 +5337,8 @@
       </c>
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="n">
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n">
         <v>1.61</v>
       </c>
       <c r="I63" s="4" t="n">
@@ -5379,10 +5377,10 @@
       <c r="F64" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G64" s="5" t="n">
+      <c r="G64" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H64" s="5" t="n">
+      <c r="H64" s="4" t="n">
         <v>0.378</v>
       </c>
       <c r="I64" s="4" t="n">
@@ -5425,10 +5423,10 @@
       <c r="F65" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G65" s="5" t="n">
+      <c r="G65" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H65" s="5" t="n">
+      <c r="H65" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I65" s="4" t="n">
@@ -5471,10 +5469,10 @@
       <c r="F66" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G66" s="5" t="n">
+      <c r="G66" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H66" s="5" t="n">
+      <c r="H66" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
       <c r="I66" s="4" t="n">
@@ -5517,10 +5515,10 @@
       <c r="F67" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G67" s="5" t="n">
+      <c r="G67" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H67" s="5" t="n">
+      <c r="H67" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
       <c r="I67" s="4" t="n">
@@ -5559,8 +5557,8 @@
       </c>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n">
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n">
         <v>1.61</v>
       </c>
       <c r="I68" s="4" t="n">
@@ -5599,10 +5597,10 @@
       <c r="F69" s="4" t="n">
         <v>0.01500080123069177</v>
       </c>
-      <c r="G69" s="5" t="n">
+      <c r="G69" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="H69" s="5" t="n">
+      <c r="H69" s="4" t="n">
         <v>0.975</v>
       </c>
       <c r="I69" s="4" t="n">
@@ -5645,10 +5643,10 @@
       <c r="F70" s="4" t="n">
         <v>2.185661076562508</v>
       </c>
-      <c r="G70" s="5" t="n">
+      <c r="G70" s="4" t="n">
         <v>0.02499999999999999</v>
       </c>
-      <c r="H70" s="5" t="n">
+      <c r="H70" s="4" t="n">
         <v>0.02499999999999999</v>
       </c>
       <c r="I70" s="4" t="n">
@@ -5687,8 +5685,8 @@
       </c>
       <c r="E71" s="4" t="n"/>
       <c r="F71" s="4" t="n"/>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n">
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n">
         <v>0.975</v>
       </c>
       <c r="I71" s="4" t="n">
@@ -5727,10 +5725,10 @@
       <c r="F72" s="4" t="n">
         <v>0.01500080123069177</v>
       </c>
-      <c r="G72" s="5" t="n">
+      <c r="G72" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="H72" s="5" t="n">
+      <c r="H72" s="4" t="n">
         <v>0.975</v>
       </c>
       <c r="I72" s="4" t="n">
@@ -5773,10 +5771,10 @@
       <c r="F73" s="4" t="n">
         <v>2.185661076562508</v>
       </c>
-      <c r="G73" s="5" t="n">
+      <c r="G73" s="4" t="n">
         <v>0.02499999999999999</v>
       </c>
-      <c r="H73" s="5" t="n">
+      <c r="H73" s="4" t="n">
         <v>0.02499999999999999</v>
       </c>
       <c r="I73" s="4" t="n">
@@ -5815,8 +5813,8 @@
       </c>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="5" t="n">
+      <c r="G74" s="4" t="n"/>
+      <c r="H74" s="4" t="n">
         <v>0.975</v>
       </c>
       <c r="I74" s="4" t="n">
@@ -5855,10 +5853,10 @@
       <c r="F75" s="4" t="n">
         <v>0.3046424810811669</v>
       </c>
-      <c r="G75" s="5" t="n">
+      <c r="G75" s="4" t="n">
         <v>0.598</v>
       </c>
-      <c r="H75" s="5" t="n">
+      <c r="H75" s="4" t="n">
         <v>0.598</v>
       </c>
       <c r="I75" s="4" t="n">
@@ -5901,10 +5899,10 @@
       <c r="F76" s="4" t="n">
         <v>0.5971558207992901</v>
       </c>
-      <c r="G76" s="5" t="n">
+      <c r="G76" s="4" t="n">
         <v>0.365</v>
       </c>
-      <c r="H76" s="5" t="n">
+      <c r="H76" s="4" t="n">
         <v>0.365</v>
       </c>
       <c r="I76" s="4" t="n">
@@ -5947,10 +5945,10 @@
       <c r="F77" s="4" t="n">
         <v>1.953376139555213</v>
       </c>
-      <c r="G77" s="5" t="n">
+      <c r="G77" s="4" t="n">
         <v>0.03700000000000001</v>
       </c>
-      <c r="H77" s="5" t="n">
+      <c r="H77" s="4" t="n">
         <v>0.03700000000000001</v>
       </c>
       <c r="I77" s="4" t="n">
@@ -5989,8 +5987,8 @@
       </c>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
-      <c r="G78" s="5" t="n"/>
-      <c r="H78" s="5" t="n">
+      <c r="G78" s="4" t="n"/>
+      <c r="H78" s="4" t="n">
         <v>0.963</v>
       </c>
       <c r="I78" s="4" t="n">
@@ -6029,10 +6027,10 @@
       <c r="F79" s="4" t="n">
         <v>0.004759061730629078</v>
       </c>
-      <c r="G79" s="5" t="n">
+      <c r="G79" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H79" s="4" t="n">
         <v>0.992</v>
       </c>
       <c r="I79" s="4" t="n">
@@ -6073,8 +6071,8 @@
         <v>2</v>
       </c>
       <c r="F80" s="4" t="n"/>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="5" t="n"/>
+      <c r="G80" s="4" t="n"/>
+      <c r="H80" s="4" t="n"/>
       <c r="I80" s="4" t="n">
         <v>0</v>
       </c>
@@ -6115,10 +6113,10 @@
       <c r="F81" s="4" t="n">
         <v>2.860775889351614</v>
       </c>
-      <c r="G81" s="5" t="n">
+      <c r="G81" s="4" t="n">
         <v>0.007999999999999997</v>
       </c>
-      <c r="H81" s="5" t="n">
+      <c r="H81" s="4" t="n">
         <v>0.007999999999999997</v>
       </c>
       <c r="I81" s="4" t="n">
@@ -6157,8 +6155,8 @@
       </c>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="5" t="n">
+      <c r="G82" s="4" t="n"/>
+      <c r="H82" s="4" t="n">
         <v>0.992</v>
       </c>
       <c r="I82" s="4" t="n">
@@ -6197,10 +6195,10 @@
       <c r="F83" s="4" t="n">
         <v>0.004759061730629078</v>
       </c>
-      <c r="G83" s="5" t="n">
+      <c r="G83" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="H83" s="5" t="n">
+      <c r="H83" s="4" t="n">
         <v>0.992</v>
       </c>
       <c r="I83" s="4" t="n">
@@ -6241,8 +6239,8 @@
         <v>2</v>
       </c>
       <c r="F84" s="4" t="n"/>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="5" t="n"/>
+      <c r="G84" s="4" t="n"/>
+      <c r="H84" s="4" t="n"/>
       <c r="I84" s="4" t="n">
         <v>0</v>
       </c>
@@ -6283,10 +6281,10 @@
       <c r="F85" s="4" t="n">
         <v>2.860775889351614</v>
       </c>
-      <c r="G85" s="5" t="n">
+      <c r="G85" s="4" t="n">
         <v>0.007999999999999997</v>
       </c>
-      <c r="H85" s="5" t="n">
+      <c r="H85" s="4" t="n">
         <v>0.007999999999999997</v>
       </c>
       <c r="I85" s="4" t="n">
@@ -6325,8 +6323,8 @@
       </c>
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="n"/>
-      <c r="G86" s="5" t="n"/>
-      <c r="H86" s="5" t="n">
+      <c r="G86" s="4" t="n"/>
+      <c r="H86" s="4" t="n">
         <v>0.992</v>
       </c>
       <c r="I86" s="4" t="n">
@@ -6365,10 +6363,10 @@
       <c r="F87" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G87" s="5" t="n">
+      <c r="G87" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H87" s="5" t="n">
+      <c r="H87" s="4" t="n">
         <v>0.298</v>
       </c>
       <c r="I87" s="4" t="n">
@@ -6411,10 +6409,10 @@
       <c r="F88" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G88" s="5" t="n">
+      <c r="G88" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H88" s="5" t="n">
+      <c r="H88" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I88" s="4" t="n">
@@ -6455,8 +6453,8 @@
         <v>1</v>
       </c>
       <c r="F89" s="4" t="n"/>
-      <c r="G89" s="5" t="n"/>
-      <c r="H89" s="5" t="n"/>
+      <c r="G89" s="4" t="n"/>
+      <c r="H89" s="4" t="n"/>
       <c r="I89" s="4" t="n">
         <v>0</v>
       </c>
@@ -6495,8 +6493,8 @@
         <v>2</v>
       </c>
       <c r="F90" s="4" t="n"/>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="5" t="n"/>
+      <c r="G90" s="4" t="n"/>
+      <c r="H90" s="4" t="n"/>
       <c r="I90" s="4" t="n">
         <v>0</v>
       </c>
@@ -6537,10 +6535,10 @@
       <c r="F91" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G91" s="5" t="n">
+      <c r="G91" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H91" s="5" t="n">
+      <c r="H91" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="I91" s="4" t="n">
@@ -6579,8 +6577,8 @@
       </c>
       <c r="E92" s="4" t="n"/>
       <c r="F92" s="4" t="n"/>
-      <c r="G92" s="5" t="n"/>
-      <c r="H92" s="5" t="n">
+      <c r="G92" s="4" t="n"/>
+      <c r="H92" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="I92" s="4" t="n">
@@ -6619,10 +6617,10 @@
       <c r="F93" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G93" s="5" t="n">
+      <c r="G93" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H93" s="5" t="n">
+      <c r="H93" s="4" t="n">
         <v>0.298</v>
       </c>
       <c r="I93" s="4" t="n">
@@ -6665,10 +6663,10 @@
       <c r="F94" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G94" s="5" t="n">
+      <c r="G94" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H94" s="5" t="n">
+      <c r="H94" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I94" s="4" t="n">
@@ -6709,8 +6707,8 @@
         <v>1</v>
       </c>
       <c r="F95" s="4" t="n"/>
-      <c r="G95" s="5" t="n"/>
-      <c r="H95" s="5" t="n"/>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
       <c r="I95" s="4" t="n">
         <v>0</v>
       </c>
@@ -6749,8 +6747,8 @@
         <v>2</v>
       </c>
       <c r="F96" s="4" t="n"/>
-      <c r="G96" s="5" t="n"/>
-      <c r="H96" s="5" t="n"/>
+      <c r="G96" s="4" t="n"/>
+      <c r="H96" s="4" t="n"/>
       <c r="I96" s="4" t="n">
         <v>0</v>
       </c>
@@ -6791,10 +6789,10 @@
       <c r="F97" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G97" s="5" t="n">
+      <c r="G97" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H97" s="5" t="n">
+      <c r="H97" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="I97" s="4" t="n">
@@ -6833,8 +6831,8 @@
       </c>
       <c r="E98" s="4" t="n"/>
       <c r="F98" s="4" t="n"/>
-      <c r="G98" s="5" t="n"/>
-      <c r="H98" s="5" t="n">
+      <c r="G98" s="4" t="n"/>
+      <c r="H98" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="I98" s="4" t="n">
@@ -6873,10 +6871,10 @@
       <c r="F99" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G99" s="5" t="n">
+      <c r="G99" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H99" s="5" t="n">
+      <c r="H99" s="4" t="n">
         <v>0.298</v>
       </c>
       <c r="I99" s="4" t="n">
@@ -6919,10 +6917,10 @@
       <c r="F100" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G100" s="5" t="n">
+      <c r="G100" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H100" s="5" t="n">
+      <c r="H100" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I100" s="4" t="n">
@@ -6963,8 +6961,8 @@
         <v>1</v>
       </c>
       <c r="F101" s="4" t="n"/>
-      <c r="G101" s="5" t="n"/>
-      <c r="H101" s="5" t="n"/>
+      <c r="G101" s="4" t="n"/>
+      <c r="H101" s="4" t="n"/>
       <c r="I101" s="4" t="n">
         <v>0</v>
       </c>
@@ -7003,8 +7001,8 @@
         <v>2</v>
       </c>
       <c r="F102" s="4" t="n"/>
-      <c r="G102" s="5" t="n"/>
-      <c r="H102" s="5" t="n"/>
+      <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
       <c r="I102" s="4" t="n">
         <v>0</v>
       </c>
@@ -7045,10 +7043,10 @@
       <c r="F103" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G103" s="5" t="n">
+      <c r="G103" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H103" s="5" t="n">
+      <c r="H103" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="I103" s="4" t="n">
@@ -7087,8 +7085,8 @@
       </c>
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="n"/>
-      <c r="G104" s="5" t="n"/>
-      <c r="H104" s="5" t="n">
+      <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="I104" s="4" t="n">
@@ -7127,10 +7125,10 @@
       <c r="F105" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G105" s="5" t="n">
+      <c r="G105" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H105" s="5" t="n">
+      <c r="H105" s="4" t="n">
         <v>0.298</v>
       </c>
       <c r="I105" s="4" t="n">
@@ -7173,10 +7171,10 @@
       <c r="F106" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G106" s="5" t="n">
+      <c r="G106" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H106" s="5" t="n">
+      <c r="H106" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I106" s="4" t="n">
@@ -7217,8 +7215,8 @@
         <v>1</v>
       </c>
       <c r="F107" s="4" t="n"/>
-      <c r="G107" s="5" t="n"/>
-      <c r="H107" s="5" t="n"/>
+      <c r="G107" s="4" t="n"/>
+      <c r="H107" s="4" t="n"/>
       <c r="I107" s="4" t="n">
         <v>0</v>
       </c>
@@ -7257,8 +7255,8 @@
         <v>2</v>
       </c>
       <c r="F108" s="4" t="n"/>
-      <c r="G108" s="5" t="n"/>
-      <c r="H108" s="5" t="n"/>
+      <c r="G108" s="4" t="n"/>
+      <c r="H108" s="4" t="n"/>
       <c r="I108" s="4" t="n">
         <v>0</v>
       </c>
@@ -7299,10 +7297,10 @@
       <c r="F109" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G109" s="5" t="n">
+      <c r="G109" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H109" s="5" t="n">
+      <c r="H109" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="I109" s="4" t="n">
@@ -7341,8 +7339,8 @@
       </c>
       <c r="E110" s="4" t="n"/>
       <c r="F110" s="4" t="n"/>
-      <c r="G110" s="5" t="n"/>
-      <c r="H110" s="5" t="n">
+      <c r="G110" s="4" t="n"/>
+      <c r="H110" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="I110" s="4" t="n">
@@ -7381,10 +7379,10 @@
       <c r="F111" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G111" s="5" t="n">
+      <c r="G111" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H111" s="5" t="n">
+      <c r="H111" s="4" t="n">
         <v>0.298</v>
       </c>
       <c r="I111" s="4" t="n">
@@ -7427,10 +7425,10 @@
       <c r="F112" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G112" s="5" t="n">
+      <c r="G112" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H112" s="5" t="n">
+      <c r="H112" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I112" s="4" t="n">
@@ -7471,8 +7469,8 @@
         <v>1</v>
       </c>
       <c r="F113" s="4" t="n"/>
-      <c r="G113" s="5" t="n"/>
-      <c r="H113" s="5" t="n"/>
+      <c r="G113" s="4" t="n"/>
+      <c r="H113" s="4" t="n"/>
       <c r="I113" s="4" t="n">
         <v>0</v>
       </c>
@@ -7511,8 +7509,8 @@
         <v>2</v>
       </c>
       <c r="F114" s="4" t="n"/>
-      <c r="G114" s="5" t="n"/>
-      <c r="H114" s="5" t="n"/>
+      <c r="G114" s="4" t="n"/>
+      <c r="H114" s="4" t="n"/>
       <c r="I114" s="4" t="n">
         <v>0</v>
       </c>
@@ -7553,10 +7551,10 @@
       <c r="F115" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G115" s="5" t="n">
+      <c r="G115" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H115" s="5" t="n">
+      <c r="H115" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="I115" s="4" t="n">
@@ -7595,8 +7593,8 @@
       </c>
       <c r="E116" s="4" t="n"/>
       <c r="F116" s="4" t="n"/>
-      <c r="G116" s="5" t="n"/>
-      <c r="H116" s="5" t="n">
+      <c r="G116" s="4" t="n"/>
+      <c r="H116" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="I116" s="4" t="n">
@@ -7635,10 +7633,10 @@
       <c r="F117" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G117" s="5" t="n">
+      <c r="G117" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H117" s="5" t="n">
+      <c r="H117" s="4" t="n">
         <v>0.298</v>
       </c>
       <c r="I117" s="4" t="n">
@@ -7681,10 +7679,10 @@
       <c r="F118" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G118" s="5" t="n">
+      <c r="G118" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H118" s="5" t="n">
+      <c r="H118" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I118" s="4" t="n">
@@ -7725,8 +7723,8 @@
         <v>1</v>
       </c>
       <c r="F119" s="4" t="n"/>
-      <c r="G119" s="5" t="n"/>
-      <c r="H119" s="5" t="n"/>
+      <c r="G119" s="4" t="n"/>
+      <c r="H119" s="4" t="n"/>
       <c r="I119" s="4" t="n">
         <v>0</v>
       </c>
@@ -7765,8 +7763,8 @@
         <v>2</v>
       </c>
       <c r="F120" s="4" t="n"/>
-      <c r="G120" s="5" t="n"/>
-      <c r="H120" s="5" t="n"/>
+      <c r="G120" s="4" t="n"/>
+      <c r="H120" s="4" t="n"/>
       <c r="I120" s="4" t="n">
         <v>0</v>
       </c>
@@ -7807,10 +7805,10 @@
       <c r="F121" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G121" s="5" t="n">
+      <c r="G121" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H121" s="5" t="n">
+      <c r="H121" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="I121" s="4" t="n">
@@ -7849,8 +7847,8 @@
       </c>
       <c r="E122" s="4" t="n"/>
       <c r="F122" s="4" t="n"/>
-      <c r="G122" s="5" t="n"/>
-      <c r="H122" s="5" t="n">
+      <c r="G122" s="4" t="n"/>
+      <c r="H122" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="I122" s="4" t="n">
@@ -7889,10 +7887,10 @@
       <c r="F123" s="4" t="n">
         <v>0.03101528962053397</v>
       </c>
-      <c r="G123" s="5" t="n">
+      <c r="G123" s="4" t="n">
         <v>0.949</v>
       </c>
-      <c r="H123" s="5" t="n">
+      <c r="H123" s="4" t="n">
         <v>0.949</v>
       </c>
       <c r="I123" s="4" t="n">
@@ -7933,8 +7931,8 @@
         <v>2</v>
       </c>
       <c r="F124" s="4" t="n"/>
-      <c r="G124" s="5" t="n"/>
-      <c r="H124" s="5" t="n"/>
+      <c r="G124" s="4" t="n"/>
+      <c r="H124" s="4" t="n"/>
       <c r="I124" s="4" t="n">
         <v>0</v>
       </c>
@@ -7975,10 +7973,10 @@
       <c r="F125" s="4" t="n">
         <v>1.763238315407753</v>
       </c>
-      <c r="G125" s="5" t="n">
+      <c r="G125" s="4" t="n">
         <v>0.05099999999999999</v>
       </c>
-      <c r="H125" s="5" t="n">
+      <c r="H125" s="4" t="n">
         <v>0.05099999999999999</v>
       </c>
       <c r="I125" s="4" t="n">
@@ -8017,8 +8015,8 @@
       </c>
       <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="n"/>
-      <c r="G126" s="5" t="n"/>
-      <c r="H126" s="5" t="n">
+      <c r="G126" s="4" t="n"/>
+      <c r="H126" s="4" t="n">
         <v>0.949</v>
       </c>
       <c r="I126" s="4" t="n">
@@ -8057,10 +8055,10 @@
       <c r="F127" s="4" t="n">
         <v>0.01560880538871424</v>
       </c>
-      <c r="G127" s="5" t="n">
+      <c r="G127" s="4" t="n">
         <v>0.9739999999999999</v>
       </c>
-      <c r="H127" s="5" t="n">
+      <c r="H127" s="4" t="n">
         <v>0.974</v>
       </c>
       <c r="I127" s="4" t="n">
@@ -8103,10 +8101,10 @@
       <c r="F128" s="4" t="n">
         <v>3.271465593833381</v>
       </c>
-      <c r="G128" s="5" t="n">
+      <c r="G128" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="H128" s="5" t="n">
+      <c r="H128" s="4" t="n">
         <v>0.004000000000000003</v>
       </c>
       <c r="I128" s="4" t="n">
@@ -8149,10 +8147,10 @@
       <c r="F129" s="4" t="n">
         <v>4.092845002796916</v>
       </c>
-      <c r="G129" s="5" t="n">
+      <c r="G129" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="H129" s="5" t="n">
+      <c r="H129" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="I129" s="4" t="n">
@@ -8193,8 +8191,8 @@
         <v>1</v>
       </c>
       <c r="F130" s="4" t="n"/>
-      <c r="G130" s="5" t="n"/>
-      <c r="H130" s="5" t="n"/>
+      <c r="G130" s="4" t="n"/>
+      <c r="H130" s="4" t="n"/>
       <c r="I130" s="4" t="n">
         <v>0</v>
       </c>
@@ -8233,8 +8231,8 @@
         <v>2</v>
       </c>
       <c r="F131" s="4" t="n"/>
-      <c r="G131" s="5" t="n"/>
-      <c r="H131" s="5" t="n"/>
+      <c r="G131" s="4" t="n"/>
+      <c r="H131" s="4" t="n"/>
       <c r="I131" s="4" t="n">
         <v>0</v>
       </c>
@@ -8273,8 +8271,8 @@
         <v>2</v>
       </c>
       <c r="F132" s="4" t="n"/>
-      <c r="G132" s="5" t="n"/>
-      <c r="H132" s="5" t="n"/>
+      <c r="G132" s="4" t="n"/>
+      <c r="H132" s="4" t="n"/>
       <c r="I132" s="4" t="n">
         <v>0</v>
       </c>
@@ -8315,10 +8313,10 @@
       <c r="F133" s="4" t="n">
         <v>2.288965458445788</v>
       </c>
-      <c r="G133" s="5" t="n">
+      <c r="G133" s="4" t="n">
         <v>0.021</v>
       </c>
-      <c r="H133" s="5" t="n">
+      <c r="H133" s="4" t="n">
         <v>0.02100000000000001</v>
       </c>
       <c r="I133" s="4" t="n">
@@ -8357,8 +8355,8 @@
       </c>
       <c r="E134" s="4" t="n"/>
       <c r="F134" s="4" t="n"/>
-      <c r="G134" s="5" t="n"/>
-      <c r="H134" s="5" t="n">
+      <c r="G134" s="4" t="n"/>
+      <c r="H134" s="4" t="n">
         <v>0.979</v>
       </c>
       <c r="I134" s="4" t="n">
@@ -8397,10 +8395,10 @@
       <c r="F135" s="4" t="n">
         <v>2.097722223529931</v>
       </c>
-      <c r="G135" s="5" t="n">
+      <c r="G135" s="4" t="n">
         <v>0.02899999999999998</v>
       </c>
-      <c r="H135" s="5" t="n">
+      <c r="H135" s="4" t="n">
         <v>0.02899999999999998</v>
       </c>
       <c r="I135" s="4" t="n">
@@ -8443,10 +8441,10 @@
       <c r="F136" s="4" t="n">
         <v>0.01743657033430621</v>
       </c>
-      <c r="G136" s="5" t="n">
+      <c r="G136" s="4" t="n">
         <v>0.971</v>
       </c>
-      <c r="H136" s="5" t="n">
+      <c r="H136" s="4" t="n">
         <v>0.971</v>
       </c>
       <c r="I136" s="4" t="n">
@@ -8485,8 +8483,8 @@
       </c>
       <c r="E137" s="4" t="n"/>
       <c r="F137" s="4" t="n"/>
-      <c r="G137" s="5" t="n"/>
-      <c r="H137" s="5" t="n">
+      <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n">
         <v>0.02899999999999998</v>
       </c>
       <c r="I137" s="4" t="n">
@@ -8525,10 +8523,10 @@
       <c r="F138" s="4" t="n">
         <v>0.00835361269485466</v>
       </c>
-      <c r="G138" s="5" t="n">
+      <c r="G138" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="H138" s="5" t="n">
+      <c r="H138" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
       <c r="I138" s="4" t="n">
@@ -8571,10 +8569,10 @@
       <c r="F139" s="4" t="n">
         <v>2.529203534999876</v>
       </c>
-      <c r="G139" s="5" t="n">
+      <c r="G139" s="4" t="n">
         <v>0.01399999999999999</v>
       </c>
-      <c r="H139" s="5" t="n">
+      <c r="H139" s="4" t="n">
         <v>0.01399999999999999</v>
       </c>
       <c r="I139" s="4" t="n">
@@ -8615,8 +8613,8 @@
         <v>-0</v>
       </c>
       <c r="F140" s="4" t="n"/>
-      <c r="G140" s="5" t="n"/>
-      <c r="H140" s="5" t="n"/>
+      <c r="G140" s="4" t="n"/>
+      <c r="H140" s="4" t="n"/>
       <c r="I140" s="4" t="n">
         <v>0</v>
       </c>
@@ -8653,8 +8651,8 @@
       </c>
       <c r="E141" s="4" t="n"/>
       <c r="F141" s="4" t="n"/>
-      <c r="G141" s="5" t="n"/>
-      <c r="H141" s="5" t="n">
+      <c r="G141" s="4" t="n"/>
+      <c r="H141" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
       <c r="I141" s="4" t="n">
@@ -8693,10 +8691,10 @@
       <c r="F142" s="4" t="n">
         <v>0.00835361269485466</v>
       </c>
-      <c r="G142" s="5" t="n">
+      <c r="G142" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="H142" s="5" t="n">
+      <c r="H142" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
       <c r="I142" s="4" t="n">
@@ -8739,10 +8737,10 @@
       <c r="F143" s="4" t="n">
         <v>2.529203534999876</v>
       </c>
-      <c r="G143" s="5" t="n">
+      <c r="G143" s="4" t="n">
         <v>0.01399999999999999</v>
       </c>
-      <c r="H143" s="5" t="n">
+      <c r="H143" s="4" t="n">
         <v>0.01399999999999999</v>
       </c>
       <c r="I143" s="4" t="n">
@@ -8783,8 +8781,8 @@
         <v>-0</v>
       </c>
       <c r="F144" s="4" t="n"/>
-      <c r="G144" s="5" t="n"/>
-      <c r="H144" s="5" t="n"/>
+      <c r="G144" s="4" t="n"/>
+      <c r="H144" s="4" t="n"/>
       <c r="I144" s="4" t="n">
         <v>0</v>
       </c>
@@ -8821,8 +8819,8 @@
       </c>
       <c r="E145" s="4" t="n"/>
       <c r="F145" s="4" t="n"/>
-      <c r="G145" s="5" t="n"/>
-      <c r="H145" s="5" t="n">
+      <c r="G145" s="4" t="n"/>
+      <c r="H145" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
       <c r="I145" s="4" t="n">
@@ -8861,10 +8859,10 @@
       <c r="F146" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G146" s="5" t="n">
+      <c r="G146" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H146" s="5" t="n">
+      <c r="H146" s="4" t="n">
         <v>0.378</v>
       </c>
       <c r="I146" s="4" t="n">
@@ -8907,10 +8905,10 @@
       <c r="F147" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G147" s="5" t="n">
+      <c r="G147" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H147" s="5" t="n">
+      <c r="H147" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
       <c r="I147" s="4" t="n">
@@ -8953,10 +8951,10 @@
       <c r="F148" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G148" s="5" t="n">
+      <c r="G148" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H148" s="5" t="n">
+      <c r="H148" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
       <c r="I148" s="4" t="n">
@@ -8999,10 +8997,10 @@
       <c r="F149" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G149" s="5" t="n">
+      <c r="G149" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H149" s="5" t="n">
+      <c r="H149" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
       <c r="I149" s="4" t="n">
@@ -9041,8 +9039,8 @@
       </c>
       <c r="E150" s="4" t="n"/>
       <c r="F150" s="4" t="n"/>
-      <c r="G150" s="5" t="n"/>
-      <c r="H150" s="5" t="n">
+      <c r="G150" s="4" t="n"/>
+      <c r="H150" s="4" t="n">
         <v>1.61</v>
       </c>
       <c r="I150" s="4" t="n">
@@ -9081,10 +9079,10 @@
       <c r="F151" s="4" t="n">
         <v>3.441917221761061</v>
       </c>
-      <c r="G151" s="5" t="n">
+      <c r="G151" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="H151" s="5" t="n">
+      <c r="H151" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
       <c r="I151" s="4" t="n">
@@ -9127,10 +9125,10 @@
       <c r="F152" s="4" t="n">
         <v>0.1248522110545241</v>
       </c>
-      <c r="G152" s="5" t="n">
+      <c r="G152" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H152" s="5" t="n">
+      <c r="H152" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="I152" s="4" t="n">
@@ -9173,10 +9171,10 @@
       <c r="F153" s="4" t="n">
         <v>0.9934131473105738</v>
       </c>
-      <c r="G153" s="5" t="n">
+      <c r="G153" s="4" t="n">
         <v>0.187</v>
       </c>
-      <c r="H153" s="5" t="n">
+      <c r="H153" s="4" t="n">
         <v>0.187</v>
       </c>
       <c r="I153" s="4" t="n">
@@ -9215,8 +9213,8 @@
       </c>
       <c r="E154" s="4" t="n"/>
       <c r="F154" s="4" t="n"/>
-      <c r="G154" s="5" t="n"/>
-      <c r="H154" s="5" t="n">
+      <c r="G154" s="4" t="n"/>
+      <c r="H154" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
       <c r="I154" s="4" t="n">
@@ -9255,10 +9253,10 @@
       <c r="F155" s="4" t="n">
         <v>3.441917221761061</v>
       </c>
-      <c r="G155" s="5" t="n">
+      <c r="G155" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="H155" s="5" t="n">
+      <c r="H155" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
       <c r="I155" s="4" t="n">
@@ -9301,10 +9299,10 @@
       <c r="F156" s="4" t="n">
         <v>0.1248522110545241</v>
       </c>
-      <c r="G156" s="5" t="n">
+      <c r="G156" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H156" s="5" t="n">
+      <c r="H156" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="I156" s="4" t="n">
@@ -9347,10 +9345,10 @@
       <c r="F157" s="4" t="n">
         <v>0.9934131473105738</v>
       </c>
-      <c r="G157" s="5" t="n">
+      <c r="G157" s="4" t="n">
         <v>0.187</v>
       </c>
-      <c r="H157" s="5" t="n">
+      <c r="H157" s="4" t="n">
         <v>0.187</v>
       </c>
       <c r="I157" s="4" t="n">
@@ -9389,8 +9387,8 @@
       </c>
       <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="n"/>
-      <c r="G158" s="5" t="n"/>
-      <c r="H158" s="5" t="n">
+      <c r="G158" s="4" t="n"/>
+      <c r="H158" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
       <c r="I158" s="4" t="n">
@@ -9427,8 +9425,8 @@
         <v>-1</v>
       </c>
       <c r="F159" s="4" t="n"/>
-      <c r="G159" s="5" t="n"/>
-      <c r="H159" s="5" t="n"/>
+      <c r="G159" s="4" t="n"/>
+      <c r="H159" s="4" t="n"/>
       <c r="I159" s="4" t="n">
         <v>0</v>
       </c>
@@ -9467,8 +9465,8 @@
         <v>-1</v>
       </c>
       <c r="F160" s="4" t="n"/>
-      <c r="G160" s="5" t="n"/>
-      <c r="H160" s="5" t="n"/>
+      <c r="G160" s="4" t="n"/>
+      <c r="H160" s="4" t="n"/>
       <c r="I160" s="4" t="n">
         <v>0</v>
       </c>
@@ -9509,10 +9507,10 @@
       <c r="F161" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="G161" s="5" t="n">
+      <c r="G161" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H161" s="5" t="n">
+      <c r="H161" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I161" s="4" t="n">
@@ -9551,8 +9549,8 @@
       </c>
       <c r="E162" s="4" t="n"/>
       <c r="F162" s="4" t="n"/>
-      <c r="G162" s="5" t="n"/>
-      <c r="H162" s="5" t="n">
+      <c r="G162" s="4" t="n"/>
+      <c r="H162" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I162" s="4" t="n">
@@ -9591,10 +9589,10 @@
       <c r="F163" s="4" t="n">
         <v>3.271465593833381</v>
       </c>
-      <c r="G163" s="5" t="n">
+      <c r="G163" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="H163" s="5" t="n">
+      <c r="H163" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
       <c r="I163" s="4" t="n">
@@ -9635,8 +9633,8 @@
         <v>-1</v>
       </c>
       <c r="F164" s="4" t="n"/>
-      <c r="G164" s="5" t="n"/>
-      <c r="H164" s="5" t="n"/>
+      <c r="G164" s="4" t="n"/>
+      <c r="H164" s="4" t="n"/>
       <c r="I164" s="4" t="n">
         <v>0</v>
       </c>
@@ -9677,10 +9675,10 @@
       <c r="F165" s="4" t="n">
         <v>0.003565707852896025</v>
       </c>
-      <c r="G165" s="5" t="n">
+      <c r="G165" s="4" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="H165" s="5" t="n">
+      <c r="H165" s="4" t="n">
         <v>0.9940000000000001</v>
       </c>
       <c r="I165" s="4" t="n">
@@ -9723,10 +9721,10 @@
       <c r="F166" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G166" s="5" t="n">
+      <c r="G166" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H166" s="5" t="n">
+      <c r="H166" s="4" t="n">
         <v>0.002</v>
       </c>
       <c r="I166" s="4" t="n">
@@ -9765,8 +9763,8 @@
       </c>
       <c r="E167" s="4" t="n"/>
       <c r="F167" s="4" t="n"/>
-      <c r="G167" s="5" t="n"/>
-      <c r="H167" s="5" t="n">
+      <c r="G167" s="4" t="n"/>
+      <c r="H167" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
       <c r="I167" s="4" t="n">
@@ -9805,10 +9803,10 @@
       <c r="F168" s="4" t="n">
         <v>3.271465593833381</v>
       </c>
-      <c r="G168" s="5" t="n">
+      <c r="G168" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="H168" s="5" t="n">
+      <c r="H168" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
       <c r="I168" s="4" t="n">
@@ -9849,8 +9847,8 @@
         <v>-1</v>
       </c>
       <c r="F169" s="4" t="n"/>
-      <c r="G169" s="5" t="n"/>
-      <c r="H169" s="5" t="n"/>
+      <c r="G169" s="4" t="n"/>
+      <c r="H169" s="4" t="n"/>
       <c r="I169" s="4" t="n">
         <v>0</v>
       </c>
@@ -9891,10 +9889,10 @@
       <c r="F170" s="4" t="n">
         <v>0.003565707852896025</v>
       </c>
-      <c r="G170" s="5" t="n">
+      <c r="G170" s="4" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="H170" s="5" t="n">
+      <c r="H170" s="4" t="n">
         <v>0.9940000000000001</v>
       </c>
       <c r="I170" s="4" t="n">
@@ -9937,10 +9935,10 @@
       <c r="F171" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G171" s="5" t="n">
+      <c r="G171" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H171" s="5" t="n">
+      <c r="H171" s="4" t="n">
         <v>0.002</v>
       </c>
       <c r="I171" s="4" t="n">
@@ -9979,8 +9977,8 @@
       </c>
       <c r="E172" s="4" t="n"/>
       <c r="F172" s="4" t="n"/>
-      <c r="G172" s="5" t="n"/>
-      <c r="H172" s="5" t="n">
+      <c r="G172" s="4" t="n"/>
+      <c r="H172" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
       <c r="I172" s="4" t="n">
@@ -10019,10 +10017,10 @@
       <c r="F173" s="4" t="n">
         <v>0.007753004432578372</v>
       </c>
-      <c r="G173" s="5" t="n">
+      <c r="G173" s="4" t="n">
         <v>0.987</v>
       </c>
-      <c r="H173" s="5" t="n">
+      <c r="H173" s="4" t="n">
         <v>0.987</v>
       </c>
       <c r="I173" s="4" t="n">
@@ -10065,10 +10063,10 @@
       <c r="F174" s="4" t="n">
         <v>2.573112508500956</v>
       </c>
-      <c r="G174" s="5" t="n">
+      <c r="G174" s="4" t="n">
         <v>0.013</v>
       </c>
-      <c r="H174" s="5" t="n">
+      <c r="H174" s="4" t="n">
         <v>0.013</v>
       </c>
       <c r="I174" s="4" t="n">
@@ -10109,8 +10107,8 @@
         <v>-0</v>
       </c>
       <c r="F175" s="4" t="n"/>
-      <c r="G175" s="5" t="n"/>
-      <c r="H175" s="5" t="n"/>
+      <c r="G175" s="4" t="n"/>
+      <c r="H175" s="4" t="n"/>
       <c r="I175" s="4" t="n">
         <v>0</v>
       </c>
@@ -10149,8 +10147,8 @@
         <v>-0</v>
       </c>
       <c r="F176" s="4" t="n"/>
-      <c r="G176" s="5" t="n"/>
-      <c r="H176" s="5" t="n"/>
+      <c r="G176" s="4" t="n"/>
+      <c r="H176" s="4" t="n"/>
       <c r="I176" s="4" t="n">
         <v>0</v>
       </c>
@@ -10187,8 +10185,8 @@
       </c>
       <c r="E177" s="4" t="n"/>
       <c r="F177" s="4" t="n"/>
-      <c r="G177" s="5" t="n"/>
-      <c r="H177" s="5" t="n">
+      <c r="G177" s="4" t="n"/>
+      <c r="H177" s="4" t="n">
         <v>0.987</v>
       </c>
       <c r="I177" s="4" t="n">

--- a/tables_Trials/kinase_project-trials-tables_values.xlsx
+++ b/tables_Trials/kinase_project-trials-tables_values.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.###;-0.###;0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -58,12 +59,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2697,28 +2699,28 @@
           <t>DB8+1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>0.07037924507405544</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>0.888</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>0.888</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>0.888</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="n">
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="n">
         <v>0.5596666666666668</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="5" t="n">
         <v>0.001452966314513559</v>
       </c>
     </row>
@@ -2743,28 +2745,28 @@
           <t>DB8+2</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>1.697337126604945</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>0.057</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>0.057</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>0.057</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="n">
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>0.3966666666666667</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="5" t="n">
         <v>0.002333333333333335</v>
       </c>
     </row>
@@ -2789,28 +2791,28 @@
           <t>DB801</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>1.718500090546677</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>0.055</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>0.055</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>0.055</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>0.04366666666666667</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="5" t="n">
         <v>0.0008819171036881955</v>
       </c>
     </row>
@@ -2835,22 +2837,22 @@
           <t>DB802</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n">
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2875,20 +2877,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>0.9450000000000001</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>0.9450000000000001</v>
       </c>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n">
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n">
         <v>0.9563333333333335</v>
       </c>
-      <c r="L6" s="4" t="n"/>
+      <c r="L6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2911,28 +2913,28 @@
           <t>STI+1</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>1.004</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>0.3146342861669798</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>0.588</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>0.588</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="5" t="n">
         <v>0.588</v>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="n">
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="5" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -2957,28 +2959,28 @@
           <t>STI+2</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>0.995</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <v>0.5732935355600606</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="5" t="n">
         <v>0.38</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <v>0.38</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="5" t="n">
         <v>0.3800000000000001</v>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4" t="n">
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>0.999</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="5" t="n">
         <v>0.001000000000000001</v>
       </c>
     </row>
@@ -3003,22 +3005,22 @@
           <t>STI+a</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>1.995</v>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="n">
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3043,22 +3045,22 @@
           <t>STI+b</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>2.002</v>
       </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="n">
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3083,28 +3085,28 @@
           <t>STI01</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="5" t="n">
         <v>-0.002</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <v>2.039396480388078</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="5" t="n">
         <v>0.03200000000000001</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="5" t="n">
         <v>0.03200000000000001</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="5" t="n">
         <v>0.032</v>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="n">
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3129,20 +3131,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n">
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n">
         <v>0.968388</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="5" t="n">
         <v>0.9683880000000001</v>
       </c>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n">
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n">
         <v>0.995009</v>
       </c>
-      <c r="L12" s="4" t="n"/>
+      <c r="L12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3165,28 +3167,28 @@
           <t>STI+1</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
         <v>1.004</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>0.3146342861669798</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="5" t="n">
         <v>0.588</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="5" t="n">
         <v>0.588</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="5" t="n">
         <v>0.588</v>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="5" t="n">
         <v>0.001527525231651947</v>
       </c>
     </row>
@@ -3211,28 +3213,28 @@
           <t>STI+2</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="5" t="n">
         <v>0.995</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="5" t="n">
         <v>0.5732935355600606</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="5" t="n">
         <v>0.38</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="5" t="n">
         <v>0.38</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="5" t="n">
         <v>0.3800000000000001</v>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="n">
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>0.997</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="5" t="n">
         <v>0.001527525231651948</v>
       </c>
     </row>
@@ -3257,22 +3259,22 @@
           <t>STI+a</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="5" t="n">
         <v>1.995</v>
       </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="n">
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3297,22 +3299,22 @@
           <t>STI+b</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="5" t="n">
         <v>2.002</v>
       </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="n">
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3337,28 +3339,28 @@
           <t>STI01</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="5" t="n">
         <v>-0.002</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="5" t="n">
         <v>2.039396480388078</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="5" t="n">
         <v>0.03200000000000001</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="5" t="n">
         <v>0.03200000000000001</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="5" t="n">
         <v>0.032</v>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="n">
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3383,20 +3385,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n">
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n">
         <v>0.968388</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="5" t="n">
         <v>0.9683880000000001</v>
       </c>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n">
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n">
         <v>0.995027</v>
       </c>
-      <c r="L18" s="4" t="n"/>
+      <c r="L18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3419,28 +3421,28 @@
           <t>NIL+1</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="5" t="n">
         <v>1.407279803103612</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="5" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="5" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="5" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
         <v>0.324</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="5" t="n">
         <v>0.1406307221058045</v>
       </c>
     </row>
@@ -3465,22 +3467,22 @@
           <t>NIL+2</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="n">
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3505,28 +3507,28 @@
           <t>NIL01</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="5" t="n">
         <v>0.05783560110369775</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="5" t="n">
         <v>0.907</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="5" t="n">
         <v>0.907</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" s="5" t="n">
         <v>0.907</v>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="n">
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="n">
         <v>0.676</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="5" t="n">
         <v>0.1406307221058045</v>
       </c>
     </row>
@@ -3551,20 +3553,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n">
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I22" s="5" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n">
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n">
         <v>0.324</v>
       </c>
-      <c r="L22" s="4" t="n"/>
+      <c r="L22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3587,28 +3589,28 @@
           <t>NIL+1</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="5" t="n">
         <v>1.407279803103612</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="5" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="5" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" s="5" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4" t="n">
+      <c r="J23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5" t="n">
         <v>0.3123333333333333</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="5" t="n">
         <v>0.08504377957525433</v>
       </c>
     </row>
@@ -3633,22 +3635,22 @@
           <t>NIL+2</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="4" t="n">
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3673,28 +3675,28 @@
           <t>NIL01</t>
         </is>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="5" t="n">
         <v>0.05783560110369775</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="5" t="n">
         <v>0.907</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="5" t="n">
         <v>0.907</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" s="5" t="n">
         <v>0.907</v>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="4" t="n">
+      <c r="J25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5" t="n">
         <v>0.6876666666666668</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="5" t="n">
         <v>0.08504377957525433</v>
       </c>
     </row>
@@ -3719,20 +3721,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n">
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I26" s="5" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n">
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n">
         <v>0.3123333333333333</v>
       </c>
-      <c r="L26" s="4" t="n"/>
+      <c r="L26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3755,28 +3757,28 @@
           <t>EMH+1</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="5" t="n">
         <v>0.3424853662747186</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="5" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="5" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="I27" s="5" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="4" t="n">
+      <c r="J27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5" t="n">
         <v>0.827</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L27" s="5" t="n">
         <v>0.03750999866702211</v>
       </c>
     </row>
@@ -3801,28 +3803,28 @@
           <t>EMH01</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="5" t="n">
         <v>0.4877791005498772</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="5" t="n">
         <v>0.439</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="5" t="n">
         <v>0.439</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" s="5" t="n">
         <v>0.439</v>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="4" t="n">
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
         <v>0.173</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="5" t="n">
         <v>0.03750999866702211</v>
       </c>
     </row>
@@ -3847,20 +3849,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n">
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="I29" s="5" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n">
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n">
         <v>0.827</v>
       </c>
-      <c r="L29" s="4" t="n"/>
+      <c r="L29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3883,28 +3885,28 @@
           <t>4MK+1</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="5" t="n">
         <v>0.0005927964476482441</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="5" t="n">
         <v>0.999</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="5" t="n">
         <v>0.999</v>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="I30" s="5" t="n">
         <v>0.999</v>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4" t="n">
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3929,22 +3931,22 @@
           <t>4MK+a</t>
         </is>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="4" t="n">
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3969,28 +3971,28 @@
           <t>4MK01</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="5" t="n">
         <v>4.092845002796916</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I32" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="J32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="n">
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4015,20 +4017,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n">
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n">
         <v>0.999</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="I33" s="5" t="n">
         <v>0.999</v>
       </c>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n">
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L33" s="4" t="n"/>
+      <c r="L33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4051,28 +4053,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="5" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="5" t="n">
         <v>0.378</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I34" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="4" t="n">
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4097,28 +4099,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I35" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="4" t="n">
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4143,28 +4145,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="5" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="5" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="I36" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="J36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="n">
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4189,28 +4191,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="n">
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="5" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="5" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I37" s="5" t="n">
         <v>0.005</v>
       </c>
-      <c r="J37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="n">
+      <c r="J37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4235,20 +4237,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="I38" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n">
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L38" s="4" t="n"/>
+      <c r="L38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4271,28 +4273,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="5" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="5" t="n">
         <v>0.378</v>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="I39" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="4" t="n">
+      <c r="J39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="L39" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4317,28 +4319,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="I40" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="4" t="n">
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4363,28 +4365,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="5" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="5" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="I41" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="J41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4" t="n">
+      <c r="J41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4409,28 +4411,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4" t="n">
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="5" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="5" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="I42" s="5" t="n">
         <v>0.005</v>
       </c>
-      <c r="J42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="n">
+      <c r="J42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4455,20 +4457,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="I43" s="4" t="n">
+      <c r="I43" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n">
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L43" s="4" t="n"/>
+      <c r="L43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4491,28 +4493,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="5" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="5" t="n">
         <v>0.378</v>
       </c>
-      <c r="I44" s="4" t="n">
+      <c r="I44" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="4" t="n">
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="L44" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4537,28 +4539,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="I45" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="4" t="n">
+      <c r="J45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4583,28 +4585,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="5" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="H46" s="5" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I46" s="4" t="n">
+      <c r="I46" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="J46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4" t="n">
+      <c r="J46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4629,28 +4631,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="n">
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="5" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="H47" s="5" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I47" s="4" t="n">
+      <c r="I47" s="5" t="n">
         <v>0.005</v>
       </c>
-      <c r="J47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="4" t="n">
+      <c r="J47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4675,20 +4677,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n">
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="I48" s="4" t="n">
+      <c r="I48" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="n">
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L48" s="4" t="n"/>
+      <c r="L48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4711,28 +4713,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="F49" s="5" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="H49" s="5" t="n">
         <v>0.378</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="I49" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4" t="n">
+      <c r="J49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="L49" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4757,28 +4759,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="H50" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I50" s="4" t="n">
+      <c r="I50" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="4" t="n">
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4803,28 +4805,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="5" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="5" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I51" s="4" t="n">
+      <c r="I51" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="J51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="n">
+      <c r="J51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4849,28 +4851,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="4" t="n">
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="5" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="H52" s="5" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I52" s="4" t="n">
+      <c r="I52" s="5" t="n">
         <v>0.005</v>
       </c>
-      <c r="J52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="n">
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4895,20 +4897,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="I53" s="4" t="n">
+      <c r="I53" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n">
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L53" s="4" t="n"/>
+      <c r="L53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4931,28 +4933,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="F54" s="5" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="H54" s="5" t="n">
         <v>0.378</v>
       </c>
-      <c r="I54" s="4" t="n">
+      <c r="I54" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="4" t="n">
+      <c r="J54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L54" s="4" t="n">
+      <c r="L54" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4977,28 +4979,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I55" s="4" t="n">
+      <c r="I55" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="4" t="n">
+      <c r="J55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5023,28 +5025,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="5" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H56" s="5" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I56" s="4" t="n">
+      <c r="I56" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="J56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4" t="n">
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5069,28 +5071,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="4" t="n">
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="5" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="5" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="I57" s="5" t="n">
         <v>0.005</v>
       </c>
-      <c r="J57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="n">
+      <c r="J57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5115,20 +5117,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n">
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="I58" s="4" t="n">
+      <c r="I58" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n">
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L58" s="4" t="n"/>
+      <c r="L58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5151,28 +5153,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="5" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H59" s="5" t="n">
         <v>0.378</v>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="I59" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="4" t="n">
+      <c r="J59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="L59" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5197,28 +5199,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="E60" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="F60" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H60" s="4" t="n">
+      <c r="H60" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I60" s="4" t="n">
+      <c r="I60" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="n">
+      <c r="J60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5243,28 +5245,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" s="5" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="H61" s="4" t="n">
+      <c r="H61" s="5" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I61" s="4" t="n">
+      <c r="I61" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="J61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="4" t="n">
+      <c r="J61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5289,28 +5291,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="4" t="n">
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="5" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="H62" s="5" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I62" s="4" t="n">
+      <c r="I62" s="5" t="n">
         <v>0.005</v>
       </c>
-      <c r="J62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="n">
+      <c r="J62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5335,20 +5337,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n">
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="I63" s="4" t="n">
+      <c r="I63" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="n">
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L63" s="4" t="n"/>
+      <c r="L63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5371,28 +5373,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="5" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H64" s="4" t="n">
+      <c r="H64" s="5" t="n">
         <v>0.378</v>
       </c>
-      <c r="I64" s="4" t="n">
+      <c r="I64" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="4" t="n">
+      <c r="J64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L64" s="4" t="n">
+      <c r="L64" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5417,28 +5419,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="F65" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="H65" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="I65" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="n">
+      <c r="J65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5463,28 +5465,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="F66" s="5" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="H66" s="4" t="n">
+      <c r="H66" s="5" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I66" s="4" t="n">
+      <c r="I66" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="J66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="n">
+      <c r="J66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5509,28 +5511,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="4" t="n">
+      <c r="E67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="5" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="5" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H67" s="4" t="n">
+      <c r="H67" s="5" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I67" s="4" t="n">
+      <c r="I67" s="5" t="n">
         <v>0.005</v>
       </c>
-      <c r="J67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="4" t="n">
+      <c r="J67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5555,20 +5557,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="4" t="n">
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="I68" s="4" t="n">
+      <c r="I68" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="J68" s="4" t="n"/>
-      <c r="K68" s="4" t="n">
+      <c r="J68" s="5" t="n"/>
+      <c r="K68" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L68" s="4" t="n"/>
+      <c r="L68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5591,28 +5593,28 @@
           <t>LQQ+1</t>
         </is>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="F69" s="5" t="n">
         <v>0.01500080123069177</v>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="H69" s="4" t="n">
+      <c r="H69" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="I69" s="4" t="n">
+      <c r="I69" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="J69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="4" t="n">
+      <c r="J69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="5" t="n">
         <v>0.999</v>
       </c>
-      <c r="L69" s="4" t="n">
+      <c r="L69" s="5" t="n">
         <v>0.0005773502691896263</v>
       </c>
     </row>
@@ -5637,28 +5639,28 @@
           <t>LQQ01</t>
         </is>
       </c>
-      <c r="E70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="4" t="n">
+      <c r="E70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="5" t="n">
         <v>2.185661076562508</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="5" t="n">
         <v>0.02499999999999999</v>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="H70" s="5" t="n">
         <v>0.02499999999999999</v>
       </c>
-      <c r="I70" s="4" t="n">
+      <c r="I70" s="5" t="n">
         <v>0.025</v>
       </c>
-      <c r="J70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="4" t="n">
+      <c r="J70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="L70" s="4" t="n">
+      <c r="L70" s="5" t="n">
         <v>0.0005773502691896258</v>
       </c>
     </row>
@@ -5683,20 +5685,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n">
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="I71" s="4" t="n">
+      <c r="I71" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="J71" s="4" t="n"/>
-      <c r="K71" s="4" t="n">
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="n">
         <v>0.999</v>
       </c>
-      <c r="L71" s="4" t="n"/>
+      <c r="L71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5719,28 +5721,28 @@
           <t>LQQ+1</t>
         </is>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="5" t="n">
         <v>0.01500080123069177</v>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="H72" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="I72" s="4" t="n">
+      <c r="I72" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="J72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="4" t="n">
+      <c r="J72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="5" t="n">
         <v>0.9936666666666666</v>
       </c>
-      <c r="L72" s="4" t="n">
+      <c r="L72" s="5" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -5765,28 +5767,28 @@
           <t>LQQ01</t>
         </is>
       </c>
-      <c r="E73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="4" t="n">
+      <c r="E73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="5" t="n">
         <v>2.185661076562508</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="5" t="n">
         <v>0.02499999999999999</v>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="5" t="n">
         <v>0.02499999999999999</v>
       </c>
-      <c r="I73" s="4" t="n">
+      <c r="I73" s="5" t="n">
         <v>0.025</v>
       </c>
-      <c r="J73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="4" t="n">
+      <c r="J73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="5" t="n">
         <v>0.006333333333333333</v>
       </c>
-      <c r="L73" s="4" t="n">
+      <c r="L73" s="5" t="n">
         <v>0.0003333333333333334</v>
       </c>
     </row>
@@ -5811,20 +5813,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E74" s="4" t="n"/>
-      <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n">
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="I74" s="4" t="n">
+      <c r="I74" s="5" t="n">
         <v>0.975</v>
       </c>
-      <c r="J74" s="4" t="n"/>
-      <c r="K74" s="4" t="n">
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="5" t="n">
         <v>0.9936666666666666</v>
       </c>
-      <c r="L74" s="4" t="n"/>
+      <c r="L74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5847,28 +5849,28 @@
           <t>0LI+1</t>
         </is>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="5" t="n">
         <v>0.3046424810811669</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="5" t="n">
         <v>0.598</v>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="5" t="n">
         <v>0.598</v>
       </c>
-      <c r="I75" s="4" t="n">
+      <c r="I75" s="5" t="n">
         <v>0.598</v>
       </c>
-      <c r="J75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="4" t="n">
+      <c r="J75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5893,28 +5895,28 @@
           <t>0LI+2</t>
         </is>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="5" t="n">
         <v>0.5971558207992901</v>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="5" t="n">
         <v>0.365</v>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="H76" s="5" t="n">
         <v>0.365</v>
       </c>
-      <c r="I76" s="4" t="n">
+      <c r="I76" s="5" t="n">
         <v>0.365</v>
       </c>
-      <c r="J76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="4" t="n">
+      <c r="J76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L76" s="4" t="n">
+      <c r="L76" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5939,28 +5941,28 @@
           <t>0LI01</t>
         </is>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" s="5" t="n">
         <v>1.953376139555213</v>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="5" t="n">
         <v>0.03700000000000001</v>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="H77" s="5" t="n">
         <v>0.03700000000000001</v>
       </c>
-      <c r="I77" s="4" t="n">
+      <c r="I77" s="5" t="n">
         <v>0.037</v>
       </c>
-      <c r="J77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4" t="n">
+      <c r="J77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5985,20 +5987,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E78" s="4" t="n"/>
-      <c r="F78" s="4" t="n"/>
-      <c r="G78" s="4" t="n"/>
-      <c r="H78" s="4" t="n">
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n">
         <v>0.963</v>
       </c>
-      <c r="I78" s="4" t="n">
+      <c r="I78" s="5" t="n">
         <v>0.963</v>
       </c>
-      <c r="J78" s="4" t="n"/>
-      <c r="K78" s="4" t="n">
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L78" s="4" t="n"/>
+      <c r="L78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -6021,28 +6023,28 @@
           <t>0WN+1</t>
         </is>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="5" t="n">
         <v>0.004759061730629078</v>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="H79" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="I79" s="4" t="n">
+      <c r="I79" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="J79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="4" t="n">
+      <c r="J79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="5" t="n">
         <v>0.9456666666666665</v>
       </c>
-      <c r="L79" s="4" t="n">
+      <c r="L79" s="5" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -6067,22 +6069,22 @@
           <t>0WN+a</t>
         </is>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E80" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F80" s="4" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="4" t="n">
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6107,28 +6109,28 @@
           <t>0WN01</t>
         </is>
       </c>
-      <c r="E81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="4" t="n">
+      <c r="E81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="5" t="n">
         <v>2.860775889351614</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="5" t="n">
         <v>0.007999999999999997</v>
       </c>
-      <c r="H81" s="4" t="n">
+      <c r="H81" s="5" t="n">
         <v>0.007999999999999997</v>
       </c>
-      <c r="I81" s="4" t="n">
+      <c r="I81" s="5" t="n">
         <v>0.008</v>
       </c>
-      <c r="J81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="4" t="n">
+      <c r="J81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="5" t="n">
         <v>0.05433333333333334</v>
       </c>
-      <c r="L81" s="4" t="n">
+      <c r="L81" s="5" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -6153,20 +6155,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n">
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="I82" s="4" t="n">
+      <c r="I82" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n">
+      <c r="J82" s="5" t="n"/>
+      <c r="K82" s="5" t="n">
         <v>0.9456666666666665</v>
       </c>
-      <c r="L82" s="4" t="n"/>
+      <c r="L82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6189,28 +6191,28 @@
           <t>0WN+1</t>
         </is>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E83" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="5" t="n">
         <v>0.004759061730629078</v>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="H83" s="4" t="n">
+      <c r="H83" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="I83" s="4" t="n">
+      <c r="I83" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="J83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="4" t="n">
+      <c r="J83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="5" t="n">
         <v>0.96</v>
       </c>
-      <c r="L83" s="4" t="n">
+      <c r="L83" s="5" t="n">
         <v>0.001527525231651948</v>
       </c>
     </row>
@@ -6235,22 +6237,22 @@
           <t>0WN+a</t>
         </is>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="E84" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F84" s="4" t="n"/>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="4" t="n">
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6275,28 +6277,28 @@
           <t>0WN01</t>
         </is>
       </c>
-      <c r="E85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="4" t="n">
+      <c r="E85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="5" t="n">
         <v>2.860775889351614</v>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="5" t="n">
         <v>0.007999999999999997</v>
       </c>
-      <c r="H85" s="4" t="n">
+      <c r="H85" s="5" t="n">
         <v>0.007999999999999997</v>
       </c>
-      <c r="I85" s="4" t="n">
+      <c r="I85" s="5" t="n">
         <v>0.008</v>
       </c>
-      <c r="J85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="4" t="n">
+      <c r="J85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="L85" s="4" t="n">
+      <c r="L85" s="5" t="n">
         <v>0.001527525231651946</v>
       </c>
     </row>
@@ -6321,20 +6323,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="4" t="n"/>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="n">
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="I86" s="4" t="n">
+      <c r="I86" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="J86" s="4" t="n"/>
-      <c r="K86" s="4" t="n">
+      <c r="J86" s="5" t="n"/>
+      <c r="K86" s="5" t="n">
         <v>0.96</v>
       </c>
-      <c r="L86" s="4" t="n"/>
+      <c r="L86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6357,28 +6359,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="5" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="H87" s="4" t="n">
+      <c r="H87" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="I87" s="4" t="n">
+      <c r="I87" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="J87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="4" t="n">
+      <c r="J87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="5" t="n">
         <v>0.7623333333333333</v>
       </c>
-      <c r="L87" s="4" t="n">
+      <c r="L87" s="5" t="n">
         <v>0.02409933147989336</v>
       </c>
     </row>
@@ -6403,28 +6405,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="E88" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H88" s="4" t="n">
+      <c r="H88" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I88" s="4" t="n">
+      <c r="I88" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="4" t="n">
+      <c r="J88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6449,22 +6451,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="4" t="n"/>
-      <c r="H89" s="4" t="n"/>
-      <c r="I89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="4" t="n">
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6489,22 +6491,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E90" s="4" t="n">
+      <c r="E90" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F90" s="4" t="n"/>
-      <c r="G90" s="4" t="n"/>
-      <c r="H90" s="4" t="n"/>
-      <c r="I90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="4" t="n">
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6529,28 +6531,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="F91" s="5" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H91" s="4" t="n">
+      <c r="H91" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I91" s="4" t="n">
+      <c r="I91" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="4" t="n">
+      <c r="J91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="5" t="n">
         <v>0.2376666666666667</v>
       </c>
-      <c r="L91" s="4" t="n">
+      <c r="L91" s="5" t="n">
         <v>0.02409933147989332</v>
       </c>
     </row>
@@ -6575,20 +6577,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E92" s="4" t="n"/>
-      <c r="F92" s="4" t="n"/>
-      <c r="G92" s="4" t="n"/>
-      <c r="H92" s="4" t="n">
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="I92" s="4" t="n">
+      <c r="I92" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="J92" s="4" t="n"/>
-      <c r="K92" s="4" t="n">
+      <c r="J92" s="5" t="n"/>
+      <c r="K92" s="5" t="n">
         <v>0.7623333333333333</v>
       </c>
-      <c r="L92" s="4" t="n"/>
+      <c r="L92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6611,28 +6613,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="E93" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="F93" s="5" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="H93" s="4" t="n">
+      <c r="H93" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="I93" s="4" t="n">
+      <c r="I93" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="J93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="4" t="n">
+      <c r="J93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="5" t="n">
         <v>0.331</v>
       </c>
-      <c r="L93" s="4" t="n">
+      <c r="L93" s="5" t="n">
         <v>0.01539480431834065</v>
       </c>
     </row>
@@ -6657,28 +6659,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E94" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="F94" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H94" s="4" t="n">
+      <c r="H94" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I94" s="4" t="n">
+      <c r="I94" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="4" t="n">
+      <c r="J94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6703,22 +6705,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E95" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="4" t="n"/>
-      <c r="H95" s="4" t="n"/>
-      <c r="I95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="4" t="n">
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6743,22 +6745,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E96" s="4" t="n">
+      <c r="E96" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="4" t="n"/>
-      <c r="I96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="4" t="n">
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6783,28 +6785,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F97" s="5" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H97" s="4" t="n">
+      <c r="H97" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I97" s="4" t="n">
+      <c r="I97" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="4" t="n">
+      <c r="J97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="5" t="n">
         <v>0.669</v>
       </c>
-      <c r="L97" s="4" t="n">
+      <c r="L97" s="5" t="n">
         <v>0.01539480431834063</v>
       </c>
     </row>
@@ -6829,20 +6831,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E98" s="4" t="n"/>
-      <c r="F98" s="4" t="n"/>
-      <c r="G98" s="4" t="n"/>
-      <c r="H98" s="4" t="n">
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="I98" s="4" t="n">
+      <c r="I98" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="J98" s="4" t="n"/>
-      <c r="K98" s="4" t="n">
+      <c r="J98" s="5" t="n"/>
+      <c r="K98" s="5" t="n">
         <v>0.331</v>
       </c>
-      <c r="L98" s="4" t="n"/>
+      <c r="L98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6865,28 +6867,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="4" t="n">
+      <c r="F99" s="5" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="H99" s="4" t="n">
+      <c r="H99" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="I99" s="4" t="n">
+      <c r="I99" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="J99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="4" t="n">
+      <c r="J99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="5" t="n">
         <v>0.6466666666666666</v>
       </c>
-      <c r="L99" s="4" t="n">
+      <c r="L99" s="5" t="n">
         <v>0.008212456663169955</v>
       </c>
     </row>
@@ -6911,28 +6913,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E100" s="4" t="n">
+      <c r="E100" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H100" s="4" t="n">
+      <c r="H100" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I100" s="4" t="n">
+      <c r="I100" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="4" t="n">
+      <c r="J100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6957,22 +6959,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E101" s="4" t="n">
+      <c r="E101" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F101" s="4" t="n"/>
-      <c r="G101" s="4" t="n"/>
-      <c r="H101" s="4" t="n"/>
-      <c r="I101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="4" t="n">
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="5" t="n"/>
+      <c r="I101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6997,22 +6999,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E102" s="4" t="n">
+      <c r="E102" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="4" t="n">
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="5" t="n"/>
+      <c r="I102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7037,28 +7039,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E103" s="4" t="n">
+      <c r="E103" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F103" s="4" t="n">
+      <c r="F103" s="5" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H103" s="4" t="n">
+      <c r="H103" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I103" s="4" t="n">
+      <c r="I103" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="4" t="n">
+      <c r="J103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="5" t="n">
         <v>0.3533333333333333</v>
       </c>
-      <c r="L103" s="4" t="n">
+      <c r="L103" s="5" t="n">
         <v>0.008212456663169936</v>
       </c>
     </row>
@@ -7083,20 +7085,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E104" s="4" t="n"/>
-      <c r="F104" s="4" t="n"/>
-      <c r="G104" s="4" t="n"/>
-      <c r="H104" s="4" t="n">
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="I104" s="4" t="n">
+      <c r="I104" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="J104" s="4" t="n"/>
-      <c r="K104" s="4" t="n">
+      <c r="J104" s="5" t="n"/>
+      <c r="K104" s="5" t="n">
         <v>0.6466666666666666</v>
       </c>
-      <c r="L104" s="4" t="n"/>
+      <c r="L104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7119,28 +7121,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E105" s="4" t="n">
+      <c r="E105" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F105" s="4" t="n">
+      <c r="F105" s="5" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="H105" s="4" t="n">
+      <c r="H105" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="I105" s="4" t="n">
+      <c r="I105" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="J105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="4" t="n">
+      <c r="J105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="5" t="n">
         <v>0.016</v>
       </c>
-      <c r="L105" s="4" t="n">
+      <c r="L105" s="5" t="n">
         <v>0.002</v>
       </c>
     </row>
@@ -7165,28 +7167,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E106" s="4" t="n">
+      <c r="E106" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F106" s="4" t="n">
+      <c r="F106" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H106" s="4" t="n">
+      <c r="H106" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I106" s="4" t="n">
+      <c r="I106" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="4" t="n">
+      <c r="J106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7211,22 +7213,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E107" s="4" t="n">
+      <c r="E107" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F107" s="4" t="n"/>
-      <c r="G107" s="4" t="n"/>
-      <c r="H107" s="4" t="n"/>
-      <c r="I107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="4" t="n">
+      <c r="F107" s="5" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="5" t="n"/>
+      <c r="I107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7251,22 +7253,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E108" s="4" t="n">
+      <c r="E108" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F108" s="4" t="n"/>
-      <c r="G108" s="4" t="n"/>
-      <c r="H108" s="4" t="n"/>
-      <c r="I108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="4" t="n">
+      <c r="F108" s="5" t="n"/>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="5" t="n"/>
+      <c r="I108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7291,28 +7293,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E109" s="4" t="n">
+      <c r="E109" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F109" s="4" t="n">
+      <c r="F109" s="5" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H109" s="4" t="n">
+      <c r="H109" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I109" s="4" t="n">
+      <c r="I109" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="4" t="n">
+      <c r="J109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="5" t="n">
         <v>0.984</v>
       </c>
-      <c r="L109" s="4" t="n">
+      <c r="L109" s="5" t="n">
         <v>0.002000000000000002</v>
       </c>
     </row>
@@ -7337,20 +7339,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E110" s="4" t="n"/>
-      <c r="F110" s="4" t="n"/>
-      <c r="G110" s="4" t="n"/>
-      <c r="H110" s="4" t="n">
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="I110" s="4" t="n">
+      <c r="I110" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="J110" s="4" t="n"/>
-      <c r="K110" s="4" t="n">
+      <c r="J110" s="5" t="n"/>
+      <c r="K110" s="5" t="n">
         <v>0.016</v>
       </c>
-      <c r="L110" s="4" t="n"/>
+      <c r="L110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7373,28 +7375,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E111" s="4" t="n">
+      <c r="E111" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F111" s="4" t="n">
+      <c r="F111" s="5" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="H111" s="4" t="n">
+      <c r="H111" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="I111" s="4" t="n">
+      <c r="I111" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="J111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="4" t="n">
+      <c r="J111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="5" t="n">
         <v>0.4796666666666667</v>
       </c>
-      <c r="L111" s="4" t="n">
+      <c r="L111" s="5" t="n">
         <v>0.02186575201339097</v>
       </c>
     </row>
@@ -7419,28 +7421,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E112" s="4" t="n">
+      <c r="E112" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F112" s="4" t="n">
+      <c r="F112" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H112" s="4" t="n">
+      <c r="H112" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I112" s="4" t="n">
+      <c r="I112" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="4" t="n">
+      <c r="J112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7465,22 +7467,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E113" s="4" t="n">
+      <c r="E113" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="4" t="n"/>
-      <c r="H113" s="4" t="n"/>
-      <c r="I113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="4" t="n">
+      <c r="F113" s="5" t="n"/>
+      <c r="G113" s="5" t="n"/>
+      <c r="H113" s="5" t="n"/>
+      <c r="I113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7505,22 +7507,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E114" s="4" t="n">
+      <c r="E114" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F114" s="4" t="n"/>
-      <c r="G114" s="4" t="n"/>
-      <c r="H114" s="4" t="n"/>
-      <c r="I114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="4" t="n">
+      <c r="F114" s="5" t="n"/>
+      <c r="G114" s="5" t="n"/>
+      <c r="H114" s="5" t="n"/>
+      <c r="I114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7545,28 +7547,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E115" s="4" t="n">
+      <c r="E115" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F115" s="4" t="n">
+      <c r="F115" s="5" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H115" s="4" t="n">
+      <c r="H115" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I115" s="4" t="n">
+      <c r="I115" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="4" t="n">
+      <c r="J115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="5" t="n">
         <v>0.5203333333333333</v>
       </c>
-      <c r="L115" s="4" t="n">
+      <c r="L115" s="5" t="n">
         <v>0.02186575201339098</v>
       </c>
     </row>
@@ -7591,20 +7593,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E116" s="4" t="n"/>
-      <c r="F116" s="4" t="n"/>
-      <c r="G116" s="4" t="n"/>
-      <c r="H116" s="4" t="n">
+      <c r="E116" s="5" t="n"/>
+      <c r="F116" s="5" t="n"/>
+      <c r="G116" s="5" t="n"/>
+      <c r="H116" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="I116" s="4" t="n">
+      <c r="I116" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="J116" s="4" t="n"/>
-      <c r="K116" s="4" t="n">
+      <c r="J116" s="5" t="n"/>
+      <c r="K116" s="5" t="n">
         <v>0.4796666666666667</v>
       </c>
-      <c r="L116" s="4" t="n"/>
+      <c r="L116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7627,28 +7629,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E117" s="4" t="n">
+      <c r="E117" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F117" s="4" t="n">
+      <c r="F117" s="5" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="H117" s="4" t="n">
+      <c r="H117" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="I117" s="4" t="n">
+      <c r="I117" s="5" t="n">
         <v>0.298</v>
       </c>
-      <c r="J117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="4" t="n">
+      <c r="J117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="5" t="n">
         <v>0.4716666666666667</v>
       </c>
-      <c r="L117" s="4" t="n">
+      <c r="L117" s="5" t="n">
         <v>0.007264831572567782</v>
       </c>
     </row>
@@ -7673,28 +7675,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E118" s="4" t="n">
+      <c r="E118" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F118" s="4" t="n">
+      <c r="F118" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H118" s="4" t="n">
+      <c r="H118" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I118" s="4" t="n">
+      <c r="I118" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="4" t="n">
+      <c r="J118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7719,22 +7721,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E119" s="4" t="n">
+      <c r="E119" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F119" s="4" t="n"/>
-      <c r="G119" s="4" t="n"/>
-      <c r="H119" s="4" t="n"/>
-      <c r="I119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="n">
+      <c r="F119" s="5" t="n"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="5" t="n"/>
+      <c r="I119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7759,22 +7761,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E120" s="4" t="n">
+      <c r="E120" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F120" s="4" t="n"/>
-      <c r="G120" s="4" t="n"/>
-      <c r="H120" s="4" t="n"/>
-      <c r="I120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="4" t="n">
+      <c r="F120" s="5" t="n"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="5" t="n"/>
+      <c r="I120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7799,28 +7801,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E121" s="4" t="n">
+      <c r="E121" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F121" s="4" t="n">
+      <c r="F121" s="5" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H121" s="4" t="n">
+      <c r="H121" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I121" s="4" t="n">
+      <c r="I121" s="5" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" s="4" t="n">
+      <c r="J121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="5" t="n">
         <v>0.5283333333333333</v>
       </c>
-      <c r="L121" s="4" t="n">
+      <c r="L121" s="5" t="n">
         <v>0.007264831572567796</v>
       </c>
     </row>
@@ -7845,20 +7847,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E122" s="4" t="n"/>
-      <c r="F122" s="4" t="n"/>
-      <c r="G122" s="4" t="n"/>
-      <c r="H122" s="4" t="n">
+      <c r="E122" s="5" t="n"/>
+      <c r="F122" s="5" t="n"/>
+      <c r="G122" s="5" t="n"/>
+      <c r="H122" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="I122" s="4" t="n">
+      <c r="I122" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="J122" s="4" t="n"/>
-      <c r="K122" s="4" t="n">
+      <c r="J122" s="5" t="n"/>
+      <c r="K122" s="5" t="n">
         <v>0.4716666666666667</v>
       </c>
-      <c r="L122" s="4" t="n"/>
+      <c r="L122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7881,28 +7883,28 @@
           <t>FMM+1</t>
         </is>
       </c>
-      <c r="E123" s="4" t="n">
+      <c r="E123" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F123" s="4" t="n">
+      <c r="F123" s="5" t="n">
         <v>0.03101528962053397</v>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="5" t="n">
         <v>0.949</v>
       </c>
-      <c r="H123" s="4" t="n">
+      <c r="H123" s="5" t="n">
         <v>0.949</v>
       </c>
-      <c r="I123" s="4" t="n">
+      <c r="I123" s="5" t="n">
         <v>0.949</v>
       </c>
-      <c r="J123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="4" t="n">
+      <c r="J123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="5" t="n">
         <v>0.5233333333333333</v>
       </c>
-      <c r="L123" s="4" t="n">
+      <c r="L123" s="5" t="n">
         <v>0.004371625682868005</v>
       </c>
     </row>
@@ -7927,22 +7929,22 @@
           <t>FMM+a</t>
         </is>
       </c>
-      <c r="E124" s="4" t="n">
+      <c r="E124" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F124" s="4" t="n"/>
-      <c r="G124" s="4" t="n"/>
-      <c r="H124" s="4" t="n"/>
-      <c r="I124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="4" t="n">
+      <c r="F124" s="5" t="n"/>
+      <c r="G124" s="5" t="n"/>
+      <c r="H124" s="5" t="n"/>
+      <c r="I124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7967,28 +7969,28 @@
           <t>FMM01</t>
         </is>
       </c>
-      <c r="E125" s="4" t="n">
+      <c r="E125" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F125" s="4" t="n">
+      <c r="F125" s="5" t="n">
         <v>1.763238315407753</v>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="5" t="n">
         <v>0.05099999999999999</v>
       </c>
-      <c r="H125" s="4" t="n">
+      <c r="H125" s="5" t="n">
         <v>0.05099999999999999</v>
       </c>
-      <c r="I125" s="4" t="n">
+      <c r="I125" s="5" t="n">
         <v>0.051</v>
       </c>
-      <c r="J125" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="4" t="n">
+      <c r="J125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="5" t="n">
         <v>0.4766666666666666</v>
       </c>
-      <c r="L125" s="4" t="n">
+      <c r="L125" s="5" t="n">
         <v>0.004371625682867987</v>
       </c>
     </row>
@@ -8013,20 +8015,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E126" s="4" t="n"/>
-      <c r="F126" s="4" t="n"/>
-      <c r="G126" s="4" t="n"/>
-      <c r="H126" s="4" t="n">
+      <c r="E126" s="5" t="n"/>
+      <c r="F126" s="5" t="n"/>
+      <c r="G126" s="5" t="n"/>
+      <c r="H126" s="5" t="n">
         <v>0.949</v>
       </c>
-      <c r="I126" s="4" t="n">
+      <c r="I126" s="5" t="n">
         <v>0.949</v>
       </c>
-      <c r="J126" s="4" t="n"/>
-      <c r="K126" s="4" t="n">
+      <c r="J126" s="5" t="n"/>
+      <c r="K126" s="5" t="n">
         <v>0.5233333333333333</v>
       </c>
-      <c r="L126" s="4" t="n"/>
+      <c r="L126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8049,28 +8051,28 @@
           <t>YY3+1</t>
         </is>
       </c>
-      <c r="E127" s="4" t="n">
+      <c r="E127" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F127" s="4" t="n">
+      <c r="F127" s="5" t="n">
         <v>0.01560880538871424</v>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="5" t="n">
         <v>0.9739999999999999</v>
       </c>
-      <c r="H127" s="4" t="n">
+      <c r="H127" s="5" t="n">
         <v>0.974</v>
       </c>
-      <c r="I127" s="4" t="n">
+      <c r="I127" s="5" t="n">
         <v>0.9739999999999999</v>
       </c>
-      <c r="J127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" s="4" t="n">
+      <c r="J127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="5" t="n">
         <v>0.984</v>
       </c>
-      <c r="L127" s="4" t="n">
+      <c r="L127" s="5" t="n">
         <v>0.001154700538379253</v>
       </c>
     </row>
@@ -8095,28 +8097,28 @@
           <t>YY3+2</t>
         </is>
       </c>
-      <c r="E128" s="4" t="n">
+      <c r="E128" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="5" t="n">
         <v>3.271465593833381</v>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="5" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="H128" s="4" t="n">
+      <c r="H128" s="5" t="n">
         <v>0.004000000000000003</v>
       </c>
-      <c r="I128" s="4" t="n">
+      <c r="I128" s="5" t="n">
         <v>0.004</v>
       </c>
-      <c r="J128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="4" t="n">
+      <c r="J128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="5" t="n">
         <v>0.002666666666666667</v>
       </c>
-      <c r="L128" s="4" t="n">
+      <c r="L128" s="5" t="n">
         <v>0.001333333333333334</v>
       </c>
     </row>
@@ -8141,28 +8143,28 @@
           <t>YY3+3</t>
         </is>
       </c>
-      <c r="E129" s="4" t="n">
+      <c r="E129" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F129" s="4" t="n">
+      <c r="F129" s="5" t="n">
         <v>4.092845002796916</v>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="H129" s="4" t="n">
+      <c r="H129" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="I129" s="4" t="n">
+      <c r="I129" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="J129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" s="4" t="n">
+      <c r="J129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="5" t="n">
         <v>0.002666666666666667</v>
       </c>
-      <c r="L129" s="4" t="n">
+      <c r="L129" s="5" t="n">
         <v>0.001333333333333334</v>
       </c>
     </row>
@@ -8187,22 +8189,22 @@
           <t>YY3+4</t>
         </is>
       </c>
-      <c r="E130" s="4" t="n">
+      <c r="E130" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="4" t="n"/>
-      <c r="G130" s="4" t="n"/>
-      <c r="H130" s="4" t="n"/>
-      <c r="I130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="4" t="n">
+      <c r="F130" s="5" t="n"/>
+      <c r="G130" s="5" t="n"/>
+      <c r="H130" s="5" t="n"/>
+      <c r="I130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="L130" s="4" t="n">
+      <c r="L130" s="5" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -8227,22 +8229,22 @@
           <t>YY3+a</t>
         </is>
       </c>
-      <c r="E131" s="4" t="n">
+      <c r="E131" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F131" s="4" t="n"/>
-      <c r="G131" s="4" t="n"/>
-      <c r="H131" s="4" t="n"/>
-      <c r="I131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="4" t="n">
+      <c r="F131" s="5" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="5" t="n"/>
+      <c r="I131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8267,22 +8269,22 @@
           <t>YY3+b</t>
         </is>
       </c>
-      <c r="E132" s="4" t="n">
+      <c r="E132" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F132" s="4" t="n"/>
-      <c r="G132" s="4" t="n"/>
-      <c r="H132" s="4" t="n"/>
-      <c r="I132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="4" t="n">
+      <c r="F132" s="5" t="n"/>
+      <c r="G132" s="5" t="n"/>
+      <c r="H132" s="5" t="n"/>
+      <c r="I132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8307,28 +8309,28 @@
           <t>YY301</t>
         </is>
       </c>
-      <c r="E133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="4" t="n">
+      <c r="E133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="5" t="n">
         <v>2.288965458445788</v>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="5" t="n">
         <v>0.021</v>
       </c>
-      <c r="H133" s="4" t="n">
+      <c r="H133" s="5" t="n">
         <v>0.02100000000000001</v>
       </c>
-      <c r="I133" s="4" t="n">
+      <c r="I133" s="5" t="n">
         <v>0.021</v>
       </c>
-      <c r="J133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" s="4" t="n">
+      <c r="J133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="5" t="n">
         <v>0.009666666666666665</v>
       </c>
-      <c r="L133" s="4" t="n">
+      <c r="L133" s="5" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -8353,20 +8355,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E134" s="4" t="n"/>
-      <c r="F134" s="4" t="n"/>
-      <c r="G134" s="4" t="n"/>
-      <c r="H134" s="4" t="n">
+      <c r="E134" s="5" t="n"/>
+      <c r="F134" s="5" t="n"/>
+      <c r="G134" s="5" t="n"/>
+      <c r="H134" s="5" t="n">
         <v>0.979</v>
       </c>
-      <c r="I134" s="4" t="n">
+      <c r="I134" s="5" t="n">
         <v>0.9789999999999999</v>
       </c>
-      <c r="J134" s="4" t="n"/>
-      <c r="K134" s="4" t="n">
+      <c r="J134" s="5" t="n"/>
+      <c r="K134" s="5" t="n">
         <v>0.9903333333333334</v>
       </c>
-      <c r="L134" s="4" t="n"/>
+      <c r="L134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8389,28 +8391,28 @@
           <t>MI1+1</t>
         </is>
       </c>
-      <c r="E135" s="4" t="n">
+      <c r="E135" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F135" s="4" t="n">
+      <c r="F135" s="5" t="n">
         <v>2.097722223529931</v>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="5" t="n">
         <v>0.02899999999999998</v>
       </c>
-      <c r="H135" s="4" t="n">
+      <c r="H135" s="5" t="n">
         <v>0.02899999999999998</v>
       </c>
-      <c r="I135" s="4" t="n">
+      <c r="I135" s="5" t="n">
         <v>0.029</v>
       </c>
-      <c r="J135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="4" t="n">
+      <c r="J135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="5" t="n">
         <v>0.04866666666666667</v>
       </c>
-      <c r="L135" s="4" t="n">
+      <c r="L135" s="5" t="n">
         <v>0.01026861453383291</v>
       </c>
     </row>
@@ -8435,28 +8437,28 @@
           <t>MI101</t>
         </is>
       </c>
-      <c r="E136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" s="4" t="n">
+      <c r="E136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="5" t="n">
         <v>0.01743657033430621</v>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="5" t="n">
         <v>0.971</v>
       </c>
-      <c r="H136" s="4" t="n">
+      <c r="H136" s="5" t="n">
         <v>0.971</v>
       </c>
-      <c r="I136" s="4" t="n">
+      <c r="I136" s="5" t="n">
         <v>0.971</v>
       </c>
-      <c r="J136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="4" t="n">
+      <c r="J136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="5" t="n">
         <v>0.9513333333333334</v>
       </c>
-      <c r="L136" s="4" t="n">
+      <c r="L136" s="5" t="n">
         <v>0.01026861453383288</v>
       </c>
     </row>
@@ -8481,20 +8483,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="n"/>
-      <c r="G137" s="4" t="n"/>
-      <c r="H137" s="4" t="n">
+      <c r="E137" s="5" t="n"/>
+      <c r="F137" s="5" t="n"/>
+      <c r="G137" s="5" t="n"/>
+      <c r="H137" s="5" t="n">
         <v>0.02899999999999998</v>
       </c>
-      <c r="I137" s="4" t="n">
+      <c r="I137" s="5" t="n">
         <v>0.029</v>
       </c>
-      <c r="J137" s="4" t="n"/>
-      <c r="K137" s="4" t="n">
+      <c r="J137" s="5" t="n"/>
+      <c r="K137" s="5" t="n">
         <v>0.04866666666666667</v>
       </c>
-      <c r="L137" s="4" t="n"/>
+      <c r="L137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8517,28 +8519,28 @@
           <t>EUI+1</t>
         </is>
       </c>
-      <c r="E138" s="4" t="n">
+      <c r="E138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F138" s="4" t="n">
+      <c r="F138" s="5" t="n">
         <v>0.00835361269485466</v>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="5" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="H138" s="4" t="n">
+      <c r="H138" s="5" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="I138" s="4" t="n">
+      <c r="I138" s="5" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="J138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" s="4" t="n">
+      <c r="J138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="5" t="n">
         <v>0.2446666666666667</v>
       </c>
-      <c r="L138" s="4" t="n">
+      <c r="L138" s="5" t="n">
         <v>0.02248209163855633</v>
       </c>
     </row>
@@ -8563,28 +8565,28 @@
           <t>EUI01</t>
         </is>
       </c>
-      <c r="E139" s="4" t="n">
+      <c r="E139" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F139" s="4" t="n">
+      <c r="F139" s="5" t="n">
         <v>2.529203534999876</v>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="5" t="n">
         <v>0.01399999999999999</v>
       </c>
-      <c r="H139" s="4" t="n">
+      <c r="H139" s="5" t="n">
         <v>0.01399999999999999</v>
       </c>
-      <c r="I139" s="4" t="n">
+      <c r="I139" s="5" t="n">
         <v>0.014</v>
       </c>
-      <c r="J139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="4" t="n">
+      <c r="J139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="5" t="n">
         <v>0.7543333333333333</v>
       </c>
-      <c r="L139" s="4" t="n">
+      <c r="L139" s="5" t="n">
         <v>0.02292984469589314</v>
       </c>
     </row>
@@ -8609,22 +8611,22 @@
           <t>EUI02</t>
         </is>
       </c>
-      <c r="E140" s="4" t="n">
+      <c r="E140" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F140" s="4" t="n"/>
-      <c r="G140" s="4" t="n"/>
-      <c r="H140" s="4" t="n"/>
-      <c r="I140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" s="4" t="n">
+      <c r="F140" s="5" t="n"/>
+      <c r="G140" s="5" t="n"/>
+      <c r="H140" s="5" t="n"/>
+      <c r="I140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="L140" s="4" t="n">
+      <c r="L140" s="5" t="n">
         <v>0.0005773502691896258</v>
       </c>
     </row>
@@ -8649,20 +8651,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E141" s="4" t="n"/>
-      <c r="F141" s="4" t="n"/>
-      <c r="G141" s="4" t="n"/>
-      <c r="H141" s="4" t="n">
+      <c r="E141" s="5" t="n"/>
+      <c r="F141" s="5" t="n"/>
+      <c r="G141" s="5" t="n"/>
+      <c r="H141" s="5" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="I141" s="4" t="n">
+      <c r="I141" s="5" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="J141" s="4" t="n"/>
-      <c r="K141" s="4" t="n">
+      <c r="J141" s="5" t="n"/>
+      <c r="K141" s="5" t="n">
         <v>0.2446666666666667</v>
       </c>
-      <c r="L141" s="4" t="n"/>
+      <c r="L141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8685,28 +8687,28 @@
           <t>EUI+1</t>
         </is>
       </c>
-      <c r="E142" s="4" t="n">
+      <c r="E142" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F142" s="4" t="n">
+      <c r="F142" s="5" t="n">
         <v>0.00835361269485466</v>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="5" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="H142" s="4" t="n">
+      <c r="H142" s="5" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="I142" s="4" t="n">
+      <c r="I142" s="5" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="J142" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" s="4" t="n">
+      <c r="J142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" s="5" t="n">
         <v>0.5206666666666667</v>
       </c>
-      <c r="L142" s="4" t="n">
+      <c r="L142" s="5" t="n">
         <v>0.01089852181618122</v>
       </c>
     </row>
@@ -8731,28 +8733,28 @@
           <t>EUI01</t>
         </is>
       </c>
-      <c r="E143" s="4" t="n">
+      <c r="E143" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F143" s="4" t="n">
+      <c r="F143" s="5" t="n">
         <v>2.529203534999876</v>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="5" t="n">
         <v>0.01399999999999999</v>
       </c>
-      <c r="H143" s="4" t="n">
+      <c r="H143" s="5" t="n">
         <v>0.01399999999999999</v>
       </c>
-      <c r="I143" s="4" t="n">
+      <c r="I143" s="5" t="n">
         <v>0.014</v>
       </c>
-      <c r="J143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" s="4" t="n">
+      <c r="J143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" s="5" t="n">
         <v>0.4793333333333333</v>
       </c>
-      <c r="L143" s="4" t="n">
+      <c r="L143" s="5" t="n">
         <v>0.01089852181618121</v>
       </c>
     </row>
@@ -8777,22 +8779,22 @@
           <t>EUI02</t>
         </is>
       </c>
-      <c r="E144" s="4" t="n">
+      <c r="E144" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F144" s="4" t="n"/>
-      <c r="G144" s="4" t="n"/>
-      <c r="H144" s="4" t="n"/>
-      <c r="I144" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="4" t="n">
+      <c r="F144" s="5" t="n"/>
+      <c r="G144" s="5" t="n"/>
+      <c r="H144" s="5" t="n"/>
+      <c r="I144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8817,20 +8819,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E145" s="4" t="n"/>
-      <c r="F145" s="4" t="n"/>
-      <c r="G145" s="4" t="n"/>
-      <c r="H145" s="4" t="n">
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="5" t="n"/>
+      <c r="G145" s="5" t="n"/>
+      <c r="H145" s="5" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="I145" s="4" t="n">
+      <c r="I145" s="5" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="J145" s="4" t="n"/>
-      <c r="K145" s="4" t="n">
+      <c r="J145" s="5" t="n"/>
+      <c r="K145" s="5" t="n">
         <v>0.5206666666666667</v>
       </c>
-      <c r="L145" s="4" t="n"/>
+      <c r="L145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8853,28 +8855,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E146" s="4" t="n">
+      <c r="E146" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F146" s="4" t="n">
+      <c r="F146" s="5" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H146" s="4" t="n">
+      <c r="H146" s="5" t="n">
         <v>0.378</v>
       </c>
-      <c r="I146" s="4" t="n">
+      <c r="I146" s="5" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J146" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" s="4" t="n">
+      <c r="J146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" s="5" t="n">
         <v>0.971</v>
       </c>
-      <c r="L146" s="4" t="n">
+      <c r="L146" s="5" t="n">
         <v>0.004000000000000004</v>
       </c>
     </row>
@@ -8899,28 +8901,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E147" s="4" t="n">
+      <c r="E147" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F147" s="4" t="n">
+      <c r="F147" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H147" s="4" t="n">
+      <c r="H147" s="5" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I147" s="4" t="n">
+      <c r="I147" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="4" t="n">
+      <c r="J147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8945,28 +8947,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E148" s="4" t="n">
+      <c r="E148" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F148" s="4" t="n">
+      <c r="F148" s="5" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="H148" s="4" t="n">
+      <c r="H148" s="5" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I148" s="4" t="n">
+      <c r="I148" s="5" t="n">
         <v>0.615</v>
       </c>
-      <c r="J148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="4" t="n">
+      <c r="J148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8991,28 +8993,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E149" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" s="4" t="n">
+      <c r="E149" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="5" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="5" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H149" s="4" t="n">
+      <c r="H149" s="5" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I149" s="4" t="n">
+      <c r="I149" s="5" t="n">
         <v>0.005</v>
       </c>
-      <c r="J149" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" s="4" t="n">
+      <c r="J149" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" s="5" t="n">
         <v>0.029</v>
       </c>
-      <c r="L149" s="4" t="n">
+      <c r="L149" s="5" t="n">
         <v>0.004</v>
       </c>
     </row>
@@ -9037,20 +9039,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E150" s="4" t="n"/>
-      <c r="F150" s="4" t="n"/>
-      <c r="G150" s="4" t="n"/>
-      <c r="H150" s="4" t="n">
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="5" t="n"/>
+      <c r="G150" s="5" t="n"/>
+      <c r="H150" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="I150" s="4" t="n">
+      <c r="I150" s="5" t="n">
         <v>1.61</v>
       </c>
-      <c r="J150" s="4" t="n"/>
-      <c r="K150" s="4" t="n">
+      <c r="J150" s="5" t="n"/>
+      <c r="K150" s="5" t="n">
         <v>0.971</v>
       </c>
-      <c r="L150" s="4" t="n"/>
+      <c r="L150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9073,28 +9075,28 @@
           <t>AXI+1</t>
         </is>
       </c>
-      <c r="E151" s="4" t="n">
+      <c r="E151" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F151" s="4" t="n">
+      <c r="F151" s="5" t="n">
         <v>3.441917221761061</v>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="5" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="H151" s="4" t="n">
+      <c r="H151" s="5" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="I151" s="4" t="n">
+      <c r="I151" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="J151" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="4" t="n">
+      <c r="J151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9119,28 +9121,28 @@
           <t>AXI01</t>
         </is>
       </c>
-      <c r="E152" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" s="4" t="n">
+      <c r="E152" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="5" t="n">
         <v>0.1248522110545241</v>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H152" s="4" t="n">
+      <c r="H152" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="I152" s="4" t="n">
+      <c r="I152" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J152" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" s="4" t="n">
+      <c r="J152" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" s="5" t="n">
         <v>0.9603333333333333</v>
       </c>
-      <c r="L152" s="4" t="n">
+      <c r="L152" s="5" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -9165,28 +9167,28 @@
           <t>AXI02</t>
         </is>
       </c>
-      <c r="E153" s="4" t="n">
+      <c r="E153" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F153" s="4" t="n">
+      <c r="F153" s="5" t="n">
         <v>0.9934131473105738</v>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="5" t="n">
         <v>0.187</v>
       </c>
-      <c r="H153" s="4" t="n">
+      <c r="H153" s="5" t="n">
         <v>0.187</v>
       </c>
-      <c r="I153" s="4" t="n">
+      <c r="I153" s="5" t="n">
         <v>0.187</v>
       </c>
-      <c r="J153" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" s="4" t="n">
+      <c r="J153" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" s="5" t="n">
         <v>0.03966666666666666</v>
       </c>
-      <c r="L153" s="4" t="n">
+      <c r="L153" s="5" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -9211,20 +9213,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E154" s="4" t="n"/>
-      <c r="F154" s="4" t="n"/>
-      <c r="G154" s="4" t="n"/>
-      <c r="H154" s="4" t="n">
+      <c r="E154" s="5" t="n"/>
+      <c r="F154" s="5" t="n"/>
+      <c r="G154" s="5" t="n"/>
+      <c r="H154" s="5" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="I154" s="4" t="n">
+      <c r="I154" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="J154" s="4" t="n"/>
-      <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="4" t="n"/>
+      <c r="J154" s="5" t="n"/>
+      <c r="K154" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -9247,28 +9249,28 @@
           <t>AXI+1</t>
         </is>
       </c>
-      <c r="E155" s="4" t="n">
+      <c r="E155" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F155" s="4" t="n">
+      <c r="F155" s="5" t="n">
         <v>3.441917221761061</v>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="5" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="H155" s="4" t="n">
+      <c r="H155" s="5" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="I155" s="4" t="n">
+      <c r="I155" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="J155" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="4" t="n">
+      <c r="J155" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9293,28 +9295,28 @@
           <t>AXI01</t>
         </is>
       </c>
-      <c r="E156" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" s="4" t="n">
+      <c r="E156" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="5" t="n">
         <v>0.1248522110545241</v>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H156" s="4" t="n">
+      <c r="H156" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="I156" s="4" t="n">
+      <c r="I156" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J156" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" s="4" t="n">
+      <c r="J156" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" s="5" t="n">
         <v>0.988</v>
       </c>
-      <c r="L156" s="4" t="n">
+      <c r="L156" s="5" t="n">
         <v>0.0005773502691896263</v>
       </c>
     </row>
@@ -9339,28 +9341,28 @@
           <t>AXI02</t>
         </is>
       </c>
-      <c r="E157" s="4" t="n">
+      <c r="E157" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F157" s="4" t="n">
+      <c r="F157" s="5" t="n">
         <v>0.9934131473105738</v>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="5" t="n">
         <v>0.187</v>
       </c>
-      <c r="H157" s="4" t="n">
+      <c r="H157" s="5" t="n">
         <v>0.187</v>
       </c>
-      <c r="I157" s="4" t="n">
+      <c r="I157" s="5" t="n">
         <v>0.187</v>
       </c>
-      <c r="J157" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" s="4" t="n">
+      <c r="J157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" s="5" t="n">
         <v>0.012</v>
       </c>
-      <c r="L157" s="4" t="n">
+      <c r="L157" s="5" t="n">
         <v>0.0005773502691896258</v>
       </c>
     </row>
@@ -9385,20 +9387,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E158" s="4" t="n"/>
-      <c r="F158" s="4" t="n"/>
-      <c r="G158" s="4" t="n"/>
-      <c r="H158" s="4" t="n">
+      <c r="E158" s="5" t="n"/>
+      <c r="F158" s="5" t="n"/>
+      <c r="G158" s="5" t="n"/>
+      <c r="H158" s="5" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="I158" s="4" t="n">
+      <c r="I158" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="J158" s="4" t="n"/>
-      <c r="K158" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" s="4" t="n"/>
+      <c r="J158" s="5" t="n"/>
+      <c r="K158" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -9421,22 +9423,22 @@
           <t>LEV-1</t>
         </is>
       </c>
-      <c r="E159" s="4" t="n">
+      <c r="E159" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="F159" s="4" t="n"/>
-      <c r="G159" s="4" t="n"/>
-      <c r="H159" s="4" t="n"/>
-      <c r="I159" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J159" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="4" t="n">
+      <c r="F159" s="5" t="n"/>
+      <c r="G159" s="5" t="n"/>
+      <c r="H159" s="5" t="n"/>
+      <c r="I159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9461,22 +9463,22 @@
           <t>LEV-2</t>
         </is>
       </c>
-      <c r="E160" s="4" t="n">
+      <c r="E160" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="F160" s="4" t="n"/>
-      <c r="G160" s="4" t="n"/>
-      <c r="H160" s="4" t="n"/>
-      <c r="I160" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="4" t="n">
+      <c r="F160" s="5" t="n"/>
+      <c r="G160" s="5" t="n"/>
+      <c r="H160" s="5" t="n"/>
+      <c r="I160" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9501,28 +9503,28 @@
           <t>LEV01</t>
         </is>
       </c>
-      <c r="E161" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" s="4" t="n">
+      <c r="E161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H161" s="4" t="n">
+      <c r="H161" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I161" s="4" t="n">
+      <c r="I161" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J161" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" s="4" t="n">
+      <c r="J161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L161" s="4" t="n">
+      <c r="L161" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9547,20 +9549,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E162" s="4" t="n"/>
-      <c r="F162" s="4" t="n"/>
-      <c r="G162" s="4" t="n"/>
-      <c r="H162" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="4" t="n"/>
-      <c r="K162" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" s="4" t="n"/>
+      <c r="E162" s="5" t="n"/>
+      <c r="F162" s="5" t="n"/>
+      <c r="G162" s="5" t="n"/>
+      <c r="H162" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="5" t="n"/>
+      <c r="K162" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -9583,28 +9585,28 @@
           <t>BAX+1</t>
         </is>
       </c>
-      <c r="E163" s="4" t="n">
+      <c r="E163" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F163" s="4" t="n">
+      <c r="F163" s="5" t="n">
         <v>3.271465593833381</v>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="5" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="H163" s="4" t="n">
+      <c r="H163" s="5" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="I163" s="4" t="n">
+      <c r="I163" s="5" t="n">
         <v>0.004</v>
       </c>
-      <c r="J163" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L163" s="4" t="n">
+      <c r="J163" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9629,22 +9631,22 @@
           <t>BAX-1</t>
         </is>
       </c>
-      <c r="E164" s="4" t="n">
+      <c r="E164" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="F164" s="4" t="n"/>
-      <c r="G164" s="4" t="n"/>
-      <c r="H164" s="4" t="n"/>
-      <c r="I164" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="4" t="n">
+      <c r="F164" s="5" t="n"/>
+      <c r="G164" s="5" t="n"/>
+      <c r="H164" s="5" t="n"/>
+      <c r="I164" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9669,28 +9671,28 @@
           <t>BAX01</t>
         </is>
       </c>
-      <c r="E165" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" s="4" t="n">
+      <c r="E165" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="5" t="n">
         <v>0.003565707852896025</v>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="5" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="H165" s="4" t="n">
+      <c r="H165" s="5" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="I165" s="4" t="n">
+      <c r="I165" s="5" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="J165" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" s="4" t="n">
+      <c r="J165" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L165" s="4" t="n">
+      <c r="L165" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9715,28 +9717,28 @@
           <t>BAX02</t>
         </is>
       </c>
-      <c r="E166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F166" s="4" t="n">
+      <c r="E166" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H166" s="4" t="n">
+      <c r="H166" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="I166" s="4" t="n">
+      <c r="I166" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L166" s="4" t="n">
+      <c r="J166" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9761,20 +9763,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E167" s="4" t="n"/>
-      <c r="F167" s="4" t="n"/>
-      <c r="G167" s="4" t="n"/>
-      <c r="H167" s="4" t="n">
+      <c r="E167" s="5" t="n"/>
+      <c r="F167" s="5" t="n"/>
+      <c r="G167" s="5" t="n"/>
+      <c r="H167" s="5" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="I167" s="4" t="n">
+      <c r="I167" s="5" t="n">
         <v>0.004</v>
       </c>
-      <c r="J167" s="4" t="n"/>
-      <c r="K167" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="4" t="n"/>
+      <c r="J167" s="5" t="n"/>
+      <c r="K167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -9797,28 +9799,28 @@
           <t>BAX+1</t>
         </is>
       </c>
-      <c r="E168" s="4" t="n">
+      <c r="E168" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F168" s="4" t="n">
+      <c r="F168" s="5" t="n">
         <v>3.271465593833381</v>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="5" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="H168" s="4" t="n">
+      <c r="H168" s="5" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="I168" s="4" t="n">
+      <c r="I168" s="5" t="n">
         <v>0.004</v>
       </c>
-      <c r="J168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="4" t="n">
+      <c r="J168" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9843,22 +9845,22 @@
           <t>BAX-1</t>
         </is>
       </c>
-      <c r="E169" s="4" t="n">
+      <c r="E169" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="F169" s="4" t="n"/>
-      <c r="G169" s="4" t="n"/>
-      <c r="H169" s="4" t="n"/>
-      <c r="I169" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L169" s="4" t="n">
+      <c r="F169" s="5" t="n"/>
+      <c r="G169" s="5" t="n"/>
+      <c r="H169" s="5" t="n"/>
+      <c r="I169" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9883,28 +9885,28 @@
           <t>BAX01</t>
         </is>
       </c>
-      <c r="E170" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="4" t="n">
+      <c r="E170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="5" t="n">
         <v>0.003565707852896025</v>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="5" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="H170" s="4" t="n">
+      <c r="H170" s="5" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="I170" s="4" t="n">
+      <c r="I170" s="5" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="J170" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" s="4" t="n">
+      <c r="J170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L170" s="4" t="n">
+      <c r="L170" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9929,28 +9931,28 @@
           <t>BAX02</t>
         </is>
       </c>
-      <c r="E171" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" s="4" t="n">
+      <c r="E171" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="5" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="H171" s="4" t="n">
+      <c r="H171" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="I171" s="4" t="n">
+      <c r="I171" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J171" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" s="4" t="n">
+      <c r="J171" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9975,20 +9977,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E172" s="4" t="n"/>
-      <c r="F172" s="4" t="n"/>
-      <c r="G172" s="4" t="n"/>
-      <c r="H172" s="4" t="n">
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="5" t="n"/>
+      <c r="G172" s="5" t="n"/>
+      <c r="H172" s="5" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="I172" s="4" t="n">
+      <c r="I172" s="5" t="n">
         <v>0.004</v>
       </c>
-      <c r="J172" s="4" t="n"/>
-      <c r="K172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="4" t="n"/>
+      <c r="J172" s="5" t="n"/>
+      <c r="K172" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -10011,28 +10013,28 @@
           <t>B49+1</t>
         </is>
       </c>
-      <c r="E173" s="4" t="n">
+      <c r="E173" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F173" s="4" t="n">
+      <c r="F173" s="5" t="n">
         <v>0.007753004432578372</v>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="5" t="n">
         <v>0.987</v>
       </c>
-      <c r="H173" s="4" t="n">
+      <c r="H173" s="5" t="n">
         <v>0.987</v>
       </c>
-      <c r="I173" s="4" t="n">
+      <c r="I173" s="5" t="n">
         <v>0.987</v>
       </c>
-      <c r="J173" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K173" s="4" t="n">
+      <c r="J173" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" s="5" t="n">
         <v>0.8933333333333334</v>
       </c>
-      <c r="L173" s="4" t="n">
+      <c r="L173" s="5" t="n">
         <v>0.005897268670984716</v>
       </c>
     </row>
@@ -10057,28 +10059,28 @@
           <t>B4901</t>
         </is>
       </c>
-      <c r="E174" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" s="4" t="n">
+      <c r="E174" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="5" t="n">
         <v>2.573112508500956</v>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="5" t="n">
         <v>0.013</v>
       </c>
-      <c r="H174" s="4" t="n">
+      <c r="H174" s="5" t="n">
         <v>0.013</v>
       </c>
-      <c r="I174" s="4" t="n">
+      <c r="I174" s="5" t="n">
         <v>0.013</v>
       </c>
-      <c r="J174" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K174" s="4" t="n">
+      <c r="J174" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" s="5" t="n">
         <v>0.1066666666666667</v>
       </c>
-      <c r="L174" s="4" t="n">
+      <c r="L174" s="5" t="n">
         <v>0.005897268670984712</v>
       </c>
     </row>
@@ -10103,22 +10105,22 @@
           <t>B4902</t>
         </is>
       </c>
-      <c r="E175" s="4" t="n">
+      <c r="E175" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F175" s="4" t="n"/>
-      <c r="G175" s="4" t="n"/>
-      <c r="H175" s="4" t="n"/>
-      <c r="I175" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J175" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K175" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L175" s="4" t="n">
+      <c r="F175" s="5" t="n"/>
+      <c r="G175" s="5" t="n"/>
+      <c r="H175" s="5" t="n"/>
+      <c r="I175" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10143,22 +10145,22 @@
           <t>B4903</t>
         </is>
       </c>
-      <c r="E176" s="4" t="n">
+      <c r="E176" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F176" s="4" t="n"/>
-      <c r="G176" s="4" t="n"/>
-      <c r="H176" s="4" t="n"/>
-      <c r="I176" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J176" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K176" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L176" s="4" t="n">
+      <c r="F176" s="5" t="n"/>
+      <c r="G176" s="5" t="n"/>
+      <c r="H176" s="5" t="n"/>
+      <c r="I176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10183,20 +10185,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E177" s="4" t="n"/>
-      <c r="F177" s="4" t="n"/>
-      <c r="G177" s="4" t="n"/>
-      <c r="H177" s="4" t="n">
+      <c r="E177" s="5" t="n"/>
+      <c r="F177" s="5" t="n"/>
+      <c r="G177" s="5" t="n"/>
+      <c r="H177" s="5" t="n">
         <v>0.987</v>
       </c>
-      <c r="I177" s="4" t="n">
+      <c r="I177" s="5" t="n">
         <v>0.987</v>
       </c>
-      <c r="J177" s="4" t="n"/>
-      <c r="K177" s="4" t="n">
+      <c r="J177" s="5" t="n"/>
+      <c r="K177" s="5" t="n">
         <v>0.8933333333333334</v>
       </c>
-      <c r="L177" s="4" t="n"/>
+      <c r="L177" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables_Trials/kinase_project-trials-tables_values.xlsx
+++ b/tables_Trials/kinase_project-trials-tables_values.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.###;-0.###;0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -59,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2699,28 +2697,28 @@
           <t>DB8+1</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="E2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>0.07037924507405544</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="4" t="n">
         <v>0.888</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.888</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="4" t="n">
         <v>0.888</v>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5" t="n">
+      <c r="J2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4" t="n">
         <v>0.5596666666666668</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="L2" s="4" t="n">
         <v>0.001452966314513559</v>
       </c>
     </row>
@@ -2745,28 +2743,28 @@
           <t>DB8+2</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5" t="n">
+      <c r="E3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>1.697337126604945</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="4" t="n">
         <v>0.057</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="4" t="n">
         <v>0.057</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="4" t="n">
         <v>0.057</v>
       </c>
-      <c r="J3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5" t="n">
+      <c r="J3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4" t="n">
         <v>0.3966666666666667</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="4" t="n">
         <v>0.002333333333333335</v>
       </c>
     </row>
@@ -2791,28 +2789,28 @@
           <t>DB801</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="4" t="n">
         <v>1.718500090546677</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="4" t="n">
         <v>0.055</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="4" t="n">
         <v>0.055</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="4" t="n">
         <v>0.055</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5" t="n">
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
         <v>0.04366666666666667</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="L4" s="4" t="n">
         <v>0.0008819171036881955</v>
       </c>
     </row>
@@ -2837,22 +2835,22 @@
           <t>DB802</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5" t="n">
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2877,22 +2875,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="5" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2915,20 +2913,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n">
         <v>0.9450000000000001</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="4" t="n">
         <v>0.9450000000000001</v>
       </c>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n">
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n">
         <v>0.9563333333333335</v>
       </c>
-      <c r="L7" s="5" t="n"/>
+      <c r="L7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2951,28 +2949,28 @@
           <t>STI+1</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="4" t="n">
         <v>1.004</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="4" t="n">
         <v>0.3146342861669798</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.588</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="4" t="n">
         <v>0.588</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="4" t="n">
         <v>0.588</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5" t="n">
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L8" s="4" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -2997,28 +2995,28 @@
           <t>STI+2</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.995</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="4" t="n">
         <v>0.5732935355600606</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="4" t="n">
         <v>0.3800000000000001</v>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5" t="n">
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>0.999</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L9" s="4" t="n">
         <v>0.001000000000000001</v>
       </c>
     </row>
@@ -3043,22 +3041,22 @@
           <t>STI+a</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="4" t="n">
         <v>1.995</v>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5" t="n">
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3083,22 +3081,22 @@
           <t>STI+b</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="4" t="n">
         <v>2.002</v>
       </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5" t="n">
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3123,28 +3121,28 @@
           <t>STI01</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="4" t="n">
         <v>-0.002</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="4" t="n">
         <v>2.039396480388078</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="4" t="n">
         <v>0.03200000000000001</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="4" t="n">
         <v>0.03200000000000001</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I12" s="4" t="n">
         <v>0.032</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="n">
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3169,22 +3167,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="5" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3207,20 +3205,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n">
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n">
         <v>0.968388</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="4" t="n">
         <v>0.9683880000000001</v>
       </c>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n">
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n">
         <v>0.995009</v>
       </c>
-      <c r="L14" s="5" t="n"/>
+      <c r="L14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3243,28 +3241,28 @@
           <t>STI+1</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="4" t="n">
         <v>1.004</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="4" t="n">
         <v>0.3146342861669798</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="4" t="n">
         <v>0.588</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="4" t="n">
         <v>0.588</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I15" s="4" t="n">
         <v>0.588</v>
       </c>
-      <c r="J15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5" t="n">
+      <c r="J15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="n">
         <v>0.003</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="L15" s="4" t="n">
         <v>0.001527525231651947</v>
       </c>
     </row>
@@ -3289,28 +3287,28 @@
           <t>STI+2</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="4" t="n">
         <v>0.995</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="4" t="n">
         <v>0.5732935355600606</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I16" s="4" t="n">
         <v>0.3800000000000001</v>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5" t="n">
+      <c r="J16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="n">
         <v>0.997</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="L16" s="4" t="n">
         <v>0.001527525231651948</v>
       </c>
     </row>
@@ -3335,22 +3333,22 @@
           <t>STI+a</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="4" t="n">
         <v>1.995</v>
       </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="5" t="n">
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3375,22 +3373,22 @@
           <t>STI+b</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="4" t="n">
         <v>2.002</v>
       </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="5" t="n">
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3415,28 +3413,28 @@
           <t>STI01</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="4" t="n">
         <v>-0.002</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="4" t="n">
         <v>2.039396480388078</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="4" t="n">
         <v>0.03200000000000001</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" s="4" t="n">
         <v>0.03200000000000001</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I19" s="4" t="n">
         <v>0.032</v>
       </c>
-      <c r="J19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="5" t="n">
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3461,22 +3459,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="5" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3499,20 +3497,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n">
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n">
         <v>0.968388</v>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I21" s="4" t="n">
         <v>0.9683880000000001</v>
       </c>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n">
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n">
         <v>0.995027</v>
       </c>
-      <c r="L21" s="5" t="n"/>
+      <c r="L21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3535,28 +3533,28 @@
           <t>NIL+1</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="5" t="n">
+      <c r="E22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4" t="n">
         <v>1.407279803103612</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I22" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5" t="n">
+      <c r="J22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4" t="n">
         <v>0.324</v>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="L22" s="4" t="n">
         <v>0.1406307221058045</v>
       </c>
     </row>
@@ -3581,22 +3579,22 @@
           <t>NIL+2</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="5" t="n">
+      <c r="E23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3621,28 +3619,28 @@
           <t>NIL01</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="4" t="n">
         <v>0.05783560110369775</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="4" t="n">
         <v>0.907</v>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H24" s="4" t="n">
         <v>0.907</v>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="I24" s="4" t="n">
         <v>0.907</v>
       </c>
-      <c r="J24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5" t="n">
+      <c r="J24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4" t="n">
         <v>0.676</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="L24" s="4" t="n">
         <v>0.1406307221058045</v>
       </c>
     </row>
@@ -3667,22 +3665,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="5" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3705,20 +3703,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n">
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="I26" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n">
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n">
         <v>0.324</v>
       </c>
-      <c r="L26" s="5" t="n"/>
+      <c r="L26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3741,28 +3739,28 @@
           <t>NIL+1</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="5" t="n">
+      <c r="E27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4" t="n">
         <v>1.407279803103612</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H27" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="I27" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="J27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="5" t="n">
+      <c r="J27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="n">
         <v>0.3123333333333333</v>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="L27" s="4" t="n">
         <v>0.08504377957525433</v>
       </c>
     </row>
@@ -3787,22 +3785,22 @@
           <t>NIL+2</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="5" t="n">
+      <c r="E28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3827,28 +3825,28 @@
           <t>NIL01</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="4" t="n">
         <v>0.05783560110369775</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G29" s="4" t="n">
         <v>0.907</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="4" t="n">
         <v>0.907</v>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I29" s="4" t="n">
         <v>0.907</v>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="5" t="n">
+      <c r="J29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="n">
         <v>0.6876666666666668</v>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="L29" s="4" t="n">
         <v>0.08504377957525433</v>
       </c>
     </row>
@@ -3873,22 +3871,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="5" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3911,20 +3909,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n">
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="I31" s="5" t="n">
+      <c r="I31" s="4" t="n">
         <v>0.09300000000000001</v>
       </c>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n">
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n">
         <v>0.3123333333333333</v>
       </c>
-      <c r="L31" s="5" t="n"/>
+      <c r="L31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3947,28 +3945,28 @@
           <t>EMH+1</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="5" t="n">
+      <c r="E32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4" t="n">
         <v>0.3424853662747186</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G32" s="4" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" s="4" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I32" s="4" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="J32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="5" t="n">
+      <c r="J32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4" t="n">
         <v>0.827</v>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="L32" s="4" t="n">
         <v>0.03750999866702211</v>
       </c>
     </row>
@@ -3993,28 +3991,28 @@
           <t>EMH01</t>
         </is>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="4" t="n">
         <v>0.4877791005498772</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G33" s="4" t="n">
         <v>0.439</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" s="4" t="n">
         <v>0.439</v>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I33" s="4" t="n">
         <v>0.439</v>
       </c>
-      <c r="J33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="5" t="n">
+      <c r="J33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4" t="n">
         <v>0.173</v>
       </c>
-      <c r="L33" s="5" t="n">
+      <c r="L33" s="4" t="n">
         <v>0.03750999866702211</v>
       </c>
     </row>
@@ -4039,22 +4037,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" s="5" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4077,20 +4075,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="I35" s="4" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n">
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n">
         <v>0.827</v>
       </c>
-      <c r="L35" s="5" t="n"/>
+      <c r="L35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4113,28 +4111,28 @@
           <t>4MK+1</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="5" t="n">
+      <c r="E36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="n">
         <v>0.0005927964476482441</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G36" s="4" t="n">
         <v>0.999</v>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="H36" s="4" t="n">
         <v>0.999</v>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="I36" s="4" t="n">
         <v>0.999</v>
       </c>
-      <c r="J36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="5" t="n">
+      <c r="J36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4159,22 +4157,22 @@
           <t>4MK+a</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="5" t="n">
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4199,28 +4197,28 @@
           <t>4MK01</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="4" t="n">
         <v>4.092845002796916</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G38" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="H38" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="I38" s="5" t="n">
+      <c r="I38" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="J38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="5" t="n">
+      <c r="J38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4245,22 +4243,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="5" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4283,20 +4281,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n">
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n">
         <v>0.999</v>
       </c>
-      <c r="I40" s="5" t="n">
+      <c r="I40" s="4" t="n">
         <v>0.999</v>
       </c>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="5" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4319,28 +4317,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="5" t="n">
+      <c r="E41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="G41" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" s="4" t="n">
         <v>0.378</v>
       </c>
-      <c r="I41" s="5" t="n">
+      <c r="I41" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="5" t="n">
+      <c r="J41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4365,28 +4363,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="5" t="n">
+      <c r="E42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G42" s="5" t="n">
+      <c r="G42" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H42" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I42" s="5" t="n">
+      <c r="I42" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="5" t="n">
+      <c r="J42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4411,28 +4409,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="G43" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="H43" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I43" s="5" t="n">
+      <c r="I43" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="J43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="5" t="n">
+      <c r="J43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4457,28 +4455,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="5" t="n">
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="G44" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="H44" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I44" s="5" t="n">
+      <c r="I44" s="4" t="n">
         <v>0.005</v>
       </c>
-      <c r="J44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="5" t="n">
+      <c r="J44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4503,22 +4501,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="H45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="5" t="n">
+      <c r="H45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" s="5" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4541,20 +4539,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n">
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="I46" s="5" t="n">
+      <c r="I46" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="5" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4577,28 +4575,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="5" t="n">
+      <c r="E47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G47" s="5" t="n">
+      <c r="G47" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H47" s="5" t="n">
+      <c r="H47" s="4" t="n">
         <v>0.378</v>
       </c>
-      <c r="I47" s="5" t="n">
+      <c r="I47" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="5" t="n">
+      <c r="J47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4623,28 +4621,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="5" t="n">
+      <c r="E48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G48" s="5" t="n">
+      <c r="G48" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H48" s="5" t="n">
+      <c r="H48" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I48" s="5" t="n">
+      <c r="I48" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="5" t="n">
+      <c r="J48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4669,28 +4667,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="G49" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="H49" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I49" s="5" t="n">
+      <c r="I49" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="J49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="5" t="n">
+      <c r="J49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4715,28 +4713,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="5" t="n">
+      <c r="E50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G50" s="5" t="n">
+      <c r="G50" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H50" s="5" t="n">
+      <c r="H50" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I50" s="5" t="n">
+      <c r="I50" s="4" t="n">
         <v>0.005</v>
       </c>
-      <c r="J50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="5" t="n">
+      <c r="J50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4761,22 +4759,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n">
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="H51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="5" t="n">
+      <c r="H51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" s="5" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4799,20 +4797,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n">
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="I52" s="5" t="n">
+      <c r="I52" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="5" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4835,28 +4833,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="5" t="n">
+      <c r="E53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G53" s="5" t="n">
+      <c r="G53" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H53" s="5" t="n">
+      <c r="H53" s="4" t="n">
         <v>0.378</v>
       </c>
-      <c r="I53" s="5" t="n">
+      <c r="I53" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="5" t="n">
+      <c r="J53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4881,28 +4879,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="5" t="n">
+      <c r="E54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G54" s="5" t="n">
+      <c r="G54" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H54" s="5" t="n">
+      <c r="H54" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I54" s="5" t="n">
+      <c r="I54" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="5" t="n">
+      <c r="J54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4927,28 +4925,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n">
+      <c r="E55" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="F55" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G55" s="5" t="n">
+      <c r="G55" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H55" s="5" t="n">
+      <c r="H55" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I55" s="5" t="n">
+      <c r="I55" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="J55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="5" t="n">
+      <c r="J55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4973,28 +4971,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="5" t="n">
+      <c r="E56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G56" s="5" t="n">
+      <c r="G56" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H56" s="5" t="n">
+      <c r="H56" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I56" s="5" t="n">
+      <c r="I56" s="4" t="n">
         <v>0.005</v>
       </c>
-      <c r="J56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="5" t="n">
+      <c r="J56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5019,22 +5017,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="n">
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="H57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" s="5" t="n">
+      <c r="H57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="5" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5057,20 +5055,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n">
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="I58" s="5" t="n">
+      <c r="I58" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="5" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5093,28 +5091,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="5" t="n">
+      <c r="E59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G59" s="5" t="n">
+      <c r="G59" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H59" s="5" t="n">
+      <c r="H59" s="4" t="n">
         <v>0.378</v>
       </c>
-      <c r="I59" s="5" t="n">
+      <c r="I59" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="5" t="n">
+      <c r="J59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5139,28 +5137,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E60" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="5" t="n">
+      <c r="E60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G60" s="5" t="n">
+      <c r="G60" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H60" s="5" t="n">
+      <c r="H60" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I60" s="5" t="n">
+      <c r="I60" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="5" t="n">
+      <c r="J60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5185,28 +5183,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F61" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G61" s="5" t="n">
+      <c r="G61" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H61" s="5" t="n">
+      <c r="H61" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I61" s="5" t="n">
+      <c r="I61" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="J61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="5" t="n">
+      <c r="J61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5231,28 +5229,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5" t="n">
+      <c r="E62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G62" s="5" t="n">
+      <c r="G62" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H62" s="5" t="n">
+      <c r="H62" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I62" s="5" t="n">
+      <c r="I62" s="4" t="n">
         <v>0.005</v>
       </c>
-      <c r="J62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="5" t="n">
+      <c r="J62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5277,22 +5275,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="n">
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="H63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" s="5" t="n">
+      <c r="H63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" s="5" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5315,20 +5313,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n">
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="I64" s="5" t="n">
+      <c r="I64" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="5" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5351,28 +5349,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="n">
+      <c r="E65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G65" s="5" t="n">
+      <c r="G65" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H65" s="5" t="n">
+      <c r="H65" s="4" t="n">
         <v>0.378</v>
       </c>
-      <c r="I65" s="5" t="n">
+      <c r="I65" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" s="5" t="n">
+      <c r="J65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5397,28 +5395,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="5" t="n">
+      <c r="E66" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G66" s="5" t="n">
+      <c r="G66" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H66" s="5" t="n">
+      <c r="H66" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I66" s="5" t="n">
+      <c r="I66" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="5" t="n">
+      <c r="J66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5443,28 +5441,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E67" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F67" s="5" t="n">
+      <c r="F67" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G67" s="5" t="n">
+      <c r="G67" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H67" s="5" t="n">
+      <c r="H67" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I67" s="5" t="n">
+      <c r="I67" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="J67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="5" t="n">
+      <c r="J67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5489,28 +5487,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="5" t="n">
+      <c r="E68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G68" s="5" t="n">
+      <c r="G68" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H68" s="5" t="n">
+      <c r="H68" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I68" s="5" t="n">
+      <c r="I68" s="4" t="n">
         <v>0.005</v>
       </c>
-      <c r="J68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="5" t="n">
+      <c r="J68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5535,22 +5533,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n">
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="H69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I69" s="5" t="n">
+      <c r="H69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="5" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5573,20 +5571,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n">
+      <c r="E70" s="4" t="n"/>
+      <c r="F70" s="4" t="n"/>
+      <c r="G70" s="4" t="n"/>
+      <c r="H70" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="I70" s="5" t="n">
+      <c r="I70" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="5" t="n"/>
+      <c r="J70" s="4" t="n"/>
+      <c r="K70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5609,28 +5607,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="5" t="n">
+      <c r="E71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G71" s="5" t="n">
+      <c r="G71" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H71" s="5" t="n">
+      <c r="H71" s="4" t="n">
         <v>0.378</v>
       </c>
-      <c r="I71" s="5" t="n">
+      <c r="I71" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" s="5" t="n">
+      <c r="J71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5655,28 +5653,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="5" t="n">
+      <c r="E72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G72" s="5" t="n">
+      <c r="G72" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H72" s="5" t="n">
+      <c r="H72" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I72" s="5" t="n">
+      <c r="I72" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="5" t="n">
+      <c r="J72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5701,28 +5699,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="E73" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="5" t="n">
+      <c r="F73" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G73" s="5" t="n">
+      <c r="G73" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H73" s="5" t="n">
+      <c r="H73" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I73" s="5" t="n">
+      <c r="I73" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="J73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="5" t="n">
+      <c r="J73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5747,28 +5745,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="5" t="n">
+      <c r="E74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G74" s="5" t="n">
+      <c r="G74" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H74" s="5" t="n">
+      <c r="H74" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I74" s="5" t="n">
+      <c r="I74" s="4" t="n">
         <v>0.005</v>
       </c>
-      <c r="J74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="5" t="n">
+      <c r="J74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5793,22 +5791,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="n">
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="H75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I75" s="5" t="n">
+      <c r="H75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="J75" s="5" t="n"/>
-      <c r="K75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="5" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5831,20 +5829,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="5" t="n">
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="I76" s="5" t="n">
+      <c r="I76" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="J76" s="5" t="n"/>
-      <c r="K76" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" s="5" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5867,28 +5865,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="5" t="n">
+      <c r="E77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G77" s="5" t="n">
+      <c r="G77" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H77" s="5" t="n">
+      <c r="H77" s="4" t="n">
         <v>0.378</v>
       </c>
-      <c r="I77" s="5" t="n">
+      <c r="I77" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J77" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" s="5" t="n">
+      <c r="J77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5913,28 +5911,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="5" t="n">
+      <c r="E78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G78" s="5" t="n">
+      <c r="G78" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H78" s="5" t="n">
+      <c r="H78" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I78" s="5" t="n">
+      <c r="I78" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="5" t="n">
+      <c r="J78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5959,28 +5957,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E79" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F79" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G79" s="5" t="n">
+      <c r="G79" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H79" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I79" s="5" t="n">
+      <c r="I79" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="J79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="5" t="n">
+      <c r="J79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6005,28 +6003,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="5" t="n">
+      <c r="E80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G80" s="5" t="n">
+      <c r="G80" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H80" s="5" t="n">
+      <c r="H80" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I80" s="5" t="n">
+      <c r="I80" s="4" t="n">
         <v>0.005</v>
       </c>
-      <c r="J80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="5" t="n">
+      <c r="J80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6051,22 +6049,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="n"/>
-      <c r="G81" s="5" t="n">
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="H81" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I81" s="5" t="n">
+      <c r="H81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="J81" s="5" t="n"/>
-      <c r="K81" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="5" t="n"/>
+      <c r="J81" s="4" t="n"/>
+      <c r="K81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6089,20 +6087,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="5" t="n">
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="n"/>
+      <c r="H82" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="I82" s="5" t="n">
+      <c r="I82" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="J82" s="5" t="n"/>
-      <c r="K82" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" s="5" t="n"/>
+      <c r="J82" s="4" t="n"/>
+      <c r="K82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6125,28 +6123,28 @@
           <t>LQQ+1</t>
         </is>
       </c>
-      <c r="E83" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="5" t="n">
+      <c r="E83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="4" t="n">
         <v>0.01500080123069177</v>
       </c>
-      <c r="G83" s="5" t="n">
+      <c r="G83" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="H83" s="5" t="n">
+      <c r="H83" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="I83" s="5" t="n">
+      <c r="I83" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="J83" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="5" t="n">
+      <c r="J83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="4" t="n">
         <v>0.999</v>
       </c>
-      <c r="L83" s="5" t="n">
+      <c r="L83" s="4" t="n">
         <v>0.0005773502691896263</v>
       </c>
     </row>
@@ -6171,28 +6169,28 @@
           <t>LQQ01</t>
         </is>
       </c>
-      <c r="E84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="5" t="n">
+      <c r="E84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="n">
         <v>2.185661076562508</v>
       </c>
-      <c r="G84" s="5" t="n">
+      <c r="G84" s="4" t="n">
         <v>0.02499999999999999</v>
       </c>
-      <c r="H84" s="5" t="n">
+      <c r="H84" s="4" t="n">
         <v>0.02499999999999999</v>
       </c>
-      <c r="I84" s="5" t="n">
+      <c r="I84" s="4" t="n">
         <v>0.025</v>
       </c>
-      <c r="J84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="5" t="n">
+      <c r="J84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="L84" s="5" t="n">
+      <c r="L84" s="4" t="n">
         <v>0.0005773502691896258</v>
       </c>
     </row>
@@ -6217,22 +6215,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
-      <c r="G85" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="5" t="n"/>
-      <c r="K85" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="5" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6255,20 +6253,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E86" s="5" t="n"/>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="n"/>
-      <c r="H86" s="5" t="n">
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="n"/>
+      <c r="G86" s="4" t="n"/>
+      <c r="H86" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="I86" s="5" t="n">
+      <c r="I86" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n">
+      <c r="J86" s="4" t="n"/>
+      <c r="K86" s="4" t="n">
         <v>0.999</v>
       </c>
-      <c r="L86" s="5" t="n"/>
+      <c r="L86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6291,28 +6289,28 @@
           <t>LQQ+1</t>
         </is>
       </c>
-      <c r="E87" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="5" t="n">
+      <c r="E87" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="4" t="n">
         <v>0.01500080123069177</v>
       </c>
-      <c r="G87" s="5" t="n">
+      <c r="G87" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="H87" s="5" t="n">
+      <c r="H87" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="I87" s="5" t="n">
+      <c r="I87" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="J87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="5" t="n">
+      <c r="J87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="4" t="n">
         <v>0.9936666666666666</v>
       </c>
-      <c r="L87" s="5" t="n">
+      <c r="L87" s="4" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -6337,28 +6335,28 @@
           <t>LQQ01</t>
         </is>
       </c>
-      <c r="E88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="5" t="n">
+      <c r="E88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="n">
         <v>2.185661076562508</v>
       </c>
-      <c r="G88" s="5" t="n">
+      <c r="G88" s="4" t="n">
         <v>0.02499999999999999</v>
       </c>
-      <c r="H88" s="5" t="n">
+      <c r="H88" s="4" t="n">
         <v>0.02499999999999999</v>
       </c>
-      <c r="I88" s="5" t="n">
+      <c r="I88" s="4" t="n">
         <v>0.025</v>
       </c>
-      <c r="J88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="5" t="n">
+      <c r="J88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="4" t="n">
         <v>0.006333333333333333</v>
       </c>
-      <c r="L88" s="5" t="n">
+      <c r="L88" s="4" t="n">
         <v>0.0003333333333333334</v>
       </c>
     </row>
@@ -6383,22 +6381,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E89" s="5" t="n"/>
-      <c r="F89" s="5" t="n"/>
-      <c r="G89" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="5" t="n"/>
-      <c r="K89" s="5" t="n">
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="4" t="n"/>
+      <c r="K89" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="L89" s="5" t="n"/>
+      <c r="L89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6421,20 +6419,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="5" t="n">
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="4" t="n"/>
+      <c r="H90" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="I90" s="5" t="n">
+      <c r="I90" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="n">
+      <c r="J90" s="4" t="n"/>
+      <c r="K90" s="4" t="n">
         <v>0.9936666666666666</v>
       </c>
-      <c r="L90" s="5" t="n"/>
+      <c r="L90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6457,28 +6455,28 @@
           <t>0LI+1</t>
         </is>
       </c>
-      <c r="E91" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" s="5" t="n">
+      <c r="E91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="4" t="n">
         <v>0.3046424810811669</v>
       </c>
-      <c r="G91" s="5" t="n">
+      <c r="G91" s="4" t="n">
         <v>0.598</v>
       </c>
-      <c r="H91" s="5" t="n">
+      <c r="H91" s="4" t="n">
         <v>0.598</v>
       </c>
-      <c r="I91" s="5" t="n">
+      <c r="I91" s="4" t="n">
         <v>0.598</v>
       </c>
-      <c r="J91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="5" t="n">
+      <c r="J91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6503,28 +6501,28 @@
           <t>0LI+2</t>
         </is>
       </c>
-      <c r="E92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="5" t="n">
+      <c r="E92" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="4" t="n">
         <v>0.5971558207992901</v>
       </c>
-      <c r="G92" s="5" t="n">
+      <c r="G92" s="4" t="n">
         <v>0.365</v>
       </c>
-      <c r="H92" s="5" t="n">
+      <c r="H92" s="4" t="n">
         <v>0.365</v>
       </c>
-      <c r="I92" s="5" t="n">
+      <c r="I92" s="4" t="n">
         <v>0.365</v>
       </c>
-      <c r="J92" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" s="5" t="n">
+      <c r="J92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6549,28 +6547,28 @@
           <t>0LI01</t>
         </is>
       </c>
-      <c r="E93" s="5" t="n">
+      <c r="E93" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F93" s="5" t="n">
+      <c r="F93" s="4" t="n">
         <v>1.953376139555213</v>
       </c>
-      <c r="G93" s="5" t="n">
+      <c r="G93" s="4" t="n">
         <v>0.03700000000000001</v>
       </c>
-      <c r="H93" s="5" t="n">
+      <c r="H93" s="4" t="n">
         <v>0.03700000000000001</v>
       </c>
-      <c r="I93" s="5" t="n">
+      <c r="I93" s="4" t="n">
         <v>0.037</v>
       </c>
-      <c r="J93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="5" t="n">
+      <c r="J93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6595,22 +6593,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E94" s="5" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="5" t="n"/>
-      <c r="K94" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="5" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6633,20 +6631,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="n"/>
-      <c r="H95" s="5" t="n">
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n">
         <v>0.963</v>
       </c>
-      <c r="I95" s="5" t="n">
+      <c r="I95" s="4" t="n">
         <v>0.963</v>
       </c>
-      <c r="J95" s="5" t="n"/>
-      <c r="K95" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" s="5" t="n"/>
+      <c r="J95" s="4" t="n"/>
+      <c r="K95" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6669,28 +6667,28 @@
           <t>0WN+1</t>
         </is>
       </c>
-      <c r="E96" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="5" t="n">
+      <c r="E96" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="4" t="n">
         <v>0.004759061730629078</v>
       </c>
-      <c r="G96" s="5" t="n">
+      <c r="G96" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="H96" s="5" t="n">
+      <c r="H96" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="I96" s="5" t="n">
+      <c r="I96" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="J96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="5" t="n">
+      <c r="J96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="4" t="n">
         <v>0.9456666666666665</v>
       </c>
-      <c r="L96" s="5" t="n">
+      <c r="L96" s="4" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -6715,22 +6713,22 @@
           <t>0WN+a</t>
         </is>
       </c>
-      <c r="E97" s="5" t="n">
+      <c r="E97" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="5" t="n"/>
-      <c r="H97" s="5" t="n"/>
-      <c r="I97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="5" t="n">
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
+      <c r="I97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6755,28 +6753,28 @@
           <t>0WN01</t>
         </is>
       </c>
-      <c r="E98" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="5" t="n">
+      <c r="E98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="n">
         <v>2.860775889351614</v>
       </c>
-      <c r="G98" s="5" t="n">
+      <c r="G98" s="4" t="n">
         <v>0.007999999999999997</v>
       </c>
-      <c r="H98" s="5" t="n">
+      <c r="H98" s="4" t="n">
         <v>0.007999999999999997</v>
       </c>
-      <c r="I98" s="5" t="n">
+      <c r="I98" s="4" t="n">
         <v>0.008</v>
       </c>
-      <c r="J98" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="5" t="n">
+      <c r="J98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="4" t="n">
         <v>0.05433333333333334</v>
       </c>
-      <c r="L98" s="5" t="n">
+      <c r="L98" s="4" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -6801,22 +6799,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E99" s="5" t="n"/>
-      <c r="F99" s="5" t="n"/>
-      <c r="G99" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I99" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="5" t="n"/>
-      <c r="K99" s="5" t="n">
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="4" t="n"/>
+      <c r="G99" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="4" t="n"/>
+      <c r="K99" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="L99" s="5" t="n"/>
+      <c r="L99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6839,20 +6837,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E100" s="5" t="n"/>
-      <c r="F100" s="5" t="n"/>
-      <c r="G100" s="5" t="n"/>
-      <c r="H100" s="5" t="n">
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="I100" s="5" t="n">
+      <c r="I100" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="J100" s="5" t="n"/>
-      <c r="K100" s="5" t="n">
+      <c r="J100" s="4" t="n"/>
+      <c r="K100" s="4" t="n">
         <v>0.9456666666666665</v>
       </c>
-      <c r="L100" s="5" t="n"/>
+      <c r="L100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6875,28 +6873,28 @@
           <t>0WN+1</t>
         </is>
       </c>
-      <c r="E101" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="5" t="n">
+      <c r="E101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="4" t="n">
         <v>0.004759061730629078</v>
       </c>
-      <c r="G101" s="5" t="n">
+      <c r="G101" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="H101" s="5" t="n">
+      <c r="H101" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="I101" s="5" t="n">
+      <c r="I101" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="J101" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="5" t="n">
+      <c r="J101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="L101" s="5" t="n">
+      <c r="L101" s="4" t="n">
         <v>0.001527525231651948</v>
       </c>
     </row>
@@ -6921,22 +6919,22 @@
           <t>0WN+a</t>
         </is>
       </c>
-      <c r="E102" s="5" t="n">
+      <c r="E102" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F102" s="5" t="n"/>
-      <c r="G102" s="5" t="n"/>
-      <c r="H102" s="5" t="n"/>
-      <c r="I102" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="5" t="n">
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6961,28 +6959,28 @@
           <t>0WN01</t>
         </is>
       </c>
-      <c r="E103" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="5" t="n">
+      <c r="E103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="n">
         <v>2.860775889351614</v>
       </c>
-      <c r="G103" s="5" t="n">
+      <c r="G103" s="4" t="n">
         <v>0.007999999999999997</v>
       </c>
-      <c r="H103" s="5" t="n">
+      <c r="H103" s="4" t="n">
         <v>0.007999999999999997</v>
       </c>
-      <c r="I103" s="5" t="n">
+      <c r="I103" s="4" t="n">
         <v>0.008</v>
       </c>
-      <c r="J103" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="5" t="n">
+      <c r="J103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="L103" s="5" t="n">
+      <c r="L103" s="4" t="n">
         <v>0.001527525231651946</v>
       </c>
     </row>
@@ -7007,22 +7005,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E104" s="5" t="n"/>
-      <c r="F104" s="5" t="n"/>
-      <c r="G104" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I104" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" s="5" t="n"/>
-      <c r="K104" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="5" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="4" t="n"/>
+      <c r="K104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7045,20 +7043,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E105" s="5" t="n"/>
-      <c r="F105" s="5" t="n"/>
-      <c r="G105" s="5" t="n"/>
-      <c r="H105" s="5" t="n">
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="n"/>
+      <c r="G105" s="4" t="n"/>
+      <c r="H105" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="I105" s="5" t="n">
+      <c r="I105" s="4" t="n">
         <v>0.992</v>
       </c>
-      <c r="J105" s="5" t="n"/>
-      <c r="K105" s="5" t="n">
+      <c r="J105" s="4" t="n"/>
+      <c r="K105" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="L105" s="5" t="n"/>
+      <c r="L105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7081,28 +7079,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E106" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="5" t="n">
+      <c r="E106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G106" s="5" t="n">
+      <c r="G106" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H106" s="5" t="n">
+      <c r="H106" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="I106" s="5" t="n">
+      <c r="I106" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="J106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="5" t="n">
+      <c r="J106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="4" t="n">
         <v>0.7623333333333333</v>
       </c>
-      <c r="L106" s="5" t="n">
+      <c r="L106" s="4" t="n">
         <v>0.02409933147989336</v>
       </c>
     </row>
@@ -7127,28 +7125,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E107" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="5" t="n">
+      <c r="E107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G107" s="5" t="n">
+      <c r="G107" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H107" s="5" t="n">
+      <c r="H107" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I107" s="5" t="n">
+      <c r="I107" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="5" t="n">
+      <c r="J107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7173,22 +7171,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E108" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" s="5" t="n"/>
-      <c r="G108" s="5" t="n"/>
-      <c r="H108" s="5" t="n"/>
-      <c r="I108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="5" t="n">
+      <c r="E108" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="4" t="n"/>
+      <c r="G108" s="4" t="n"/>
+      <c r="H108" s="4" t="n"/>
+      <c r="I108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7213,22 +7211,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E109" s="5" t="n">
+      <c r="E109" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F109" s="5" t="n"/>
-      <c r="G109" s="5" t="n"/>
-      <c r="H109" s="5" t="n"/>
-      <c r="I109" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="5" t="n">
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="n"/>
+      <c r="H109" s="4" t="n"/>
+      <c r="I109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7253,28 +7251,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E110" s="5" t="n">
+      <c r="E110" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F110" s="5" t="n">
+      <c r="F110" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G110" s="5" t="n">
+      <c r="G110" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H110" s="5" t="n">
+      <c r="H110" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="I110" s="5" t="n">
+      <c r="I110" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="5" t="n">
+      <c r="J110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="4" t="n">
         <v>0.2376666666666667</v>
       </c>
-      <c r="L110" s="5" t="n">
+      <c r="L110" s="4" t="n">
         <v>0.02409933147989332</v>
       </c>
     </row>
@@ -7299,22 +7297,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E111" s="5" t="n"/>
-      <c r="F111" s="5" t="n"/>
-      <c r="G111" s="5" t="n">
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="H111" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I111" s="5" t="n">
+      <c r="H111" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="J111" s="5" t="n"/>
-      <c r="K111" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="5" t="n"/>
+      <c r="J111" s="4" t="n"/>
+      <c r="K111" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7337,20 +7335,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E112" s="5" t="n"/>
-      <c r="F112" s="5" t="n"/>
-      <c r="G112" s="5" t="n"/>
-      <c r="H112" s="5" t="n">
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="I112" s="5" t="n">
+      <c r="I112" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="J112" s="5" t="n"/>
-      <c r="K112" s="5" t="n">
+      <c r="J112" s="4" t="n"/>
+      <c r="K112" s="4" t="n">
         <v>0.7623333333333333</v>
       </c>
-      <c r="L112" s="5" t="n"/>
+      <c r="L112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7373,28 +7371,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E113" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="5" t="n">
+      <c r="E113" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G113" s="5" t="n">
+      <c r="G113" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H113" s="5" t="n">
+      <c r="H113" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="I113" s="5" t="n">
+      <c r="I113" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="J113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="5" t="n">
+      <c r="J113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="4" t="n">
         <v>0.331</v>
       </c>
-      <c r="L113" s="5" t="n">
+      <c r="L113" s="4" t="n">
         <v>0.01539480431834065</v>
       </c>
     </row>
@@ -7419,28 +7417,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E114" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="5" t="n">
+      <c r="E114" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G114" s="5" t="n">
+      <c r="G114" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H114" s="5" t="n">
+      <c r="H114" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I114" s="5" t="n">
+      <c r="I114" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="5" t="n">
+      <c r="J114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7465,22 +7463,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E115" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F115" s="5" t="n"/>
-      <c r="G115" s="5" t="n"/>
-      <c r="H115" s="5" t="n"/>
-      <c r="I115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="5" t="n">
+      <c r="E115" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7505,22 +7503,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E116" s="5" t="n">
+      <c r="E116" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F116" s="5" t="n"/>
-      <c r="G116" s="5" t="n"/>
-      <c r="H116" s="5" t="n"/>
-      <c r="I116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="5" t="n">
+      <c r="F116" s="4" t="n"/>
+      <c r="G116" s="4" t="n"/>
+      <c r="H116" s="4" t="n"/>
+      <c r="I116" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7545,28 +7543,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E117" s="5" t="n">
+      <c r="E117" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F117" s="5" t="n">
+      <c r="F117" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G117" s="5" t="n">
+      <c r="G117" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H117" s="5" t="n">
+      <c r="H117" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="I117" s="5" t="n">
+      <c r="I117" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="5" t="n">
+      <c r="J117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="4" t="n">
         <v>0.669</v>
       </c>
-      <c r="L117" s="5" t="n">
+      <c r="L117" s="4" t="n">
         <v>0.01539480431834063</v>
       </c>
     </row>
@@ -7591,22 +7589,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E118" s="5" t="n"/>
-      <c r="F118" s="5" t="n"/>
-      <c r="G118" s="5" t="n">
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="n"/>
+      <c r="G118" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="H118" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I118" s="5" t="n">
+      <c r="H118" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="J118" s="5" t="n"/>
-      <c r="K118" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="5" t="n"/>
+      <c r="J118" s="4" t="n"/>
+      <c r="K118" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7629,20 +7627,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E119" s="5" t="n"/>
-      <c r="F119" s="5" t="n"/>
-      <c r="G119" s="5" t="n"/>
-      <c r="H119" s="5" t="n">
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="4" t="n"/>
+      <c r="G119" s="4" t="n"/>
+      <c r="H119" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="I119" s="5" t="n">
+      <c r="I119" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="J119" s="5" t="n"/>
-      <c r="K119" s="5" t="n">
+      <c r="J119" s="4" t="n"/>
+      <c r="K119" s="4" t="n">
         <v>0.331</v>
       </c>
-      <c r="L119" s="5" t="n"/>
+      <c r="L119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7665,28 +7663,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E120" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="5" t="n">
+      <c r="E120" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G120" s="5" t="n">
+      <c r="G120" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H120" s="5" t="n">
+      <c r="H120" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="I120" s="5" t="n">
+      <c r="I120" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="J120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="5" t="n">
+      <c r="J120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="4" t="n">
         <v>0.6466666666666666</v>
       </c>
-      <c r="L120" s="5" t="n">
+      <c r="L120" s="4" t="n">
         <v>0.008212456663169955</v>
       </c>
     </row>
@@ -7711,28 +7709,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E121" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F121" s="5" t="n">
+      <c r="E121" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G121" s="5" t="n">
+      <c r="G121" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H121" s="5" t="n">
+      <c r="H121" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I121" s="5" t="n">
+      <c r="I121" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J121" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="5" t="n">
+      <c r="J121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7757,22 +7755,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E122" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F122" s="5" t="n"/>
-      <c r="G122" s="5" t="n"/>
-      <c r="H122" s="5" t="n"/>
-      <c r="I122" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="5" t="n">
+      <c r="E122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" s="4" t="n"/>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7797,22 +7795,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E123" s="5" t="n">
+      <c r="E123" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F123" s="5" t="n"/>
-      <c r="G123" s="5" t="n"/>
-      <c r="H123" s="5" t="n"/>
-      <c r="I123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="5" t="n">
+      <c r="F123" s="4" t="n"/>
+      <c r="G123" s="4" t="n"/>
+      <c r="H123" s="4" t="n"/>
+      <c r="I123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7837,28 +7835,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E124" s="5" t="n">
+      <c r="E124" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F124" s="5" t="n">
+      <c r="F124" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G124" s="5" t="n">
+      <c r="G124" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H124" s="5" t="n">
+      <c r="H124" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="I124" s="5" t="n">
+      <c r="I124" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="5" t="n">
+      <c r="J124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="4" t="n">
         <v>0.3533333333333333</v>
       </c>
-      <c r="L124" s="5" t="n">
+      <c r="L124" s="4" t="n">
         <v>0.008212456663169936</v>
       </c>
     </row>
@@ -7883,22 +7881,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E125" s="5" t="n"/>
-      <c r="F125" s="5" t="n"/>
-      <c r="G125" s="5" t="n">
+      <c r="E125" s="4" t="n"/>
+      <c r="F125" s="4" t="n"/>
+      <c r="G125" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="H125" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I125" s="5" t="n">
+      <c r="H125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="J125" s="5" t="n"/>
-      <c r="K125" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L125" s="5" t="n"/>
+      <c r="J125" s="4" t="n"/>
+      <c r="K125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7921,20 +7919,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E126" s="5" t="n"/>
-      <c r="F126" s="5" t="n"/>
-      <c r="G126" s="5" t="n"/>
-      <c r="H126" s="5" t="n">
+      <c r="E126" s="4" t="n"/>
+      <c r="F126" s="4" t="n"/>
+      <c r="G126" s="4" t="n"/>
+      <c r="H126" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="I126" s="5" t="n">
+      <c r="I126" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="J126" s="5" t="n"/>
-      <c r="K126" s="5" t="n">
+      <c r="J126" s="4" t="n"/>
+      <c r="K126" s="4" t="n">
         <v>0.6466666666666666</v>
       </c>
-      <c r="L126" s="5" t="n"/>
+      <c r="L126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7957,28 +7955,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E127" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F127" s="5" t="n">
+      <c r="E127" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G127" s="5" t="n">
+      <c r="G127" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H127" s="5" t="n">
+      <c r="H127" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="I127" s="5" t="n">
+      <c r="I127" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="J127" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" s="5" t="n">
+      <c r="J127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="4" t="n">
         <v>0.016</v>
       </c>
-      <c r="L127" s="5" t="n">
+      <c r="L127" s="4" t="n">
         <v>0.002</v>
       </c>
     </row>
@@ -8003,28 +8001,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E128" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F128" s="5" t="n">
+      <c r="E128" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G128" s="5" t="n">
+      <c r="G128" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H128" s="5" t="n">
+      <c r="H128" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I128" s="5" t="n">
+      <c r="I128" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="5" t="n">
+      <c r="J128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8049,22 +8047,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E129" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F129" s="5" t="n"/>
-      <c r="G129" s="5" t="n"/>
-      <c r="H129" s="5" t="n"/>
-      <c r="I129" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="5" t="n">
+      <c r="E129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="4" t="n"/>
+      <c r="G129" s="4" t="n"/>
+      <c r="H129" s="4" t="n"/>
+      <c r="I129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8089,22 +8087,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E130" s="5" t="n">
+      <c r="E130" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F130" s="5" t="n"/>
-      <c r="G130" s="5" t="n"/>
-      <c r="H130" s="5" t="n"/>
-      <c r="I130" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="5" t="n">
+      <c r="F130" s="4" t="n"/>
+      <c r="G130" s="4" t="n"/>
+      <c r="H130" s="4" t="n"/>
+      <c r="I130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8129,28 +8127,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E131" s="5" t="n">
+      <c r="E131" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F131" s="5" t="n">
+      <c r="F131" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G131" s="5" t="n">
+      <c r="G131" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H131" s="5" t="n">
+      <c r="H131" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="I131" s="5" t="n">
+      <c r="I131" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="5" t="n">
+      <c r="J131" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="4" t="n">
         <v>0.984</v>
       </c>
-      <c r="L131" s="5" t="n">
+      <c r="L131" s="4" t="n">
         <v>0.002000000000000002</v>
       </c>
     </row>
@@ -8175,22 +8173,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E132" s="5" t="n"/>
-      <c r="F132" s="5" t="n"/>
-      <c r="G132" s="5" t="n">
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="n"/>
+      <c r="G132" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="H132" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I132" s="5" t="n">
+      <c r="H132" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="J132" s="5" t="n"/>
-      <c r="K132" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" s="5" t="n"/>
+      <c r="J132" s="4" t="n"/>
+      <c r="K132" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8213,20 +8211,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E133" s="5" t="n"/>
-      <c r="F133" s="5" t="n"/>
-      <c r="G133" s="5" t="n"/>
-      <c r="H133" s="5" t="n">
+      <c r="E133" s="4" t="n"/>
+      <c r="F133" s="4" t="n"/>
+      <c r="G133" s="4" t="n"/>
+      <c r="H133" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="I133" s="5" t="n">
+      <c r="I133" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="J133" s="5" t="n"/>
-      <c r="K133" s="5" t="n">
+      <c r="J133" s="4" t="n"/>
+      <c r="K133" s="4" t="n">
         <v>0.016</v>
       </c>
-      <c r="L133" s="5" t="n"/>
+      <c r="L133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8249,28 +8247,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E134" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F134" s="5" t="n">
+      <c r="E134" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G134" s="5" t="n">
+      <c r="G134" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H134" s="5" t="n">
+      <c r="H134" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="I134" s="5" t="n">
+      <c r="I134" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="J134" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="5" t="n">
+      <c r="J134" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="4" t="n">
         <v>0.4796666666666667</v>
       </c>
-      <c r="L134" s="5" t="n">
+      <c r="L134" s="4" t="n">
         <v>0.02186575201339097</v>
       </c>
     </row>
@@ -8295,28 +8293,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E135" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F135" s="5" t="n">
+      <c r="E135" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G135" s="5" t="n">
+      <c r="G135" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H135" s="5" t="n">
+      <c r="H135" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I135" s="5" t="n">
+      <c r="I135" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J135" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="5" t="n">
+      <c r="J135" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8341,22 +8339,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E136" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F136" s="5" t="n"/>
-      <c r="G136" s="5" t="n"/>
-      <c r="H136" s="5" t="n"/>
-      <c r="I136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="5" t="n">
+      <c r="E136" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="n"/>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8381,22 +8379,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E137" s="5" t="n">
+      <c r="E137" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F137" s="5" t="n"/>
-      <c r="G137" s="5" t="n"/>
-      <c r="H137" s="5" t="n"/>
-      <c r="I137" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="5" t="n">
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8421,28 +8419,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E138" s="5" t="n">
+      <c r="E138" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F138" s="5" t="n">
+      <c r="F138" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G138" s="5" t="n">
+      <c r="G138" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H138" s="5" t="n">
+      <c r="H138" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="I138" s="5" t="n">
+      <c r="I138" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" s="5" t="n">
+      <c r="J138" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="4" t="n">
         <v>0.5203333333333333</v>
       </c>
-      <c r="L138" s="5" t="n">
+      <c r="L138" s="4" t="n">
         <v>0.02186575201339098</v>
       </c>
     </row>
@@ -8467,22 +8465,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E139" s="5" t="n"/>
-      <c r="F139" s="5" t="n"/>
-      <c r="G139" s="5" t="n">
+      <c r="E139" s="4" t="n"/>
+      <c r="F139" s="4" t="n"/>
+      <c r="G139" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="H139" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I139" s="5" t="n">
+      <c r="H139" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="J139" s="5" t="n"/>
-      <c r="K139" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L139" s="5" t="n"/>
+      <c r="J139" s="4" t="n"/>
+      <c r="K139" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8505,20 +8503,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E140" s="5" t="n"/>
-      <c r="F140" s="5" t="n"/>
-      <c r="G140" s="5" t="n"/>
-      <c r="H140" s="5" t="n">
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="4" t="n"/>
+      <c r="G140" s="4" t="n"/>
+      <c r="H140" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="I140" s="5" t="n">
+      <c r="I140" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="J140" s="5" t="n"/>
-      <c r="K140" s="5" t="n">
+      <c r="J140" s="4" t="n"/>
+      <c r="K140" s="4" t="n">
         <v>0.4796666666666667</v>
       </c>
-      <c r="L140" s="5" t="n"/>
+      <c r="L140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8541,28 +8539,28 @@
           <t>IRE+1</t>
         </is>
       </c>
-      <c r="E141" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F141" s="5" t="n">
+      <c r="E141" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="4" t="n">
         <v>0.7173171120424642</v>
       </c>
-      <c r="G141" s="5" t="n">
+      <c r="G141" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="H141" s="5" t="n">
+      <c r="H141" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="I141" s="5" t="n">
+      <c r="I141" s="4" t="n">
         <v>0.298</v>
       </c>
-      <c r="J141" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" s="5" t="n">
+      <c r="J141" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" s="4" t="n">
         <v>0.4716666666666667</v>
       </c>
-      <c r="L141" s="5" t="n">
+      <c r="L141" s="4" t="n">
         <v>0.007264831572567782</v>
       </c>
     </row>
@@ -8587,28 +8585,28 @@
           <t>IRE+2</t>
         </is>
       </c>
-      <c r="E142" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" s="5" t="n">
+      <c r="E142" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G142" s="5" t="n">
+      <c r="G142" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H142" s="5" t="n">
+      <c r="H142" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I142" s="5" t="n">
+      <c r="I142" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J142" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" s="5" t="n">
+      <c r="J142" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8633,22 +8631,22 @@
           <t>IRE+3</t>
         </is>
       </c>
-      <c r="E143" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F143" s="5" t="n"/>
-      <c r="G143" s="5" t="n"/>
-      <c r="H143" s="5" t="n"/>
-      <c r="I143" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="5" t="n">
+      <c r="E143" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8673,22 +8671,22 @@
           <t>IRE+a</t>
         </is>
       </c>
-      <c r="E144" s="5" t="n">
+      <c r="E144" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F144" s="5" t="n"/>
-      <c r="G144" s="5" t="n"/>
-      <c r="H144" s="5" t="n"/>
-      <c r="I144" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="5" t="n">
+      <c r="F144" s="4" t="n"/>
+      <c r="G144" s="4" t="n"/>
+      <c r="H144" s="4" t="n"/>
+      <c r="I144" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8713,28 +8711,28 @@
           <t>IRE01</t>
         </is>
       </c>
-      <c r="E145" s="5" t="n">
+      <c r="E145" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F145" s="5" t="n">
+      <c r="F145" s="4" t="n">
         <v>0.2113299042836991</v>
       </c>
-      <c r="G145" s="5" t="n">
+      <c r="G145" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="H145" s="5" t="n">
+      <c r="H145" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="I145" s="5" t="n">
+      <c r="I145" s="4" t="n">
         <v>0.6999999999999998</v>
       </c>
-      <c r="J145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" s="5" t="n">
+      <c r="J145" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="4" t="n">
         <v>0.5283333333333333</v>
       </c>
-      <c r="L145" s="5" t="n">
+      <c r="L145" s="4" t="n">
         <v>0.007264831572567796</v>
       </c>
     </row>
@@ -8759,22 +8757,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E146" s="5" t="n"/>
-      <c r="F146" s="5" t="n"/>
-      <c r="G146" s="5" t="n">
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="H146" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I146" s="5" t="n">
+      <c r="H146" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" s="4" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="J146" s="5" t="n"/>
-      <c r="K146" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" s="5" t="n"/>
+      <c r="J146" s="4" t="n"/>
+      <c r="K146" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -8797,20 +8795,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E147" s="5" t="n"/>
-      <c r="F147" s="5" t="n"/>
-      <c r="G147" s="5" t="n"/>
-      <c r="H147" s="5" t="n">
+      <c r="E147" s="4" t="n"/>
+      <c r="F147" s="4" t="n"/>
+      <c r="G147" s="4" t="n"/>
+      <c r="H147" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="I147" s="5" t="n">
+      <c r="I147" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="J147" s="5" t="n"/>
-      <c r="K147" s="5" t="n">
+      <c r="J147" s="4" t="n"/>
+      <c r="K147" s="4" t="n">
         <v>0.4716666666666667</v>
       </c>
-      <c r="L147" s="5" t="n"/>
+      <c r="L147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -8833,28 +8831,28 @@
           <t>FMM+1</t>
         </is>
       </c>
-      <c r="E148" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" s="5" t="n">
+      <c r="E148" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="4" t="n">
         <v>0.03101528962053397</v>
       </c>
-      <c r="G148" s="5" t="n">
+      <c r="G148" s="4" t="n">
         <v>0.949</v>
       </c>
-      <c r="H148" s="5" t="n">
+      <c r="H148" s="4" t="n">
         <v>0.949</v>
       </c>
-      <c r="I148" s="5" t="n">
+      <c r="I148" s="4" t="n">
         <v>0.949</v>
       </c>
-      <c r="J148" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" s="5" t="n">
+      <c r="J148" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" s="4" t="n">
         <v>0.5233333333333333</v>
       </c>
-      <c r="L148" s="5" t="n">
+      <c r="L148" s="4" t="n">
         <v>0.004371625682868005</v>
       </c>
     </row>
@@ -8879,22 +8877,22 @@
           <t>FMM+a</t>
         </is>
       </c>
-      <c r="E149" s="5" t="n">
+      <c r="E149" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F149" s="5" t="n"/>
-      <c r="G149" s="5" t="n"/>
-      <c r="H149" s="5" t="n"/>
-      <c r="I149" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" s="5" t="n">
+      <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="n"/>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8919,28 +8917,28 @@
           <t>FMM01</t>
         </is>
       </c>
-      <c r="E150" s="5" t="n">
+      <c r="E150" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F150" s="5" t="n">
+      <c r="F150" s="4" t="n">
         <v>1.763238315407753</v>
       </c>
-      <c r="G150" s="5" t="n">
+      <c r="G150" s="4" t="n">
         <v>0.05099999999999999</v>
       </c>
-      <c r="H150" s="5" t="n">
+      <c r="H150" s="4" t="n">
         <v>0.05099999999999999</v>
       </c>
-      <c r="I150" s="5" t="n">
+      <c r="I150" s="4" t="n">
         <v>0.051</v>
       </c>
-      <c r="J150" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" s="5" t="n">
+      <c r="J150" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" s="4" t="n">
         <v>0.4766666666666666</v>
       </c>
-      <c r="L150" s="5" t="n">
+      <c r="L150" s="4" t="n">
         <v>0.004371625682867987</v>
       </c>
     </row>
@@ -8965,22 +8963,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E151" s="5" t="n"/>
-      <c r="F151" s="5" t="n"/>
-      <c r="G151" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H151" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I151" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J151" s="5" t="n"/>
-      <c r="K151" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L151" s="5" t="n"/>
+      <c r="E151" s="4" t="n"/>
+      <c r="F151" s="4" t="n"/>
+      <c r="G151" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="4" t="n"/>
+      <c r="K151" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9003,20 +9001,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E152" s="5" t="n"/>
-      <c r="F152" s="5" t="n"/>
-      <c r="G152" s="5" t="n"/>
-      <c r="H152" s="5" t="n">
+      <c r="E152" s="4" t="n"/>
+      <c r="F152" s="4" t="n"/>
+      <c r="G152" s="4" t="n"/>
+      <c r="H152" s="4" t="n">
         <v>0.949</v>
       </c>
-      <c r="I152" s="5" t="n">
+      <c r="I152" s="4" t="n">
         <v>0.949</v>
       </c>
-      <c r="J152" s="5" t="n"/>
-      <c r="K152" s="5" t="n">
+      <c r="J152" s="4" t="n"/>
+      <c r="K152" s="4" t="n">
         <v>0.5233333333333333</v>
       </c>
-      <c r="L152" s="5" t="n"/>
+      <c r="L152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9039,28 +9037,28 @@
           <t>YY3+1</t>
         </is>
       </c>
-      <c r="E153" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F153" s="5" t="n">
+      <c r="E153" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="4" t="n">
         <v>0.01560880538871424</v>
       </c>
-      <c r="G153" s="5" t="n">
+      <c r="G153" s="4" t="n">
         <v>0.9739999999999999</v>
       </c>
-      <c r="H153" s="5" t="n">
+      <c r="H153" s="4" t="n">
         <v>0.974</v>
       </c>
-      <c r="I153" s="5" t="n">
+      <c r="I153" s="4" t="n">
         <v>0.9739999999999999</v>
       </c>
-      <c r="J153" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" s="5" t="n">
+      <c r="J153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" s="4" t="n">
         <v>0.984</v>
       </c>
-      <c r="L153" s="5" t="n">
+      <c r="L153" s="4" t="n">
         <v>0.001154700538379253</v>
       </c>
     </row>
@@ -9085,28 +9083,28 @@
           <t>YY3+2</t>
         </is>
       </c>
-      <c r="E154" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F154" s="5" t="n">
+      <c r="E154" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="4" t="n">
         <v>3.271465593833381</v>
       </c>
-      <c r="G154" s="5" t="n">
+      <c r="G154" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="H154" s="5" t="n">
+      <c r="H154" s="4" t="n">
         <v>0.004000000000000003</v>
       </c>
-      <c r="I154" s="5" t="n">
+      <c r="I154" s="4" t="n">
         <v>0.004</v>
       </c>
-      <c r="J154" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" s="5" t="n">
+      <c r="J154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" s="4" t="n">
         <v>0.002666666666666667</v>
       </c>
-      <c r="L154" s="5" t="n">
+      <c r="L154" s="4" t="n">
         <v>0.001333333333333334</v>
       </c>
     </row>
@@ -9131,28 +9129,28 @@
           <t>YY3+3</t>
         </is>
       </c>
-      <c r="E155" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F155" s="5" t="n">
+      <c r="E155" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" s="4" t="n">
         <v>4.092845002796916</v>
       </c>
-      <c r="G155" s="5" t="n">
+      <c r="G155" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="H155" s="5" t="n">
+      <c r="H155" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="I155" s="5" t="n">
+      <c r="I155" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="J155" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" s="5" t="n">
+      <c r="J155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" s="4" t="n">
         <v>0.002666666666666667</v>
       </c>
-      <c r="L155" s="5" t="n">
+      <c r="L155" s="4" t="n">
         <v>0.001333333333333334</v>
       </c>
     </row>
@@ -9177,22 +9175,22 @@
           <t>YY3+4</t>
         </is>
       </c>
-      <c r="E156" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F156" s="5" t="n"/>
-      <c r="G156" s="5" t="n"/>
-      <c r="H156" s="5" t="n"/>
-      <c r="I156" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" s="5" t="n">
+      <c r="E156" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" s="4" t="n"/>
+      <c r="G156" s="4" t="n"/>
+      <c r="H156" s="4" t="n"/>
+      <c r="I156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="L156" s="5" t="n">
+      <c r="L156" s="4" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -9217,22 +9215,22 @@
           <t>YY3+a</t>
         </is>
       </c>
-      <c r="E157" s="5" t="n">
+      <c r="E157" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F157" s="5" t="n"/>
-      <c r="G157" s="5" t="n"/>
-      <c r="H157" s="5" t="n"/>
-      <c r="I157" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" s="5" t="n">
+      <c r="F157" s="4" t="n"/>
+      <c r="G157" s="4" t="n"/>
+      <c r="H157" s="4" t="n"/>
+      <c r="I157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9257,22 +9255,22 @@
           <t>YY3+b</t>
         </is>
       </c>
-      <c r="E158" s="5" t="n">
+      <c r="E158" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F158" s="5" t="n"/>
-      <c r="G158" s="5" t="n"/>
-      <c r="H158" s="5" t="n"/>
-      <c r="I158" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" s="5" t="n">
+      <c r="F158" s="4" t="n"/>
+      <c r="G158" s="4" t="n"/>
+      <c r="H158" s="4" t="n"/>
+      <c r="I158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9297,28 +9295,28 @@
           <t>YY301</t>
         </is>
       </c>
-      <c r="E159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" s="5" t="n">
+      <c r="E159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="4" t="n">
         <v>2.288965458445788</v>
       </c>
-      <c r="G159" s="5" t="n">
+      <c r="G159" s="4" t="n">
         <v>0.021</v>
       </c>
-      <c r="H159" s="5" t="n">
+      <c r="H159" s="4" t="n">
         <v>0.02100000000000001</v>
       </c>
-      <c r="I159" s="5" t="n">
+      <c r="I159" s="4" t="n">
         <v>0.021</v>
       </c>
-      <c r="J159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" s="5" t="n">
+      <c r="J159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" s="4" t="n">
         <v>0.009666666666666665</v>
       </c>
-      <c r="L159" s="5" t="n">
+      <c r="L159" s="4" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -9343,22 +9341,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E160" s="5" t="n"/>
-      <c r="F160" s="5" t="n"/>
-      <c r="G160" s="5" t="n">
+      <c r="E160" s="4" t="n"/>
+      <c r="F160" s="4" t="n"/>
+      <c r="G160" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="H160" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I160" s="5" t="n">
+      <c r="H160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="J160" s="5" t="n"/>
-      <c r="K160" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L160" s="5" t="n"/>
+      <c r="J160" s="4" t="n"/>
+      <c r="K160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -9381,20 +9379,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E161" s="5" t="n"/>
-      <c r="F161" s="5" t="n"/>
-      <c r="G161" s="5" t="n"/>
-      <c r="H161" s="5" t="n">
+      <c r="E161" s="4" t="n"/>
+      <c r="F161" s="4" t="n"/>
+      <c r="G161" s="4" t="n"/>
+      <c r="H161" s="4" t="n">
         <v>0.979</v>
       </c>
-      <c r="I161" s="5" t="n">
+      <c r="I161" s="4" t="n">
         <v>0.9789999999999999</v>
       </c>
-      <c r="J161" s="5" t="n"/>
-      <c r="K161" s="5" t="n">
+      <c r="J161" s="4" t="n"/>
+      <c r="K161" s="4" t="n">
         <v>0.9903333333333334</v>
       </c>
-      <c r="L161" s="5" t="n"/>
+      <c r="L161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9417,28 +9415,28 @@
           <t>MI1+1</t>
         </is>
       </c>
-      <c r="E162" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F162" s="5" t="n">
+      <c r="E162" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" s="4" t="n">
         <v>2.097722223529931</v>
       </c>
-      <c r="G162" s="5" t="n">
+      <c r="G162" s="4" t="n">
         <v>0.02899999999999998</v>
       </c>
-      <c r="H162" s="5" t="n">
+      <c r="H162" s="4" t="n">
         <v>0.02899999999999998</v>
       </c>
-      <c r="I162" s="5" t="n">
+      <c r="I162" s="4" t="n">
         <v>0.029</v>
       </c>
-      <c r="J162" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K162" s="5" t="n">
+      <c r="J162" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" s="4" t="n">
         <v>0.04866666666666667</v>
       </c>
-      <c r="L162" s="5" t="n">
+      <c r="L162" s="4" t="n">
         <v>0.01026861453383291</v>
       </c>
     </row>
@@ -9463,28 +9461,28 @@
           <t>MI101</t>
         </is>
       </c>
-      <c r="E163" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F163" s="5" t="n">
+      <c r="E163" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="4" t="n">
         <v>0.01743657033430621</v>
       </c>
-      <c r="G163" s="5" t="n">
+      <c r="G163" s="4" t="n">
         <v>0.971</v>
       </c>
-      <c r="H163" s="5" t="n">
+      <c r="H163" s="4" t="n">
         <v>0.971</v>
       </c>
-      <c r="I163" s="5" t="n">
+      <c r="I163" s="4" t="n">
         <v>0.971</v>
       </c>
-      <c r="J163" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" s="5" t="n">
+      <c r="J163" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" s="4" t="n">
         <v>0.9513333333333334</v>
       </c>
-      <c r="L163" s="5" t="n">
+      <c r="L163" s="4" t="n">
         <v>0.01026861453383288</v>
       </c>
     </row>
@@ -9509,22 +9507,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E164" s="5" t="n"/>
-      <c r="F164" s="5" t="n"/>
-      <c r="G164" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H164" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I164" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J164" s="5" t="n"/>
-      <c r="K164" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L164" s="5" t="n"/>
+      <c r="E164" s="4" t="n"/>
+      <c r="F164" s="4" t="n"/>
+      <c r="G164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="4" t="n"/>
+      <c r="K164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -9547,20 +9545,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E165" s="5" t="n"/>
-      <c r="F165" s="5" t="n"/>
-      <c r="G165" s="5" t="n"/>
-      <c r="H165" s="5" t="n">
+      <c r="E165" s="4" t="n"/>
+      <c r="F165" s="4" t="n"/>
+      <c r="G165" s="4" t="n"/>
+      <c r="H165" s="4" t="n">
         <v>0.02899999999999998</v>
       </c>
-      <c r="I165" s="5" t="n">
+      <c r="I165" s="4" t="n">
         <v>0.029</v>
       </c>
-      <c r="J165" s="5" t="n"/>
-      <c r="K165" s="5" t="n">
+      <c r="J165" s="4" t="n"/>
+      <c r="K165" s="4" t="n">
         <v>0.04866666666666667</v>
       </c>
-      <c r="L165" s="5" t="n"/>
+      <c r="L165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -9583,28 +9581,28 @@
           <t>EUI+1</t>
         </is>
       </c>
-      <c r="E166" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F166" s="5" t="n">
+      <c r="E166" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="4" t="n">
         <v>0.00835361269485466</v>
       </c>
-      <c r="G166" s="5" t="n">
+      <c r="G166" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="H166" s="5" t="n">
+      <c r="H166" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="I166" s="5" t="n">
+      <c r="I166" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="J166" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" s="5" t="n">
+      <c r="J166" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" s="4" t="n">
         <v>0.2446666666666667</v>
       </c>
-      <c r="L166" s="5" t="n">
+      <c r="L166" s="4" t="n">
         <v>0.02248209163855633</v>
       </c>
     </row>
@@ -9629,28 +9627,28 @@
           <t>EUI01</t>
         </is>
       </c>
-      <c r="E167" s="5" t="n">
+      <c r="E167" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F167" s="5" t="n">
+      <c r="F167" s="4" t="n">
         <v>2.529203534999876</v>
       </c>
-      <c r="G167" s="5" t="n">
+      <c r="G167" s="4" t="n">
         <v>0.01399999999999999</v>
       </c>
-      <c r="H167" s="5" t="n">
+      <c r="H167" s="4" t="n">
         <v>0.01399999999999999</v>
       </c>
-      <c r="I167" s="5" t="n">
+      <c r="I167" s="4" t="n">
         <v>0.014</v>
       </c>
-      <c r="J167" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" s="5" t="n">
+      <c r="J167" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" s="4" t="n">
         <v>0.7543333333333333</v>
       </c>
-      <c r="L167" s="5" t="n">
+      <c r="L167" s="4" t="n">
         <v>0.02292984469589314</v>
       </c>
     </row>
@@ -9675,22 +9673,22 @@
           <t>EUI02</t>
         </is>
       </c>
-      <c r="E168" s="5" t="n">
+      <c r="E168" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F168" s="5" t="n"/>
-      <c r="G168" s="5" t="n"/>
-      <c r="H168" s="5" t="n"/>
-      <c r="I168" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" s="5" t="n">
+      <c r="F168" s="4" t="n"/>
+      <c r="G168" s="4" t="n"/>
+      <c r="H168" s="4" t="n"/>
+      <c r="I168" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="L168" s="5" t="n">
+      <c r="L168" s="4" t="n">
         <v>0.0005773502691896258</v>
       </c>
     </row>
@@ -9715,22 +9713,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E169" s="5" t="n"/>
-      <c r="F169" s="5" t="n"/>
-      <c r="G169" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H169" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I169" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J169" s="5" t="n"/>
-      <c r="K169" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L169" s="5" t="n"/>
+      <c r="E169" s="4" t="n"/>
+      <c r="F169" s="4" t="n"/>
+      <c r="G169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" s="4" t="n"/>
+      <c r="K169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -9753,20 +9751,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E170" s="5" t="n"/>
-      <c r="F170" s="5" t="n"/>
-      <c r="G170" s="5" t="n"/>
-      <c r="H170" s="5" t="n">
+      <c r="E170" s="4" t="n"/>
+      <c r="F170" s="4" t="n"/>
+      <c r="G170" s="4" t="n"/>
+      <c r="H170" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="I170" s="5" t="n">
+      <c r="I170" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="J170" s="5" t="n"/>
-      <c r="K170" s="5" t="n">
+      <c r="J170" s="4" t="n"/>
+      <c r="K170" s="4" t="n">
         <v>0.2446666666666667</v>
       </c>
-      <c r="L170" s="5" t="n"/>
+      <c r="L170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -9789,28 +9787,28 @@
           <t>EUI+1</t>
         </is>
       </c>
-      <c r="E171" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" s="5" t="n">
+      <c r="E171" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="4" t="n">
         <v>0.00835361269485466</v>
       </c>
-      <c r="G171" s="5" t="n">
+      <c r="G171" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="H171" s="5" t="n">
+      <c r="H171" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="I171" s="5" t="n">
+      <c r="I171" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="J171" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" s="5" t="n">
+      <c r="J171" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" s="4" t="n">
         <v>0.5206666666666667</v>
       </c>
-      <c r="L171" s="5" t="n">
+      <c r="L171" s="4" t="n">
         <v>0.01089852181618122</v>
       </c>
     </row>
@@ -9835,28 +9833,28 @@
           <t>EUI01</t>
         </is>
       </c>
-      <c r="E172" s="5" t="n">
+      <c r="E172" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F172" s="5" t="n">
+      <c r="F172" s="4" t="n">
         <v>2.529203534999876</v>
       </c>
-      <c r="G172" s="5" t="n">
+      <c r="G172" s="4" t="n">
         <v>0.01399999999999999</v>
       </c>
-      <c r="H172" s="5" t="n">
+      <c r="H172" s="4" t="n">
         <v>0.01399999999999999</v>
       </c>
-      <c r="I172" s="5" t="n">
+      <c r="I172" s="4" t="n">
         <v>0.014</v>
       </c>
-      <c r="J172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K172" s="5" t="n">
+      <c r="J172" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" s="4" t="n">
         <v>0.4793333333333333</v>
       </c>
-      <c r="L172" s="5" t="n">
+      <c r="L172" s="4" t="n">
         <v>0.01089852181618121</v>
       </c>
     </row>
@@ -9881,22 +9879,22 @@
           <t>EUI02</t>
         </is>
       </c>
-      <c r="E173" s="5" t="n">
+      <c r="E173" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F173" s="5" t="n"/>
-      <c r="G173" s="5" t="n"/>
-      <c r="H173" s="5" t="n"/>
-      <c r="I173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K173" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" s="5" t="n">
+      <c r="F173" s="4" t="n"/>
+      <c r="G173" s="4" t="n"/>
+      <c r="H173" s="4" t="n"/>
+      <c r="I173" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9921,22 +9919,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E174" s="5" t="n"/>
-      <c r="F174" s="5" t="n"/>
-      <c r="G174" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H174" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I174" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J174" s="5" t="n"/>
-      <c r="K174" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L174" s="5" t="n"/>
+      <c r="E174" s="4" t="n"/>
+      <c r="F174" s="4" t="n"/>
+      <c r="G174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" s="4" t="n"/>
+      <c r="K174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -9959,20 +9957,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E175" s="5" t="n"/>
-      <c r="F175" s="5" t="n"/>
-      <c r="G175" s="5" t="n"/>
-      <c r="H175" s="5" t="n">
+      <c r="E175" s="4" t="n"/>
+      <c r="F175" s="4" t="n"/>
+      <c r="G175" s="4" t="n"/>
+      <c r="H175" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="I175" s="5" t="n">
+      <c r="I175" s="4" t="n">
         <v>0.9860000000000001</v>
       </c>
-      <c r="J175" s="5" t="n"/>
-      <c r="K175" s="5" t="n">
+      <c r="J175" s="4" t="n"/>
+      <c r="K175" s="4" t="n">
         <v>0.5206666666666667</v>
       </c>
-      <c r="L175" s="5" t="n"/>
+      <c r="L175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -9995,28 +9993,28 @@
           <t>VGH+1</t>
         </is>
       </c>
-      <c r="E176" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F176" s="5" t="n">
+      <c r="E176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="4" t="n">
         <v>0.5764201918923106</v>
       </c>
-      <c r="G176" s="5" t="n">
+      <c r="G176" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="H176" s="5" t="n">
+      <c r="H176" s="4" t="n">
         <v>0.378</v>
       </c>
-      <c r="I176" s="5" t="n">
+      <c r="I176" s="4" t="n">
         <v>0.3779999999999999</v>
       </c>
-      <c r="J176" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K176" s="5" t="n">
+      <c r="J176" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" s="4" t="n">
         <v>0.971</v>
       </c>
-      <c r="L176" s="5" t="n">
+      <c r="L176" s="4" t="n">
         <v>0.004000000000000004</v>
       </c>
     </row>
@@ -10041,28 +10039,28 @@
           <t>VGH+2</t>
         </is>
       </c>
-      <c r="E177" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F177" s="5" t="n">
+      <c r="E177" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G177" s="5" t="n">
+      <c r="G177" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H177" s="5" t="n">
+      <c r="H177" s="4" t="n">
         <v>0.002000000000000001</v>
       </c>
-      <c r="I177" s="5" t="n">
+      <c r="I177" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J177" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K177" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L177" s="5" t="n">
+      <c r="J177" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10087,28 +10085,28 @@
           <t>VGH+a</t>
         </is>
       </c>
-      <c r="E178" s="5" t="n">
+      <c r="E178" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F178" s="5" t="n">
+      <c r="F178" s="4" t="n">
         <v>0.2880338091215544</v>
       </c>
-      <c r="G178" s="5" t="n">
+      <c r="G178" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="H178" s="5" t="n">
+      <c r="H178" s="4" t="n">
         <v>0.6150000000000001</v>
       </c>
-      <c r="I178" s="5" t="n">
+      <c r="I178" s="4" t="n">
         <v>0.615</v>
       </c>
-      <c r="J178" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L178" s="5" t="n">
+      <c r="J178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10133,28 +10131,28 @@
           <t>VGH01</t>
         </is>
       </c>
-      <c r="E179" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" s="5" t="n">
+      <c r="E179" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" s="4" t="n">
         <v>3.139253039679712</v>
       </c>
-      <c r="G179" s="5" t="n">
+      <c r="G179" s="4" t="n">
         <v>0.005000000000000002</v>
       </c>
-      <c r="H179" s="5" t="n">
+      <c r="H179" s="4" t="n">
         <v>0.005000000000000003</v>
       </c>
-      <c r="I179" s="5" t="n">
+      <c r="I179" s="4" t="n">
         <v>0.005</v>
       </c>
-      <c r="J179" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K179" s="5" t="n">
+      <c r="J179" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" s="4" t="n">
         <v>0.029</v>
       </c>
-      <c r="L179" s="5" t="n">
+      <c r="L179" s="4" t="n">
         <v>0.004</v>
       </c>
     </row>
@@ -10179,22 +10177,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E180" s="5" t="n"/>
-      <c r="F180" s="5" t="n"/>
-      <c r="G180" s="5" t="n">
+      <c r="E180" s="4" t="n"/>
+      <c r="F180" s="4" t="n"/>
+      <c r="G180" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="H180" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I180" s="5" t="n">
+      <c r="H180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I180" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="J180" s="5" t="n"/>
-      <c r="K180" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L180" s="5" t="n"/>
+      <c r="J180" s="4" t="n"/>
+      <c r="K180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -10217,20 +10215,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E181" s="5" t="n"/>
-      <c r="F181" s="5" t="n"/>
-      <c r="G181" s="5" t="n"/>
-      <c r="H181" s="5" t="n">
+      <c r="E181" s="4" t="n"/>
+      <c r="F181" s="4" t="n"/>
+      <c r="G181" s="4" t="n"/>
+      <c r="H181" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="I181" s="5" t="n">
+      <c r="I181" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="J181" s="5" t="n"/>
-      <c r="K181" s="5" t="n">
+      <c r="J181" s="4" t="n"/>
+      <c r="K181" s="4" t="n">
         <v>0.971</v>
       </c>
-      <c r="L181" s="5" t="n"/>
+      <c r="L181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10253,28 +10251,28 @@
           <t>AXI+1</t>
         </is>
       </c>
-      <c r="E182" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" s="5" t="n">
+      <c r="E182" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="4" t="n">
         <v>3.441917221761061</v>
       </c>
-      <c r="G182" s="5" t="n">
+      <c r="G182" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="H182" s="5" t="n">
+      <c r="H182" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="I182" s="5" t="n">
+      <c r="I182" s="4" t="n">
         <v>0.003</v>
       </c>
-      <c r="J182" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" s="5" t="n">
+      <c r="J182" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10299,28 +10297,28 @@
           <t>AXI01</t>
         </is>
       </c>
-      <c r="E183" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F183" s="5" t="n">
+      <c r="E183" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="4" t="n">
         <v>0.1248522110545241</v>
       </c>
-      <c r="G183" s="5" t="n">
+      <c r="G183" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H183" s="5" t="n">
+      <c r="H183" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="I183" s="5" t="n">
+      <c r="I183" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J183" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" s="5" t="n">
+      <c r="J183" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" s="4" t="n">
         <v>0.9603333333333333</v>
       </c>
-      <c r="L183" s="5" t="n">
+      <c r="L183" s="4" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -10345,28 +10343,28 @@
           <t>AXI02</t>
         </is>
       </c>
-      <c r="E184" s="5" t="n">
+      <c r="E184" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F184" s="5" t="n">
+      <c r="F184" s="4" t="n">
         <v>0.9934131473105738</v>
       </c>
-      <c r="G184" s="5" t="n">
+      <c r="G184" s="4" t="n">
         <v>0.187</v>
       </c>
-      <c r="H184" s="5" t="n">
+      <c r="H184" s="4" t="n">
         <v>0.187</v>
       </c>
-      <c r="I184" s="5" t="n">
+      <c r="I184" s="4" t="n">
         <v>0.187</v>
       </c>
-      <c r="J184" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K184" s="5" t="n">
+      <c r="J184" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" s="4" t="n">
         <v>0.03966666666666666</v>
       </c>
-      <c r="L184" s="5" t="n">
+      <c r="L184" s="4" t="n">
         <v>0.0003333333333333337</v>
       </c>
     </row>
@@ -10391,22 +10389,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E185" s="5" t="n"/>
-      <c r="F185" s="5" t="n"/>
-      <c r="G185" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H185" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I185" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J185" s="5" t="n"/>
-      <c r="K185" s="5" t="n">
+      <c r="E185" s="4" t="n"/>
+      <c r="F185" s="4" t="n"/>
+      <c r="G185" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" s="4" t="n"/>
+      <c r="K185" s="4" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="L185" s="5" t="n"/>
+      <c r="L185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -10429,20 +10427,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E186" s="5" t="n"/>
-      <c r="F186" s="5" t="n"/>
-      <c r="G186" s="5" t="n"/>
-      <c r="H186" s="5" t="n">
+      <c r="E186" s="4" t="n"/>
+      <c r="F186" s="4" t="n"/>
+      <c r="G186" s="4" t="n"/>
+      <c r="H186" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="I186" s="5" t="n">
+      <c r="I186" s="4" t="n">
         <v>0.003</v>
       </c>
-      <c r="J186" s="5" t="n"/>
-      <c r="K186" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L186" s="5" t="n"/>
+      <c r="J186" s="4" t="n"/>
+      <c r="K186" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -10465,28 +10463,28 @@
           <t>AXI+1</t>
         </is>
       </c>
-      <c r="E187" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F187" s="5" t="n">
+      <c r="E187" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" s="4" t="n">
         <v>3.441917221761061</v>
       </c>
-      <c r="G187" s="5" t="n">
+      <c r="G187" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="H187" s="5" t="n">
+      <c r="H187" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="I187" s="5" t="n">
+      <c r="I187" s="4" t="n">
         <v>0.003</v>
       </c>
-      <c r="J187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L187" s="5" t="n">
+      <c r="J187" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10511,28 +10509,28 @@
           <t>AXI01</t>
         </is>
       </c>
-      <c r="E188" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" s="5" t="n">
+      <c r="E188" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="4" t="n">
         <v>0.1248522110545241</v>
       </c>
-      <c r="G188" s="5" t="n">
+      <c r="G188" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H188" s="5" t="n">
+      <c r="H188" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="I188" s="5" t="n">
+      <c r="I188" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J188" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" s="5" t="n">
+      <c r="J188" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" s="4" t="n">
         <v>0.988</v>
       </c>
-      <c r="L188" s="5" t="n">
+      <c r="L188" s="4" t="n">
         <v>0.0005773502691896263</v>
       </c>
     </row>
@@ -10557,28 +10555,28 @@
           <t>AXI02</t>
         </is>
       </c>
-      <c r="E189" s="5" t="n">
+      <c r="E189" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F189" s="5" t="n">
+      <c r="F189" s="4" t="n">
         <v>0.9934131473105738</v>
       </c>
-      <c r="G189" s="5" t="n">
+      <c r="G189" s="4" t="n">
         <v>0.187</v>
       </c>
-      <c r="H189" s="5" t="n">
+      <c r="H189" s="4" t="n">
         <v>0.187</v>
       </c>
-      <c r="I189" s="5" t="n">
+      <c r="I189" s="4" t="n">
         <v>0.187</v>
       </c>
-      <c r="J189" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" s="5" t="n">
+      <c r="J189" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" s="4" t="n">
         <v>0.012</v>
       </c>
-      <c r="L189" s="5" t="n">
+      <c r="L189" s="4" t="n">
         <v>0.0005773502691896258</v>
       </c>
     </row>
@@ -10603,22 +10601,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E190" s="5" t="n"/>
-      <c r="F190" s="5" t="n"/>
-      <c r="G190" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H190" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I190" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J190" s="5" t="n"/>
-      <c r="K190" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L190" s="5" t="n"/>
+      <c r="E190" s="4" t="n"/>
+      <c r="F190" s="4" t="n"/>
+      <c r="G190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" s="4" t="n"/>
+      <c r="K190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -10641,20 +10639,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E191" s="5" t="n"/>
-      <c r="F191" s="5" t="n"/>
-      <c r="G191" s="5" t="n"/>
-      <c r="H191" s="5" t="n">
+      <c r="E191" s="4" t="n"/>
+      <c r="F191" s="4" t="n"/>
+      <c r="G191" s="4" t="n"/>
+      <c r="H191" s="4" t="n">
         <v>0.003000000000000002</v>
       </c>
-      <c r="I191" s="5" t="n">
+      <c r="I191" s="4" t="n">
         <v>0.003</v>
       </c>
-      <c r="J191" s="5" t="n"/>
-      <c r="K191" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" s="5" t="n"/>
+      <c r="J191" s="4" t="n"/>
+      <c r="K191" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -10677,22 +10675,22 @@
           <t>LEV-1</t>
         </is>
       </c>
-      <c r="E192" s="5" t="n">
+      <c r="E192" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="F192" s="5" t="n"/>
-      <c r="G192" s="5" t="n"/>
-      <c r="H192" s="5" t="n"/>
-      <c r="I192" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J192" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K192" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" s="5" t="n">
+      <c r="F192" s="4" t="n"/>
+      <c r="G192" s="4" t="n"/>
+      <c r="H192" s="4" t="n"/>
+      <c r="I192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10717,22 +10715,22 @@
           <t>LEV-2</t>
         </is>
       </c>
-      <c r="E193" s="5" t="n">
+      <c r="E193" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="F193" s="5" t="n"/>
-      <c r="G193" s="5" t="n"/>
-      <c r="H193" s="5" t="n"/>
-      <c r="I193" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" s="5" t="n">
+      <c r="F193" s="4" t="n"/>
+      <c r="G193" s="4" t="n"/>
+      <c r="H193" s="4" t="n"/>
+      <c r="I193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10757,28 +10755,28 @@
           <t>LEV01</t>
         </is>
       </c>
-      <c r="E194" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F194" s="5" t="n">
+      <c r="E194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="G194" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H194" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I194" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J194" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L194" s="5" t="n">
+      <c r="G194" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L194" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10803,22 +10801,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E195" s="5" t="n"/>
-      <c r="F195" s="5" t="n"/>
-      <c r="G195" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H195" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I195" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J195" s="5" t="n"/>
-      <c r="K195" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L195" s="5" t="n"/>
+      <c r="E195" s="4" t="n"/>
+      <c r="F195" s="4" t="n"/>
+      <c r="G195" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I195" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J195" s="4" t="n"/>
+      <c r="K195" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -10841,20 +10839,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E196" s="5" t="n"/>
-      <c r="F196" s="5" t="n"/>
-      <c r="G196" s="5" t="n"/>
-      <c r="H196" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I196" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" s="5" t="n"/>
-      <c r="K196" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" s="5" t="n"/>
+      <c r="E196" s="4" t="n"/>
+      <c r="F196" s="4" t="n"/>
+      <c r="G196" s="4" t="n"/>
+      <c r="H196" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="4" t="n"/>
+      <c r="K196" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -10877,28 +10875,28 @@
           <t>BAX+1</t>
         </is>
       </c>
-      <c r="E197" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" s="5" t="n">
+      <c r="E197" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="4" t="n">
         <v>3.271465593833381</v>
       </c>
-      <c r="G197" s="5" t="n">
+      <c r="G197" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="H197" s="5" t="n">
+      <c r="H197" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="I197" s="5" t="n">
+      <c r="I197" s="4" t="n">
         <v>0.004</v>
       </c>
-      <c r="J197" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L197" s="5" t="n">
+      <c r="J197" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10923,22 +10921,22 @@
           <t>BAX-1</t>
         </is>
       </c>
-      <c r="E198" s="5" t="n">
+      <c r="E198" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="F198" s="5" t="n"/>
-      <c r="G198" s="5" t="n"/>
-      <c r="H198" s="5" t="n"/>
-      <c r="I198" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L198" s="5" t="n">
+      <c r="F198" s="4" t="n"/>
+      <c r="G198" s="4" t="n"/>
+      <c r="H198" s="4" t="n"/>
+      <c r="I198" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10963,28 +10961,28 @@
           <t>BAX01</t>
         </is>
       </c>
-      <c r="E199" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F199" s="5" t="n">
+      <c r="E199" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="4" t="n">
         <v>0.003565707852896025</v>
       </c>
-      <c r="G199" s="5" t="n">
+      <c r="G199" s="4" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="H199" s="5" t="n">
+      <c r="H199" s="4" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="I199" s="5" t="n">
+      <c r="I199" s="4" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="J199" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L199" s="5" t="n">
+      <c r="J199" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L199" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11009,28 +11007,28 @@
           <t>BAX02</t>
         </is>
       </c>
-      <c r="E200" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F200" s="5" t="n">
+      <c r="E200" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G200" s="5" t="n">
+      <c r="G200" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H200" s="5" t="n">
+      <c r="H200" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="I200" s="5" t="n">
+      <c r="I200" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J200" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L200" s="5" t="n">
+      <c r="J200" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11055,22 +11053,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E201" s="5" t="n"/>
-      <c r="F201" s="5" t="n"/>
-      <c r="G201" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H201" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I201" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J201" s="5" t="n"/>
-      <c r="K201" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L201" s="5" t="n"/>
+      <c r="E201" s="4" t="n"/>
+      <c r="F201" s="4" t="n"/>
+      <c r="G201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J201" s="4" t="n"/>
+      <c r="K201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -11093,20 +11091,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E202" s="5" t="n"/>
-      <c r="F202" s="5" t="n"/>
-      <c r="G202" s="5" t="n"/>
-      <c r="H202" s="5" t="n">
+      <c r="E202" s="4" t="n"/>
+      <c r="F202" s="4" t="n"/>
+      <c r="G202" s="4" t="n"/>
+      <c r="H202" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="I202" s="5" t="n">
+      <c r="I202" s="4" t="n">
         <v>0.004</v>
       </c>
-      <c r="J202" s="5" t="n"/>
-      <c r="K202" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L202" s="5" t="n"/>
+      <c r="J202" s="4" t="n"/>
+      <c r="K202" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -11129,28 +11127,28 @@
           <t>BAX+1</t>
         </is>
       </c>
-      <c r="E203" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F203" s="5" t="n">
+      <c r="E203" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="4" t="n">
         <v>3.271465593833381</v>
       </c>
-      <c r="G203" s="5" t="n">
+      <c r="G203" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="H203" s="5" t="n">
+      <c r="H203" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="I203" s="5" t="n">
+      <c r="I203" s="4" t="n">
         <v>0.004</v>
       </c>
-      <c r="J203" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K203" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L203" s="5" t="n">
+      <c r="J203" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11175,22 +11173,22 @@
           <t>BAX-1</t>
         </is>
       </c>
-      <c r="E204" s="5" t="n">
+      <c r="E204" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="F204" s="5" t="n"/>
-      <c r="G204" s="5" t="n"/>
-      <c r="H204" s="5" t="n"/>
-      <c r="I204" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K204" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L204" s="5" t="n">
+      <c r="F204" s="4" t="n"/>
+      <c r="G204" s="4" t="n"/>
+      <c r="H204" s="4" t="n"/>
+      <c r="I204" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11215,28 +11213,28 @@
           <t>BAX01</t>
         </is>
       </c>
-      <c r="E205" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F205" s="5" t="n">
+      <c r="E205" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="4" t="n">
         <v>0.003565707852896025</v>
       </c>
-      <c r="G205" s="5" t="n">
+      <c r="G205" s="4" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="H205" s="5" t="n">
+      <c r="H205" s="4" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="I205" s="5" t="n">
+      <c r="I205" s="4" t="n">
         <v>0.9940000000000001</v>
       </c>
-      <c r="J205" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K205" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L205" s="5" t="n">
+      <c r="J205" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L205" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11261,28 +11259,28 @@
           <t>BAX02</t>
         </is>
       </c>
-      <c r="E206" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F206" s="5" t="n">
+      <c r="E206" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" s="4" t="n">
         <v>3.682155298315148</v>
       </c>
-      <c r="G206" s="5" t="n">
+      <c r="G206" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="H206" s="5" t="n">
+      <c r="H206" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="I206" s="5" t="n">
+      <c r="I206" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="J206" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K206" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L206" s="5" t="n">
+      <c r="J206" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11307,22 +11305,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E207" s="5" t="n"/>
-      <c r="F207" s="5" t="n"/>
-      <c r="G207" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H207" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I207" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J207" s="5" t="n"/>
-      <c r="K207" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L207" s="5" t="n"/>
+      <c r="E207" s="4" t="n"/>
+      <c r="F207" s="4" t="n"/>
+      <c r="G207" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I207" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J207" s="4" t="n"/>
+      <c r="K207" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -11345,20 +11343,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E208" s="5" t="n"/>
-      <c r="F208" s="5" t="n"/>
-      <c r="G208" s="5" t="n"/>
-      <c r="H208" s="5" t="n">
+      <c r="E208" s="4" t="n"/>
+      <c r="F208" s="4" t="n"/>
+      <c r="G208" s="4" t="n"/>
+      <c r="H208" s="4" t="n">
         <v>0.004000000000000002</v>
       </c>
-      <c r="I208" s="5" t="n">
+      <c r="I208" s="4" t="n">
         <v>0.004</v>
       </c>
-      <c r="J208" s="5" t="n"/>
-      <c r="K208" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" s="5" t="n"/>
+      <c r="J208" s="4" t="n"/>
+      <c r="K208" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -11381,28 +11379,28 @@
           <t>B49+1</t>
         </is>
       </c>
-      <c r="E209" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F209" s="5" t="n">
+      <c r="E209" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" s="4" t="n">
         <v>0.007753004432578372</v>
       </c>
-      <c r="G209" s="5" t="n">
+      <c r="G209" s="4" t="n">
         <v>0.987</v>
       </c>
-      <c r="H209" s="5" t="n">
+      <c r="H209" s="4" t="n">
         <v>0.987</v>
       </c>
-      <c r="I209" s="5" t="n">
+      <c r="I209" s="4" t="n">
         <v>0.987</v>
       </c>
-      <c r="J209" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" s="5" t="n">
+      <c r="J209" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" s="4" t="n">
         <v>0.8933333333333334</v>
       </c>
-      <c r="L209" s="5" t="n">
+      <c r="L209" s="4" t="n">
         <v>0.005897268670984716</v>
       </c>
     </row>
@@ -11427,28 +11425,28 @@
           <t>B4901</t>
         </is>
       </c>
-      <c r="E210" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F210" s="5" t="n">
+      <c r="E210" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" s="4" t="n">
         <v>2.573112508500956</v>
       </c>
-      <c r="G210" s="5" t="n">
+      <c r="G210" s="4" t="n">
         <v>0.013</v>
       </c>
-      <c r="H210" s="5" t="n">
+      <c r="H210" s="4" t="n">
         <v>0.013</v>
       </c>
-      <c r="I210" s="5" t="n">
+      <c r="I210" s="4" t="n">
         <v>0.013</v>
       </c>
-      <c r="J210" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" s="5" t="n">
+      <c r="J210" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" s="4" t="n">
         <v>0.1066666666666667</v>
       </c>
-      <c r="L210" s="5" t="n">
+      <c r="L210" s="4" t="n">
         <v>0.005897268670984712</v>
       </c>
     </row>
@@ -11473,22 +11471,22 @@
           <t>B4902</t>
         </is>
       </c>
-      <c r="E211" s="5" t="n">
+      <c r="E211" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F211" s="5" t="n"/>
-      <c r="G211" s="5" t="n"/>
-      <c r="H211" s="5" t="n"/>
-      <c r="I211" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J211" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K211" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L211" s="5" t="n">
+      <c r="F211" s="4" t="n"/>
+      <c r="G211" s="4" t="n"/>
+      <c r="H211" s="4" t="n"/>
+      <c r="I211" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11513,22 +11511,22 @@
           <t>B4903</t>
         </is>
       </c>
-      <c r="E212" s="5" t="n">
+      <c r="E212" s="4" t="n">
         <v>-0</v>
       </c>
-      <c r="F212" s="5" t="n"/>
-      <c r="G212" s="5" t="n"/>
-      <c r="H212" s="5" t="n"/>
-      <c r="I212" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J212" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L212" s="5" t="n">
+      <c r="F212" s="4" t="n"/>
+      <c r="G212" s="4" t="n"/>
+      <c r="H212" s="4" t="n"/>
+      <c r="I212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11553,22 +11551,22 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="E213" s="5" t="n"/>
-      <c r="F213" s="5" t="n"/>
-      <c r="G213" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H213" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I213" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J213" s="5" t="n"/>
-      <c r="K213" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L213" s="5" t="n"/>
+      <c r="E213" s="4" t="n"/>
+      <c r="F213" s="4" t="n"/>
+      <c r="G213" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" s="4" t="n"/>
+      <c r="K213" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -11591,20 +11589,20 @@
           <t>ensemble charge</t>
         </is>
       </c>
-      <c r="E214" s="5" t="n"/>
-      <c r="F214" s="5" t="n"/>
-      <c r="G214" s="5" t="n"/>
-      <c r="H214" s="5" t="n">
+      <c r="E214" s="4" t="n"/>
+      <c r="F214" s="4" t="n"/>
+      <c r="G214" s="4" t="n"/>
+      <c r="H214" s="4" t="n">
         <v>0.987</v>
       </c>
-      <c r="I214" s="5" t="n">
+      <c r="I214" s="4" t="n">
         <v>0.987</v>
       </c>
-      <c r="J214" s="5" t="n"/>
-      <c r="K214" s="5" t="n">
+      <c r="J214" s="4" t="n"/>
+      <c r="K214" s="4" t="n">
         <v>0.8933333333333334</v>
       </c>
-      <c r="L214" s="5" t="n"/>
+      <c r="L214" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables_Trials/kinase_project-trials-tables_values.xlsx
+++ b/tables_Trials/kinase_project-trials-tables_values.xlsx
@@ -540,34 +540,34 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.5233333333333333</v>
+        <v>0.5766666666666667</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.003333333333333337</v>
+        <v>0.062271805640898</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>-0.4266666666666665</v>
+        <v>-0.3733333333333332</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.003333333333333337</v>
+        <v>0.062271805640898</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.5166666666666667</v>
+        <v>0.4766666666666666</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.01201850425154664</v>
+        <v>0.01763834207376394</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.02516611478423582</v>
+        <v>0.03214550253664318</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.1833333333333333</v>
+        <v>0.1833333333333334</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.02788866755113585</v>
+        <v>0.03666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-9.299999999999999</v>
+        <v>-9.586666666666666</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.2542308662089115</v>
+        <v>0.1299145017993671</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.763333333333334</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.1457166199626291</v>
+        <v>0.1332082746845871</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.6599999999999984</v>
+        <v>0.8233333333333324</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.2930301463444789</v>
+        <v>0.1860704764927047</v>
       </c>
     </row>
     <row r="4">
@@ -664,22 +664,22 @@
         <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>-6.173333333333333</v>
+        <v>-6.19</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.008819171036882061</v>
+        <v>0.005773502691896392</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>-5.373333333333332</v>
+        <v>-5.373333333333334</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.01201850425154666</v>
+        <v>0.01763834207376407</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.8000000000000007</v>
+        <v>0.8166666666666664</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.01490711984999868</v>
+        <v>0.0185592145427669</v>
       </c>
     </row>
     <row r="5">
@@ -708,34 +708,34 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.7633333333333333</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.02333333333333336</v>
+        <v>0.01666666666666668</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.4633333333333333</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.02333333333333336</v>
+        <v>0.01666666666666668</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-7.093333333333334</v>
+        <v>-7.076666666666667</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.02905932629027105</v>
+        <v>0.03929942040850527</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-6.513333333333333</v>
+        <v>-6.476666666666667</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.03480102169636851</v>
+        <v>0.03844187531556909</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.580000000000001</v>
+        <v>0.6000000000000005</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.04533823502911808</v>
+        <v>0.05497474167490194</v>
       </c>
     </row>
     <row r="6">
@@ -764,34 +764,34 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.33</v>
+        <v>0.3499999999999999</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01527525231651947</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.04999999999999993</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01527525231651947</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-5.993333333333333</v>
+        <v>-6.03</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.04176654695380556</v>
+        <v>0.01154700538379253</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-5.72</v>
+        <v>-5.760000000000001</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.06027713773341715</v>
+        <v>0.009999999999999789</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.2733333333333334</v>
+        <v>0.2699999999999996</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.07333333333333339</v>
+        <v>0.01527525231651934</v>
       </c>
     </row>
     <row r="7">
@@ -820,34 +820,34 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.65</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.006666666666666673</v>
+        <v>0.005773502691896263</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.3466666666666666</v>
+        <v>0.35</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.006666666666666673</v>
+        <v>0.005773502691896263</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>-4.833333333333333</v>
+        <v>-4.873333333333334</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.05840471822645087</v>
+        <v>0.09207484877955421</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>-4.286666666666666</v>
+        <v>-4.326666666666667</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.04702245326555283</v>
+        <v>0.0906151814604545</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0.5466666666666669</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.07498147919467996</v>
+        <v>0.1291854825005073</v>
       </c>
     </row>
     <row r="8">
@@ -876,34 +876,34 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9733333333333333</v>
+        <v>0.9633333333333333</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0.003333333333333337</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.6366666666666668</v>
+        <v>-0.6466666666666668</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0.003333333333333337</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>6.993333333333333</v>
+        <v>7.023333333333333</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.02848001248439175</v>
+        <v>0.01452966314513554</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>7.736666666666667</v>
+        <v>7.743333333333333</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.02185812841434013</v>
+        <v>0.02027587510099415</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.7433333333333341</v>
+        <v>0.7199999999999998</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.03590109871423009</v>
+        <v>0.02494438257849299</v>
       </c>
     </row>
     <row r="9">
@@ -944,22 +944,22 @@
         <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-5.91</v>
+        <v>-5.796666666666667</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.005773502691896135</v>
+        <v>0.14379769740082</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>-4.986666666666667</v>
+        <v>-4.86</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.008819171036882061</v>
+        <v>0.140118997046558</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0.9233333333333329</v>
+        <v>0.9366666666666665</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.01054092553389461</v>
+        <v>0.200776271285008</v>
       </c>
     </row>
     <row r="10">
@@ -1000,22 +1000,22 @@
         <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-4.626666666666666</v>
+        <v>-4.59</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.02027587510099415</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-3.64</v>
+        <v>-3.606666666666667</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.01732050807568879</v>
+        <v>0.008819171036882033</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.9866666666666659</v>
+        <v>0.9833333333333329</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.02666666666666674</v>
+        <v>0.008819171036882033</v>
       </c>
     </row>
     <row r="11">
@@ -1056,22 +1056,22 @@
         <v>0.03666666666666667</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-8.396666666666667</v>
+        <v>-8.376666666666667</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.02728450923957465</v>
+        <v>0.01201850425154695</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-7.603333333333333</v>
+        <v>-7.593333333333334</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.05364492313143687</v>
+        <v>0.04702245326555301</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.7933333333333339</v>
+        <v>0.7833333333333332</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.06018490028422582</v>
+        <v>0.04853406592853693</v>
       </c>
     </row>
     <row r="12">
@@ -1100,34 +1100,34 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
+        <v>0.4133333333333333</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.1270607903503061</v>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>0.3233333333333333</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>0.1434495652756667</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>0.2333333333333333</v>
-      </c>
       <c r="J12" s="4" t="n">
-        <v>0.1434495652756667</v>
+        <v>0.1270607903503061</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>-4.596666666666667</v>
+        <v>-4.603333333333333</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.008819171036882005</v>
+        <v>0.01201850425154666</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>-4.28</v>
+        <v>-4.213333333333334</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1252996408614165</v>
+        <v>0.1277149604044534</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.3166666666666664</v>
+        <v>0.3899999999999997</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1256096245427783</v>
+        <v>0.128279209365959</v>
       </c>
     </row>
     <row r="13">
@@ -1156,34 +1156,34 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.05000000000000001</v>
+        <v>0.04666666666666667</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.01154700538379252</v>
+        <v>0.003333333333333334</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.02000000000000001</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.01154700538379252</v>
+        <v>0.003333333333333334</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.153333333333333</v>
+        <v>1.176666666666667</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.05333333333333331</v>
+        <v>0.05783117190965824</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>1.28</v>
+        <v>1.303333333333333</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.055075705472861</v>
+        <v>0.05238744548500569</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>0.1266666666666667</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.07666666666666663</v>
+        <v>0.07803133273813082</v>
       </c>
     </row>
     <row r="14">
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>-4.813333333333333</v>
+        <v>-4.806666666666666</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.008819171036882061</v>
+        <v>0.003333333333333262</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>-3.866666666666667</v>
+        <v>-3.853333333333333</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0.006666666666666673</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.9466666666666668</v>
+        <v>0.9533333333333327</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.01105541596785141</v>
+        <v>0.007453559924999273</v>
       </c>
     </row>
     <row r="15">
@@ -1268,34 +1268,34 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.9566666666666667</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.003333333333333337</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.01666666666666672</v>
+        <v>0.009999999999999898</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.003333333333333337</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-4.573333333333333</v>
+        <v>-4.58</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.02666666666666669</v>
+        <v>0.03785938897200204</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>-3.926666666666667</v>
+        <v>-3.94</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.02603416558635561</v>
+        <v>0.03785938897200178</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0.6466666666666661</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.03726779962499658</v>
+        <v>0.05354126134736348</v>
       </c>
     </row>
     <row r="16">
@@ -1324,13 +1324,13 @@
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.006666666666666667</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0.003333333333333334</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.2866666666666667</v>
+        <v>-0.2933333333333333</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>0.003333333333333334</v>
@@ -1339,7 +1339,7 @@
         <v>-3.01</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0</v>
+        <v>0.0115470053837924</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-2.943333333333333</v>
@@ -1351,7 +1351,7 @@
         <v>0.06666666666666643</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.01201850425154666</v>
+        <v>0.01666666666666661</v>
       </c>
     </row>
     <row r="17">
@@ -1392,22 +1392,22 @@
         <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.005773502691896263</v>
+        <v>0.02516611478423586</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1.543333333333333</v>
+        <v>1.58</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.003333333333333337</v>
+        <v>0.02645751311064586</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.02333333333333298</v>
+        <v>0.02000000000000024</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.006666666666666673</v>
+        <v>0.03651483716701106</v>
       </c>
     </row>
     <row r="18">
@@ -1448,22 +1448,22 @@
         <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>5.423333333333333</v>
+        <v>5.510000000000001</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.04484541349024553</v>
+        <v>0.04041451884327371</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>5.416666666666667</v>
+        <v>5.503333333333333</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.04409585518440991</v>
+        <v>0.04910306620885409</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>-0.006666666666665932</v>
+        <v>-0.006666666666667709</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.06289320754704394</v>
+        <v>0.06359594676112963</v>
       </c>
     </row>
     <row r="19">
@@ -1504,22 +1504,22 @@
         <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-1.653333333333333</v>
+        <v>-1.646666666666667</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.01201850425154664</v>
+        <v>0.006666666666666673</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>0.2</v>
+        <v>0.2033333333333333</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.01</v>
+        <v>0.006666666666666664</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1.853333333333333</v>
+        <v>1.85</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.01563471919941144</v>
+        <v>0.009428090415820637</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1560,22 @@
         <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.603333333333333</v>
+        <v>4.58</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.04484541349024582</v>
+        <v>0.005773502691896135</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>4.623333333333334</v>
+        <v>4.613333333333333</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.04333333333333343</v>
+        <v>0.006666666666666821</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.02000000000000046</v>
+        <v>0.03333333333333321</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.06236095644623251</v>
+        <v>0.008819171036882005</v>
       </c>
     </row>
     <row r="21">
@@ -1616,22 +1616,22 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>3.52</v>
+        <v>3.493333333333334</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.009999999999999934</v>
+        <v>0.0348010216963684</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>3.523333333333333</v>
+        <v>3.5</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.01452966314513552</v>
+        <v>0.02886751345948119</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0.003333333333333854</v>
+        <v>0.006666666666666377</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.01763834207376385</v>
+        <v>0.04521553322083498</v>
       </c>
     </row>
     <row r="22">
@@ -1660,34 +1660,34 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.8933333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.003333333333333337</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>-0.09666666666666646</v>
+        <v>-0.08999999999999986</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.003333333333333337</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.546666666666666</v>
+        <v>2.533333333333333</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.02185812841433998</v>
+        <v>0.00333333333333341</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>3.343333333333334</v>
+        <v>3.34</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.01763834207376395</v>
+        <v>0.02081665999466127</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.7966666666666673</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.02808716591058786</v>
+        <v>0.02108185106778915</v>
       </c>
     </row>
     <row r="23">
@@ -1716,34 +1716,34 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.2466666666666667</v>
+        <v>0.2233333333333334</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.02185812841434</v>
+        <v>0.003333333333333337</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-0.7433333333333332</v>
+        <v>-0.7666666666666665</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.02185812841434</v>
+        <v>0.003333333333333337</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-3.503333333333333</v>
+        <v>-3.516666666666667</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.02333333333333328</v>
+        <v>0.02403700850309314</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-3.43</v>
+        <v>-3.443333333333333</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.01527525231651943</v>
+        <v>0.01666666666666661</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>0.07333333333333369</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.02788866755113579</v>
+        <v>0.02924988129130694</v>
       </c>
     </row>
     <row r="24">
@@ -1784,22 +1784,22 @@
         <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-5.613333333333333</v>
+        <v>-5.609999999999999</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1685559583969405</v>
+        <v>0.1900876990584435</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>-4.673333333333333</v>
+        <v>-4.66</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1783566962889567</v>
+        <v>0.1852025917745214</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.9400000000000004</v>
+        <v>0.9499999999999993</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.2454021642574129</v>
+        <v>0.2653927906581741</v>
       </c>
     </row>
     <row r="25">
@@ -1840,22 +1840,22 @@
         <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-5.903333333333333</v>
+        <v>-5.733333333333333</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.01452966314513551</v>
+        <v>0.1867559310377524</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-4.973333333333334</v>
+        <v>-4.783333333333334</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.008819171036882061</v>
+        <v>0.1870234685214072</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>0.9299999999999997</v>
+        <v>0.9499999999999993</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.01699673171197594</v>
+        <v>0.2643020157992662</v>
       </c>
     </row>
     <row r="26">
@@ -1896,22 +1896,22 @@
         <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2233333333333333</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.07218802609235905</v>
+        <v>0.0523874454850057</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.2033333333333334</v>
+        <v>0.2233333333333334</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0717247826378334</v>
+        <v>0.05174724898753343</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.02999999999999994</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.101762250149825</v>
+        <v>0.07363574011458175</v>
       </c>
     </row>
     <row r="27">
@@ -1940,34 +1940,34 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0</v>
+        <v>0.003333333333333337</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.04000000000000004</v>
+        <v>-0.04333333333333322</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0</v>
+        <v>0.003333333333333337</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-6.406666666666666</v>
+        <v>-6.47</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.02962731472438545</v>
+        <v>0.0360555127546399</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-5.613333333333333</v>
+        <v>-5.653333333333333</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.03179797338056494</v>
+        <v>0.01855921454276693</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.793333333333333</v>
+        <v>0.8166666666666664</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.04346134936801783</v>
+        <v>0.04055175020198823</v>
       </c>
     </row>
     <row r="28">
@@ -2008,22 +2008,22 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-0.5166666666666667</v>
+        <v>-0.6133333333333333</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.05174724898753341</v>
+        <v>0.02333333333333336</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.1366666666666667</v>
+        <v>0.03</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.05811865258054232</v>
+        <v>0.01154700538379252</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.6533333333333334</v>
+        <v>0.6433333333333333</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.07781745019952502</v>
+        <v>0.02603416558635554</v>
       </c>
     </row>
     <row r="29">
@@ -2052,34 +2052,34 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.48</v>
+        <v>0.4966666666666666</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.02081665999466133</v>
+        <v>0.01201850425154664</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.18</v>
+        <v>0.1966666666666667</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.02081665999466133</v>
+        <v>0.01201850425154664</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.91</v>
+        <v>1.923333333333333</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0</v>
+        <v>0.01333333333333335</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.313333333333333</v>
+        <v>2.35</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.01763834207376395</v>
+        <v>0.03214550253664328</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.4033333333333331</v>
+        <v>0.426666666666667</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.01763834207376395</v>
+        <v>0.0348010216963686</v>
       </c>
     </row>
     <row r="30">
@@ -2111,31 +2111,31 @@
         <v>0.52</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.01154700538379253</v>
+        <v>0.005773502691896263</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-0.4699999999999999</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.01154700538379253</v>
+        <v>0.005773502691896263</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-3.54</v>
+        <v>-3.566666666666666</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.05567764362830015</v>
+        <v>0.03333333333333337</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-3.026666666666667</v>
+        <v>-3.056666666666667</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.06227180564089795</v>
+        <v>0.04096068575814838</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.5133333333333336</v>
+        <v>0.5099999999999998</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.08353309390761103</v>
+        <v>0.05280993172584957</v>
       </c>
     </row>
     <row r="31">
@@ -2176,22 +2176,22 @@
         <v>0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-3.873333333333333</v>
+        <v>-4.056666666666667</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1128912948125073</v>
+        <v>0.1183685393637647</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-3.483333333333333</v>
+        <v>-3.653333333333334</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1297861488928785</v>
+        <v>0.1120019841094095</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0.3900000000000001</v>
+        <v>0.4033333333333329</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1720142112992089</v>
+        <v>0.1629587541544042</v>
       </c>
     </row>
     <row r="32">
@@ -2220,34 +2220,34 @@
         <v>0</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.4633333333333333</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.008819171036881963</v>
+        <v>0.01763834207376394</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.1633333333333333</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.008819171036881963</v>
+        <v>0.01763834207376394</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>-1.396666666666667</v>
+        <v>-1.353333333333333</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.01333333333333327</v>
+        <v>0.008819171036881977</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>-0.9266666666666667</v>
+        <v>-0.8966666666666666</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.00881917103688195</v>
+        <v>0.03527668414752788</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>0.4699999999999998</v>
+        <v>0.4566666666666669</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.01598610507770901</v>
+        <v>0.03636237371545239</v>
       </c>
     </row>
     <row r="33">
@@ -2288,22 +2288,22 @@
         <v>0</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-2.14</v>
+        <v>-2.13</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.03464101615137758</v>
+        <v>0.01000000000000008</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>-1.493333333333333</v>
+        <v>-1.45</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.02333333333333336</v>
+        <v>0.01527525231651948</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>0.6466666666666667</v>
+        <v>0.6800000000000004</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.0417665469538056</v>
+        <v>0.0182574185835056</v>
       </c>
     </row>
     <row r="34">
@@ -2344,22 +2344,22 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>-5.463333333333334</v>
+        <v>-5.43</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.04409585518440996</v>
+        <v>0.02516611478423588</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>-4.506666666666667</v>
+        <v>-4.483333333333333</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.03756475889861544</v>
+        <v>0.02333333333333311</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.956666666666667</v>
+        <v>0.9466666666666663</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.05792715732327595</v>
+        <v>0.03431876713662323</v>
       </c>
     </row>
     <row r="35">
@@ -2400,22 +2400,22 @@
         <v>0</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-6.363333333333333</v>
+        <v>-6.22</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.02603416558635547</v>
+        <v>0.1350308606701939</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>-5.423333333333333</v>
+        <v>-5.283333333333333</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.02027587510099415</v>
+        <v>0.1316983084342562</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>0.9400000000000004</v>
+        <v>0.9366666666666665</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.03299831645537224</v>
+        <v>0.1886207246772682</v>
       </c>
     </row>
     <row r="36">
@@ -2456,22 +2456,22 @@
         <v>0</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-5.63</v>
+        <v>-5.626666666666666</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.1552417469626</v>
+        <v>0.1534419904864519</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-4.693333333333334</v>
+        <v>-4.71</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1550268793897797</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.9366666666666656</v>
+        <v>0.9166666666666661</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0.22776693741142</v>
+        <v>0.218123308653105</v>
       </c>
     </row>
     <row r="37">
@@ -2512,22 +2512,22 @@
         <v>0</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.05567764362830022</v>
+        <v>0.0338296385503074</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0.73</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.05859465277082315</v>
+        <v>0.04666666666666668</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0.99</v>
+        <v>1.016666666666667</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>0.0808290376865476</v>
+        <v>0.05763872155263528</v>
       </c>
     </row>
     <row r="38">
@@ -2556,34 +2556,34 @@
         <v>0</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.3133333333333333</v>
+        <v>0.2366666666666667</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.08412952976082641</v>
+        <v>0.006666666666666664</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.2233333333333333</v>
+        <v>0.1466666666666667</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>0.08412952976082641</v>
+        <v>0.006666666666666664</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>-8.023333333333333</v>
+        <v>-7.936666666666667</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.03844187531556922</v>
+        <v>0.02403700850309333</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>-7.733333333333333</v>
+        <v>-7.713333333333334</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.06741249472052241</v>
+        <v>0.03179797338056469</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>0.29</v>
+        <v>0.2233333333333327</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.07760297817881884</v>
+        <v>0.03986086914367123</v>
       </c>
     </row>
   </sheetData>
@@ -2716,10 +2716,10 @@
         <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.5596666666666668</v>
+        <v>0.5656666666666667</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.001452966314513559</v>
+        <v>0.003666666666666633</v>
       </c>
     </row>
     <row r="3">
@@ -2762,10 +2762,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.3966666666666667</v>
+        <v>0.3886666666666667</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.002333333333333335</v>
+        <v>0.003382963855030743</v>
       </c>
     </row>
     <row r="4">
@@ -2808,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.04366666666666667</v>
+        <v>0.04566666666666667</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0008819171036881955</v>
+        <v>0.0006666666666666674</v>
       </c>
     </row>
     <row r="5">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="L6" s="4" t="n"/>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n">
-        <v>0.9563333333333335</v>
+        <v>0.9543333333333333</v>
       </c>
       <c r="L7" s="4" t="n"/>
     </row>
@@ -3260,10 +3260,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.001527525231651947</v>
+        <v>0.0005773502691896258</v>
       </c>
     </row>
     <row r="16">
@@ -3306,10 +3306,10 @@
         <v>0</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.997</v>
+        <v>0.996</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.001527525231651948</v>
+        <v>0.0005773502691896263</v>
       </c>
     </row>
     <row r="17">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n">
-        <v>0.995027</v>
+        <v>0.995036</v>
       </c>
       <c r="L21" s="4" t="n"/>
     </row>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.324</v>
+        <v>0.4133333333333333</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1406307221058045</v>
+        <v>0.1255870658591525</v>
       </c>
     </row>
     <row r="23">
@@ -3638,10 +3638,10 @@
         <v>0</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.676</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1406307221058045</v>
+        <v>0.1255870658591526</v>
       </c>
     </row>
     <row r="25">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n">
-        <v>0.324</v>
+        <v>0.4133333333333333</v>
       </c>
       <c r="L26" s="4" t="n"/>
     </row>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.3123333333333333</v>
+        <v>0.2343333333333334</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.08504377957525433</v>
+        <v>0.0065659052011974</v>
       </c>
     </row>
     <row r="28">
@@ -3844,10 +3844,10 @@
         <v>0</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.6876666666666668</v>
+        <v>0.7656666666666667</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.08504377957525433</v>
+        <v>0.00656590520119741</v>
       </c>
     </row>
     <row r="30">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n">
-        <v>0.3123333333333333</v>
+        <v>0.2343333333333334</v>
       </c>
       <c r="L31" s="4" t="n"/>
     </row>
@@ -3964,10 +3964,10 @@
         <v>0</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.827</v>
+        <v>0.8263333333333334</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.03750999866702211</v>
+        <v>0.03733779735216194</v>
       </c>
     </row>
     <row r="33">
@@ -4010,10 +4010,10 @@
         <v>0</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.173</v>
+        <v>0.1736666666666667</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.03750999866702211</v>
+        <v>0.03733779735216194</v>
       </c>
     </row>
     <row r="34">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n">
-        <v>0.827</v>
+        <v>0.8263333333333334</v>
       </c>
       <c r="L35" s="4" t="n"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>0.9996666666666667</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>0</v>
+        <v>0.0003333333333333337</v>
       </c>
     </row>
     <row r="72">
@@ -5764,10 +5764,10 @@
         <v>0</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>0.0003333333333333333</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0</v>
+        <v>0.0003333333333333334</v>
       </c>
     </row>
     <row r="75">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n">
-        <v>1</v>
+        <v>0.9996666666666667</v>
       </c>
       <c r="L76" s="4" t="n"/>
     </row>
@@ -6142,10 +6142,10 @@
         <v>0</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0.999</v>
+        <v>0.9996666666666667</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>0.0005773502691896263</v>
+        <v>0.0003333333333333337</v>
       </c>
     </row>
     <row r="84">
@@ -6188,10 +6188,10 @@
         <v>0</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0.001</v>
+        <v>0.0003333333333333333</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.0005773502691896258</v>
+        <v>0.0003333333333333334</v>
       </c>
     </row>
     <row r="85">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="n">
-        <v>0.999</v>
+        <v>0.9996666666666667</v>
       </c>
       <c r="L86" s="4" t="n"/>
     </row>
@@ -6686,10 +6686,10 @@
         <v>0</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0.9456666666666665</v>
+        <v>0.945</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.0003333333333333337</v>
+        <v>0.0005773502691896263</v>
       </c>
     </row>
     <row r="97">
@@ -6772,10 +6772,10 @@
         <v>0</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0.05433333333333334</v>
+        <v>0.055</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>0.0003333333333333337</v>
+        <v>0.0005773502691896263</v>
       </c>
     </row>
     <row r="99">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="L99" s="4" t="n"/>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="n">
-        <v>0.9456666666666665</v>
+        <v>0.945</v>
       </c>
       <c r="L100" s="4" t="n"/>
     </row>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0.96</v>
+        <v>0.9613333333333333</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>0.001527525231651948</v>
+        <v>0.0003333333333333337</v>
       </c>
     </row>
     <row r="102">
@@ -6978,10 +6978,10 @@
         <v>0</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0.04</v>
+        <v>0.03866666666666666</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>0.001527525231651946</v>
+        <v>0.0003333333333333337</v>
       </c>
     </row>
     <row r="104">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="L104" s="4" t="n"/>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="n">
-        <v>0.96</v>
+        <v>0.9613333333333333</v>
       </c>
       <c r="L105" s="4" t="n"/>
     </row>
@@ -7098,10 +7098,10 @@
         <v>0</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0.7623333333333333</v>
+        <v>0.783</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>0.02409933147989336</v>
+        <v>0.01656301099840648</v>
       </c>
     </row>
     <row r="107">
@@ -7270,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0.2376666666666667</v>
+        <v>0.217</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>0.02409933147989332</v>
+        <v>0.01656301099840646</v>
       </c>
     </row>
     <row r="111">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="J112" s="4" t="n"/>
       <c r="K112" s="4" t="n">
-        <v>0.7623333333333333</v>
+        <v>0.783</v>
       </c>
       <c r="L112" s="4" t="n"/>
     </row>
@@ -7390,10 +7390,10 @@
         <v>0</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0.331</v>
+        <v>0.3496666666666666</v>
       </c>
       <c r="L113" s="4" t="n">
-        <v>0.01539480431834065</v>
+        <v>0.001201850425154664</v>
       </c>
     </row>
     <row r="114">
@@ -7562,10 +7562,10 @@
         <v>0</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0.669</v>
+        <v>0.6503333333333333</v>
       </c>
       <c r="L117" s="4" t="n">
-        <v>0.01539480431834063</v>
+        <v>0.001201850425154664</v>
       </c>
     </row>
     <row r="118">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="J119" s="4" t="n"/>
       <c r="K119" s="4" t="n">
-        <v>0.331</v>
+        <v>0.3496666666666666</v>
       </c>
       <c r="L119" s="4" t="n"/>
     </row>
@@ -7682,10 +7682,10 @@
         <v>0</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.6513333333333334</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.008212456663169955</v>
+        <v>0.006936217348894943</v>
       </c>
     </row>
     <row r="121">
@@ -7854,10 +7854,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0.3533333333333333</v>
+        <v>0.3486666666666667</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0.008212456663169936</v>
+        <v>0.006936217348894928</v>
       </c>
     </row>
     <row r="125">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="J126" s="4" t="n"/>
       <c r="K126" s="4" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.6513333333333334</v>
       </c>
       <c r="L126" s="4" t="n"/>
     </row>
@@ -7974,10 +7974,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0.016</v>
+        <v>0.009333333333333334</v>
       </c>
       <c r="L127" s="4" t="n">
-        <v>0.002</v>
+        <v>0.004666666666666667</v>
       </c>
     </row>
     <row r="128">
@@ -8146,10 +8146,10 @@
         <v>0</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0.984</v>
+        <v>0.9906666666666667</v>
       </c>
       <c r="L131" s="4" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.004666666666666671</v>
       </c>
     </row>
     <row r="132">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="J133" s="4" t="n"/>
       <c r="K133" s="4" t="n">
-        <v>0.016</v>
+        <v>0.009333333333333334</v>
       </c>
       <c r="L133" s="4" t="n"/>
     </row>
@@ -8266,10 +8266,10 @@
         <v>0</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0.4796666666666667</v>
+        <v>0.4973333333333333</v>
       </c>
       <c r="L134" s="4" t="n">
-        <v>0.02186575201339097</v>
+        <v>0.01297861488928787</v>
       </c>
     </row>
     <row r="135">
@@ -8438,10 +8438,10 @@
         <v>0</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0.5203333333333333</v>
+        <v>0.5026666666666667</v>
       </c>
       <c r="L138" s="4" t="n">
-        <v>0.02186575201339098</v>
+        <v>0.01297861488928787</v>
       </c>
     </row>
     <row r="139">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="J140" s="4" t="n"/>
       <c r="K140" s="4" t="n">
-        <v>0.4796666666666667</v>
+        <v>0.4973333333333333</v>
       </c>
       <c r="L140" s="4" t="n"/>
     </row>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0.4716666666666667</v>
+        <v>0.4623333333333333</v>
       </c>
       <c r="L141" s="4" t="n">
-        <v>0.007264831572567782</v>
+        <v>0.01858613581260087</v>
       </c>
     </row>
     <row r="142">
@@ -8730,10 +8730,10 @@
         <v>0</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0.5283333333333333</v>
+        <v>0.5376666666666666</v>
       </c>
       <c r="L145" s="4" t="n">
-        <v>0.007264831572567796</v>
+        <v>0.01858613581260085</v>
       </c>
     </row>
     <row r="146">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="J147" s="4" t="n"/>
       <c r="K147" s="4" t="n">
-        <v>0.4716666666666667</v>
+        <v>0.4623333333333333</v>
       </c>
       <c r="L147" s="4" t="n"/>
     </row>
@@ -8850,10 +8850,10 @@
         <v>0</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0.5233333333333333</v>
+        <v>0.5756666666666667</v>
       </c>
       <c r="L148" s="4" t="n">
-        <v>0.004371625682868005</v>
+        <v>0.06091615366861056</v>
       </c>
     </row>
     <row r="149">
@@ -8936,10 +8936,10 @@
         <v>0</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0.4766666666666666</v>
+        <v>0.4243333333333334</v>
       </c>
       <c r="L150" s="4" t="n">
-        <v>0.004371625682867987</v>
+        <v>0.06091615366861058</v>
       </c>
     </row>
     <row r="151">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="J152" s="4" t="n"/>
       <c r="K152" s="4" t="n">
-        <v>0.5233333333333333</v>
+        <v>0.5756666666666667</v>
       </c>
       <c r="L152" s="4" t="n"/>
     </row>
@@ -9056,10 +9056,10 @@
         <v>0</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0.984</v>
+        <v>0.9846666666666666</v>
       </c>
       <c r="L153" s="4" t="n">
-        <v>0.001154700538379253</v>
+        <v>0.002185812841434002</v>
       </c>
     </row>
     <row r="154">
@@ -9102,10 +9102,10 @@
         <v>0</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0.002666666666666667</v>
+        <v>0.003333333333333334</v>
       </c>
       <c r="L154" s="4" t="n">
-        <v>0.001333333333333334</v>
+        <v>0.0006666666666666668</v>
       </c>
     </row>
     <row r="155">
@@ -9148,10 +9148,10 @@
         <v>0</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0.002666666666666667</v>
+        <v>0.004</v>
       </c>
       <c r="L155" s="4" t="n">
-        <v>0.001333333333333334</v>
+        <v>0.002309401076758503</v>
       </c>
     </row>
     <row r="156">
@@ -9188,10 +9188,10 @@
         <v>0</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="L156" s="4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -9314,10 +9314,10 @@
         <v>0</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0.009666666666666665</v>
+        <v>0.008</v>
       </c>
       <c r="L159" s="4" t="n">
-        <v>0.0003333333333333337</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="160">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="J160" s="4" t="n"/>
       <c r="K160" s="4" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="L160" s="4" t="n"/>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="J161" s="4" t="n"/>
       <c r="K161" s="4" t="n">
-        <v>0.9903333333333334</v>
+        <v>0.9919999999999999</v>
       </c>
       <c r="L161" s="4" t="n"/>
     </row>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0.04866666666666667</v>
+        <v>0.04266666666666667</v>
       </c>
       <c r="L162" s="4" t="n">
-        <v>0.01026861453383291</v>
+        <v>0.003382963855030741</v>
       </c>
     </row>
     <row r="163">
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0.9513333333333334</v>
+        <v>0.9573333333333333</v>
       </c>
       <c r="L163" s="4" t="n">
-        <v>0.01026861453383288</v>
+        <v>0.003382963855030743</v>
       </c>
     </row>
     <row r="164">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="J164" s="4" t="n"/>
       <c r="K164" s="4" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="L164" s="4" t="n"/>
     </row>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="J165" s="4" t="n"/>
       <c r="K165" s="4" t="n">
-        <v>0.04866666666666667</v>
+        <v>0.04266666666666667</v>
       </c>
       <c r="L165" s="4" t="n"/>
     </row>
@@ -9600,10 +9600,10 @@
         <v>0</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0.2446666666666667</v>
+        <v>0.2216666666666667</v>
       </c>
       <c r="L166" s="4" t="n">
-        <v>0.02248209163855633</v>
+        <v>0.005174724898753346</v>
       </c>
     </row>
     <row r="167">
@@ -9646,10 +9646,10 @@
         <v>0</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0.7543333333333333</v>
+        <v>0.7766666666666667</v>
       </c>
       <c r="L167" s="4" t="n">
-        <v>0.02292984469589314</v>
+        <v>0.005364492313143699</v>
       </c>
     </row>
     <row r="168">
@@ -9686,10 +9686,10 @@
         <v>0</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0.001</v>
+        <v>0.001666666666666667</v>
       </c>
       <c r="L168" s="4" t="n">
-        <v>0.0005773502691896258</v>
+        <v>0.0003333333333333334</v>
       </c>
     </row>
     <row r="169">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="J170" s="4" t="n"/>
       <c r="K170" s="4" t="n">
-        <v>0.2446666666666667</v>
+        <v>0.2216666666666667</v>
       </c>
       <c r="L170" s="4" t="n"/>
     </row>
@@ -9806,10 +9806,10 @@
         <v>0</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0.5206666666666667</v>
+        <v>0.522</v>
       </c>
       <c r="L171" s="4" t="n">
-        <v>0.01089852181618122</v>
+        <v>0.005686240703077332</v>
       </c>
     </row>
     <row r="172">
@@ -9852,10 +9852,10 @@
         <v>0</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0.4793333333333333</v>
+        <v>0.478</v>
       </c>
       <c r="L172" s="4" t="n">
-        <v>0.01089852181618121</v>
+        <v>0.005686240703077332</v>
       </c>
     </row>
     <row r="173">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="J175" s="4" t="n"/>
       <c r="K175" s="4" t="n">
-        <v>0.5206666666666667</v>
+        <v>0.522</v>
       </c>
       <c r="L175" s="4" t="n"/>
     </row>
@@ -10012,10 +10012,10 @@
         <v>0</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>0.971</v>
+        <v>0.9613333333333333</v>
       </c>
       <c r="L176" s="4" t="n">
-        <v>0.004000000000000004</v>
+        <v>0.00284800124843918</v>
       </c>
     </row>
     <row r="177">
@@ -10150,10 +10150,10 @@
         <v>0</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0.029</v>
+        <v>0.03866666666666667</v>
       </c>
       <c r="L179" s="4" t="n">
-        <v>0.004</v>
+        <v>0.002848001248439177</v>
       </c>
     </row>
     <row r="180">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="J180" s="4" t="n"/>
       <c r="K180" s="4" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="L180" s="4" t="n"/>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="J181" s="4" t="n"/>
       <c r="K181" s="4" t="n">
-        <v>0.971</v>
+        <v>0.9613333333333333</v>
       </c>
       <c r="L181" s="4" t="n"/>
     </row>
@@ -10316,7 +10316,7 @@
         <v>0</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>0.9603333333333333</v>
+        <v>0.9606666666666666</v>
       </c>
       <c r="L183" s="4" t="n">
         <v>0.0003333333333333337</v>
@@ -10362,7 +10362,7 @@
         <v>0</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0.03966666666666666</v>
+        <v>0.03933333333333333</v>
       </c>
       <c r="L184" s="4" t="n">
         <v>0.0003333333333333337</v>
@@ -10531,7 +10531,7 @@
         <v>0.988</v>
       </c>
       <c r="L188" s="4" t="n">
-        <v>0.0005773502691896263</v>
+        <v>0.001000000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -10577,7 +10577,7 @@
         <v>0.012</v>
       </c>
       <c r="L189" s="4" t="n">
-        <v>0.0005773502691896258</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="190">
@@ -11398,10 +11398,10 @@
         <v>0</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>0.8933333333333334</v>
+        <v>0.899</v>
       </c>
       <c r="L209" s="4" t="n">
-        <v>0.005897268670984716</v>
+        <v>0.01101514109457221</v>
       </c>
     </row>
     <row r="210">
@@ -11444,10 +11444,10 @@
         <v>0</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.101</v>
       </c>
       <c r="L210" s="4" t="n">
-        <v>0.005897268670984712</v>
+        <v>0.01101514109457221</v>
       </c>
     </row>
     <row r="211">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="J214" s="4" t="n"/>
       <c r="K214" s="4" t="n">
-        <v>0.8933333333333334</v>
+        <v>0.899</v>
       </c>
       <c r="L214" s="4" t="n"/>
     </row>
